--- a/ReportforHeaderU/ReportforHeaderU.xlsx
+++ b/ReportforHeaderU/ReportforHeaderU.xlsx
@@ -3122,7 +3122,7 @@
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>70.81</v>
+        <v>70.52</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -3887,10 +3887,10 @@
         <v>72.26000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>92.97</v>
+        <v>85.05</v>
       </c>
       <c r="K77" t="n">
-        <v>77.72</v>
+        <v>84.95</v>
       </c>
     </row>
     <row r="78">
@@ -4234,9 +4234,11 @@
       <c r="I85" t="n">
         <v>111.04</v>
       </c>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="n">
+        <v>110.2</v>
+      </c>
       <c r="K85" t="n">
-        <v>159.7</v>
+        <v>100.76</v>
       </c>
     </row>
     <row r="86">
@@ -6075,13 +6077,13 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>87.65000000000001</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="J126" t="n">
         <v>83.06</v>
       </c>
       <c r="K126" t="n">
-        <v>105.53</v>
+        <v>105.96</v>
       </c>
     </row>
     <row r="127">
@@ -6165,13 +6167,13 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>48.41</v>
+        <v>48.33</v>
       </c>
       <c r="J128" t="n">
         <v>46.73</v>
       </c>
       <c r="K128" t="n">
-        <v>103.6</v>
+        <v>103.44</v>
       </c>
     </row>
     <row r="129">
@@ -7014,13 +7016,13 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>49.83</v>
+        <v>50.4</v>
       </c>
       <c r="J147" t="n">
-        <v>50.44</v>
+        <v>51.05</v>
       </c>
       <c r="K147" t="n">
-        <v>98.79000000000001</v>
+        <v>98.73999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -7777,13 +7779,13 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>42.05</v>
+        <v>41.99</v>
       </c>
       <c r="J164" t="n">
-        <v>41.44</v>
+        <v>41.99</v>
       </c>
       <c r="K164" t="n">
-        <v>101.46</v>
+        <v>100</v>
       </c>
     </row>
     <row r="165">
@@ -7912,10 +7914,10 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>46.63</v>
+        <v>47.16</v>
       </c>
       <c r="J167" t="n">
-        <v>46.63</v>
+        <v>47.16</v>
       </c>
       <c r="K167" t="n">
         <v>100</v>
@@ -8002,13 +8004,13 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>40.83</v>
+        <v>40.96</v>
       </c>
       <c r="J169" t="n">
         <v>40.83</v>
       </c>
       <c r="K169" t="n">
-        <v>100</v>
+        <v>100.32</v>
       </c>
     </row>
     <row r="170">
@@ -8137,13 +8139,13 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>39.23</v>
+        <v>38.75</v>
       </c>
       <c r="J172" t="n">
-        <v>38.93</v>
+        <v>38.48</v>
       </c>
       <c r="K172" t="n">
-        <v>100.78</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="173">
@@ -9157,7 +9159,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9202,7 +9204,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9247,7 +9249,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9292,7 +9294,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9337,7 +9339,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9427,7 +9429,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9472,7 +9474,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9517,7 +9519,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9562,7 +9564,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9607,7 +9609,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9652,7 +9654,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9697,7 +9699,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -10149,12 +10151,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="n">
+        <v>283.8</v>
+      </c>
       <c r="J217" t="n">
         <v>283.8</v>
       </c>
       <c r="K217" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="218">
@@ -10192,12 +10196,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="n">
+        <v>306.66</v>
+      </c>
       <c r="J218" t="n">
         <v>306.66</v>
       </c>
       <c r="K218" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="219">
@@ -10235,12 +10241,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
+      <c r="I219" t="n">
+        <v>75.41</v>
+      </c>
       <c r="J219" t="n">
         <v>75.41</v>
       </c>
       <c r="K219" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="220">
@@ -10278,12 +10286,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
+      <c r="I220" t="n">
+        <v>252.66</v>
+      </c>
       <c r="J220" t="n">
         <v>252.66</v>
       </c>
       <c r="K220" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="221">
@@ -10367,13 +10377,13 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>29.24</v>
+        <v>29.5</v>
       </c>
       <c r="J222" t="n">
         <v>29.5</v>
       </c>
       <c r="K222" t="n">
-        <v>99.15000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="223">
@@ -10403,7 +10413,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10547,10 +10557,10 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>170.83</v>
+        <v>171.23</v>
       </c>
       <c r="J226" t="n">
-        <v>170.83</v>
+        <v>171.23</v>
       </c>
       <c r="K226" t="n">
         <v>100</v>
@@ -13724,13 +13734,13 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>29.47</v>
+        <v>29.53</v>
       </c>
       <c r="J297" t="n">
         <v>29.17</v>
       </c>
       <c r="K297" t="n">
-        <v>101.01</v>
+        <v>101.21</v>
       </c>
     </row>
     <row r="298">
@@ -13814,13 +13824,13 @@
         </is>
       </c>
       <c r="I299" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="J299" t="n">
         <v>23.75</v>
       </c>
-      <c r="J299" t="n">
-        <v>23.44</v>
-      </c>
       <c r="K299" t="n">
-        <v>101.34</v>
+        <v>102.36</v>
       </c>
     </row>
     <row r="300">
@@ -13993,12 +14003,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
+      <c r="I303" t="n">
+        <v>13.56</v>
+      </c>
       <c r="J303" t="n">
-        <v>14.26</v>
+        <v>14.02</v>
       </c>
       <c r="K303" t="n">
-        <v>0</v>
+        <v>96.67</v>
       </c>
     </row>
     <row r="304">
@@ -14036,12 +14048,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr"/>
+      <c r="I304" t="n">
+        <v>46.04</v>
+      </c>
       <c r="J304" t="n">
         <v>45.99</v>
       </c>
       <c r="K304" t="n">
-        <v>0</v>
+        <v>100.11</v>
       </c>
     </row>
     <row r="305">
@@ -14083,10 +14097,10 @@
         <v>38.61</v>
       </c>
       <c r="J305" t="n">
-        <v>38.99</v>
+        <v>38.75</v>
       </c>
       <c r="K305" t="n">
-        <v>99.03</v>
+        <v>99.65000000000001</v>
       </c>
     </row>
     <row r="306">
@@ -16056,13 +16070,13 @@
         </is>
       </c>
       <c r="I349" t="n">
-        <v>54.93</v>
+        <v>54.97</v>
       </c>
       <c r="J349" t="n">
-        <v>54.76</v>
+        <v>54.8</v>
       </c>
       <c r="K349" t="n">
-        <v>100.32</v>
+        <v>100.31</v>
       </c>
     </row>
     <row r="350">
@@ -16101,13 +16115,13 @@
         </is>
       </c>
       <c r="I350" t="n">
-        <v>47.15</v>
+        <v>47.46</v>
       </c>
       <c r="J350" t="n">
         <v>47.09</v>
       </c>
       <c r="K350" t="n">
-        <v>100.12</v>
+        <v>100.78</v>
       </c>
     </row>
     <row r="351">
@@ -16146,13 +16160,13 @@
         </is>
       </c>
       <c r="I351" t="n">
-        <v>92.47</v>
+        <v>93.7</v>
       </c>
       <c r="J351" t="n">
-        <v>84.64</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="K351" t="n">
-        <v>109.26</v>
+        <v>108.58</v>
       </c>
     </row>
     <row r="352">
@@ -16182,7 +16196,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -16227,7 +16241,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -16504,13 +16518,13 @@
         </is>
       </c>
       <c r="I359" t="n">
-        <v>52.31</v>
+        <v>52.01</v>
       </c>
       <c r="J359" t="n">
-        <v>51.18</v>
+        <v>51.16</v>
       </c>
       <c r="K359" t="n">
-        <v>102.2</v>
+        <v>101.66</v>
       </c>
     </row>
     <row r="360">
@@ -16996,12 +17010,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I370" t="inlineStr"/>
+      <c r="I370" t="n">
+        <v>72.17</v>
+      </c>
       <c r="J370" t="n">
         <v>82</v>
       </c>
       <c r="K370" t="n">
-        <v>0</v>
+        <v>88.01000000000001</v>
       </c>
     </row>
     <row r="371">
@@ -19323,10 +19339,10 @@
         </is>
       </c>
       <c r="I422" t="n">
-        <v>29.43</v>
+        <v>32.25</v>
       </c>
       <c r="J422" t="n">
-        <v>29.43</v>
+        <v>32.25</v>
       </c>
       <c r="K422" t="n">
         <v>100</v>
@@ -19680,12 +19696,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I430" t="inlineStr"/>
+      <c r="I430" t="n">
+        <v>189.29</v>
+      </c>
       <c r="J430" t="n">
         <v>188.93</v>
       </c>
       <c r="K430" t="n">
-        <v>0</v>
+        <v>100.19</v>
       </c>
     </row>
     <row r="431">
@@ -20576,12 +20594,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I450" t="inlineStr"/>
+      <c r="I450" t="n">
+        <v>12.51</v>
+      </c>
       <c r="J450" t="n">
         <v>12.11</v>
       </c>
       <c r="K450" t="n">
-        <v>0</v>
+        <v>103.32</v>
       </c>
     </row>
     <row r="451">
@@ -23400,10 +23420,10 @@
         <v>51.73</v>
       </c>
       <c r="J514" t="n">
-        <v>51.81</v>
+        <v>51.85</v>
       </c>
       <c r="K514" t="n">
-        <v>99.84999999999999</v>
+        <v>99.77</v>
       </c>
     </row>
     <row r="515">
@@ -23442,10 +23462,10 @@
         </is>
       </c>
       <c r="I515" t="n">
-        <v>26.12</v>
+        <v>26.17</v>
       </c>
       <c r="J515" t="n">
-        <v>26.19</v>
+        <v>26.24</v>
       </c>
       <c r="K515" t="n">
         <v>99.73999999999999</v>
@@ -23578,7 +23598,7 @@
       </c>
       <c r="I518" t="inlineStr"/>
       <c r="J518" t="n">
-        <v>73.31999999999999</v>
+        <v>72.45</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
@@ -27260,10 +27280,10 @@
         </is>
       </c>
       <c r="I601" t="n">
-        <v>150.42</v>
+        <v>150.55</v>
       </c>
       <c r="J601" t="n">
-        <v>150.51</v>
+        <v>150.64</v>
       </c>
       <c r="K601" t="n">
         <v>99.94</v>
@@ -27485,10 +27505,10 @@
         </is>
       </c>
       <c r="I606" t="n">
-        <v>8.94</v>
+        <v>9.82</v>
       </c>
       <c r="J606" t="n">
-        <v>8.94</v>
+        <v>9.82</v>
       </c>
       <c r="K606" t="n">
         <v>100</v>
@@ -27755,13 +27775,13 @@
         </is>
       </c>
       <c r="I612" t="n">
-        <v>371.67</v>
+        <v>366.54</v>
       </c>
       <c r="J612" t="n">
         <v>380.71</v>
       </c>
       <c r="K612" t="n">
-        <v>97.63</v>
+        <v>96.28</v>
       </c>
     </row>
     <row r="613">
@@ -27845,10 +27865,10 @@
         </is>
       </c>
       <c r="I614" t="n">
-        <v>16.53</v>
+        <v>16.23</v>
       </c>
       <c r="J614" t="n">
-        <v>16.53</v>
+        <v>16.23</v>
       </c>
       <c r="K614" t="n">
         <v>100</v>
@@ -27890,10 +27910,10 @@
         </is>
       </c>
       <c r="I615" t="n">
-        <v>17.81</v>
+        <v>17.83</v>
       </c>
       <c r="J615" t="n">
-        <v>17.81</v>
+        <v>17.83</v>
       </c>
       <c r="K615" t="n">
         <v>100</v>
@@ -28159,12 +28179,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I621" t="inlineStr"/>
+      <c r="I621" t="n">
+        <v>42.01</v>
+      </c>
       <c r="J621" t="n">
-        <v>41.31</v>
+        <v>42.01</v>
       </c>
       <c r="K621" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="622">
@@ -28428,10 +28450,10 @@
         </is>
       </c>
       <c r="I627" t="n">
-        <v>36.46</v>
+        <v>36.17</v>
       </c>
       <c r="J627" t="n">
-        <v>36.46</v>
+        <v>36.17</v>
       </c>
       <c r="K627" t="n">
         <v>100</v>
@@ -28563,10 +28585,10 @@
         </is>
       </c>
       <c r="I630" t="n">
-        <v>51.76</v>
+        <v>52</v>
       </c>
       <c r="J630" t="n">
-        <v>51.76</v>
+        <v>52</v>
       </c>
       <c r="K630" t="n">
         <v>100</v>
@@ -29448,7 +29470,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -29493,7 +29515,7 @@
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -29538,7 +29560,7 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -29583,7 +29605,7 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -29628,7 +29650,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -29718,7 +29740,7 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -29763,7 +29785,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -29808,7 +29830,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -29853,7 +29875,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -29898,7 +29920,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -29943,7 +29965,7 @@
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -29988,7 +30010,7 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -30661,7 +30683,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -31835,12 +31857,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I703" t="inlineStr"/>
+      <c r="I703" t="n">
+        <v>25.28</v>
+      </c>
       <c r="J703" t="n">
-        <v>25.25</v>
+        <v>25.28</v>
       </c>
       <c r="K703" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="704">
@@ -31882,10 +31906,10 @@
         <v>61.74</v>
       </c>
       <c r="J704" t="n">
-        <v>62.21</v>
+        <v>61.74</v>
       </c>
       <c r="K704" t="n">
-        <v>99.23999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="705">
@@ -34035,13 +34059,13 @@
         </is>
       </c>
       <c r="I752" t="n">
-        <v>25</v>
+        <v>25.06</v>
       </c>
       <c r="J752" t="n">
         <v>24.73</v>
       </c>
       <c r="K752" t="n">
-        <v>101.1</v>
+        <v>101.33</v>
       </c>
     </row>
     <row r="753">
@@ -34124,12 +34148,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I754" t="inlineStr"/>
+      <c r="I754" t="n">
+        <v>26.04</v>
+      </c>
       <c r="J754" t="n">
         <v>25.85</v>
       </c>
       <c r="K754" t="n">
-        <v>0</v>
+        <v>100.76</v>
       </c>
     </row>
     <row r="755">
@@ -34168,13 +34194,13 @@
         </is>
       </c>
       <c r="I755" t="n">
-        <v>39.26</v>
+        <v>39.31</v>
       </c>
       <c r="J755" t="n">
         <v>39.31</v>
       </c>
       <c r="K755" t="n">
-        <v>99.88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="756">
@@ -34302,12 +34328,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I758" t="inlineStr"/>
+      <c r="I758" t="n">
+        <v>43.48</v>
+      </c>
       <c r="J758" t="n">
         <v>44.14</v>
       </c>
       <c r="K758" t="n">
-        <v>0</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="759">
@@ -34345,12 +34373,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I759" t="inlineStr"/>
+      <c r="I759" t="n">
+        <v>44.78</v>
+      </c>
       <c r="J759" t="n">
-        <v>43.73</v>
+        <v>44.53</v>
       </c>
       <c r="K759" t="n">
-        <v>0</v>
+        <v>100.57</v>
       </c>
     </row>
     <row r="760">
@@ -34389,13 +34419,13 @@
         </is>
       </c>
       <c r="I760" t="n">
-        <v>170.52</v>
+        <v>172.22</v>
       </c>
       <c r="J760" t="n">
-        <v>173.13</v>
+        <v>172.22</v>
       </c>
       <c r="K760" t="n">
-        <v>98.48999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="761">
@@ -34434,10 +34464,10 @@
         </is>
       </c>
       <c r="I761" t="n">
-        <v>22.52</v>
+        <v>23.35</v>
       </c>
       <c r="J761" t="n">
-        <v>22.57</v>
+        <v>23.4</v>
       </c>
       <c r="K761" t="n">
         <v>99.79000000000001</v>
@@ -34842,10 +34872,10 @@
         <v>53.02</v>
       </c>
       <c r="J770" t="n">
-        <v>53.03</v>
+        <v>53.02</v>
       </c>
       <c r="K770" t="n">
-        <v>99.98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="771">
@@ -34887,10 +34917,10 @@
         <v>66.94</v>
       </c>
       <c r="J771" t="n">
-        <v>69.55</v>
+        <v>66.94</v>
       </c>
       <c r="K771" t="n">
-        <v>96.25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="772">
@@ -34932,10 +34962,10 @@
         <v>141.01</v>
       </c>
       <c r="J772" t="n">
-        <v>138.48</v>
+        <v>141.01</v>
       </c>
       <c r="K772" t="n">
-        <v>101.82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="773">
@@ -34973,12 +35003,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I773" t="inlineStr"/>
+      <c r="I773" t="n">
+        <v>22.01</v>
+      </c>
       <c r="J773" t="n">
         <v>22.01</v>
       </c>
       <c r="K773" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="774">
@@ -35016,12 +35048,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I774" t="inlineStr"/>
+      <c r="I774" t="n">
+        <v>27.64</v>
+      </c>
       <c r="J774" t="n">
-        <v>27.46</v>
+        <v>27.64</v>
       </c>
       <c r="K774" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="775">
@@ -35063,10 +35097,10 @@
         <v>65.3</v>
       </c>
       <c r="J775" t="n">
-        <v>62.54</v>
+        <v>65.3</v>
       </c>
       <c r="K775" t="n">
-        <v>104.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="776">
@@ -35243,10 +35277,10 @@
         <v>41.65</v>
       </c>
       <c r="J779" t="n">
-        <v>41.94</v>
+        <v>41.65</v>
       </c>
       <c r="K779" t="n">
-        <v>99.31</v>
+        <v>100</v>
       </c>
     </row>
     <row r="780">
@@ -35284,12 +35318,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I780" t="inlineStr"/>
+      <c r="I780" t="n">
+        <v>42.35</v>
+      </c>
       <c r="J780" t="n">
         <v>42.35</v>
       </c>
       <c r="K780" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="781">
@@ -35327,12 +35363,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I781" t="inlineStr"/>
+      <c r="I781" t="n">
+        <v>59.48</v>
+      </c>
       <c r="J781" t="n">
         <v>59.56</v>
       </c>
       <c r="K781" t="n">
-        <v>0</v>
+        <v>99.86</v>
       </c>
     </row>
     <row r="782">
@@ -36260,7 +36298,7 @@
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
@@ -36303,7 +36341,7 @@
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
@@ -36580,13 +36618,13 @@
         </is>
       </c>
       <c r="I809" t="n">
-        <v>32.9</v>
+        <v>32.71</v>
       </c>
       <c r="J809" t="n">
-        <v>32.97</v>
+        <v>32.69</v>
       </c>
       <c r="K809" t="n">
-        <v>99.77</v>
+        <v>100.06</v>
       </c>
     </row>
     <row r="810">
@@ -36892,12 +36930,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I816" t="inlineStr"/>
+      <c r="I816" t="n">
+        <v>65.47</v>
+      </c>
       <c r="J816" t="n">
-        <v>67.48999999999999</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K816" t="n">
-        <v>0</v>
+        <v>99.22</v>
       </c>
     </row>
     <row r="817">
@@ -38949,13 +38989,13 @@
         </is>
       </c>
       <c r="I862" t="n">
-        <v>29.68</v>
+        <v>29.91</v>
       </c>
       <c r="J862" t="n">
         <v>29.91</v>
       </c>
       <c r="K862" t="n">
-        <v>99.26000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="863">
@@ -39263,12 +39303,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I869" t="inlineStr"/>
+      <c r="I869" t="n">
+        <v>153.42</v>
+      </c>
       <c r="J869" t="n">
         <v>155.67</v>
       </c>
       <c r="K869" t="n">
-        <v>0</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="870">
@@ -40118,10 +40160,10 @@
         <v>11.56</v>
       </c>
       <c r="J888" t="n">
-        <v>11.96</v>
+        <v>11.68</v>
       </c>
       <c r="K888" t="n">
-        <v>96.68000000000001</v>
+        <v>98.98</v>
       </c>
     </row>
     <row r="889">
@@ -42147,9 +42189,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I935" t="inlineStr"/>
-      <c r="J935" t="inlineStr"/>
-      <c r="K935" t="inlineStr"/>
+      <c r="I935" t="n">
+        <v>217.05</v>
+      </c>
+      <c r="J935" t="n">
+        <v>217.05</v>
+      </c>
+      <c r="K935" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="n">
@@ -42232,13 +42280,13 @@
         </is>
       </c>
       <c r="I937" t="n">
-        <v>97.73999999999999</v>
+        <v>98.53</v>
       </c>
       <c r="J937" t="n">
         <v>98.92</v>
       </c>
       <c r="K937" t="n">
-        <v>98.8</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="938">
@@ -42322,13 +42370,13 @@
         </is>
       </c>
       <c r="I939" t="n">
-        <v>688.7</v>
+        <v>679.27</v>
       </c>
       <c r="J939" t="n">
-        <v>686.02</v>
+        <v>676.89</v>
       </c>
       <c r="K939" t="n">
-        <v>100.39</v>
+        <v>100.35</v>
       </c>
     </row>
     <row r="940">
@@ -42367,13 +42415,13 @@
         </is>
       </c>
       <c r="I940" t="n">
-        <v>497.69</v>
+        <v>519.4</v>
       </c>
       <c r="J940" t="n">
         <v>519.4</v>
       </c>
       <c r="K940" t="n">
-        <v>95.81999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="941">
@@ -42411,9 +42459,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I941" t="inlineStr"/>
-      <c r="J941" t="inlineStr"/>
-      <c r="K941" t="inlineStr"/>
+      <c r="I941" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="J941" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="K941" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="942">
       <c r="A942" t="n">
@@ -42851,7 +42905,7 @@
       </c>
       <c r="I951" t="inlineStr"/>
       <c r="J951" t="n">
-        <v>77.23999999999999</v>
+        <v>76.97</v>
       </c>
       <c r="K951" t="n">
         <v>0</v>
@@ -44526,13 +44580,13 @@
         </is>
       </c>
       <c r="I989" t="n">
-        <v>55.91</v>
+        <v>55.35</v>
       </c>
       <c r="J989" t="n">
-        <v>59.73</v>
+        <v>57.48</v>
       </c>
       <c r="K989" t="n">
-        <v>93.61</v>
+        <v>96.29000000000001</v>
       </c>
     </row>
     <row r="990">
@@ -45876,13 +45930,13 @@
         </is>
       </c>
       <c r="I1019" t="n">
-        <v>85.91</v>
+        <v>85.2</v>
       </c>
       <c r="J1019" t="n">
-        <v>83.31999999999999</v>
+        <v>82.47</v>
       </c>
       <c r="K1019" t="n">
-        <v>103.11</v>
+        <v>103.31</v>
       </c>
     </row>
     <row r="1020">
@@ -46760,10 +46814,10 @@
         </is>
       </c>
       <c r="I1039" t="n">
-        <v>22.99</v>
+        <v>23.18</v>
       </c>
       <c r="J1039" t="n">
-        <v>23.19</v>
+        <v>23.39</v>
       </c>
       <c r="K1039" t="n">
         <v>99.12</v>
@@ -46808,10 +46862,10 @@
         <v>49.22</v>
       </c>
       <c r="J1040" t="n">
-        <v>49.49</v>
+        <v>49.65</v>
       </c>
       <c r="K1040" t="n">
-        <v>99.45999999999999</v>
+        <v>99.14</v>
       </c>
     </row>
     <row r="1041">
@@ -47567,10 +47621,10 @@
         <v>35.08</v>
       </c>
       <c r="J1057" t="n">
-        <v>34.3</v>
+        <v>35.08</v>
       </c>
       <c r="K1057" t="n">
-        <v>102.25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1058">
@@ -47790,10 +47844,10 @@
         <v>35.11</v>
       </c>
       <c r="J1062" t="n">
-        <v>35.37</v>
+        <v>35.11</v>
       </c>
       <c r="K1062" t="n">
-        <v>99.26000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1063">
@@ -47835,10 +47889,10 @@
         <v>29.92</v>
       </c>
       <c r="J1063" t="n">
-        <v>29.55</v>
+        <v>29.92</v>
       </c>
       <c r="K1063" t="n">
-        <v>101.26</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1064">
@@ -47921,12 +47975,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1065" t="inlineStr"/>
+      <c r="I1065" t="n">
+        <v>36.53</v>
+      </c>
       <c r="J1065" t="n">
         <v>36.53</v>
       </c>
       <c r="K1065" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1066">
@@ -48274,10 +48330,10 @@
         </is>
       </c>
       <c r="I1073" t="n">
-        <v>20.65</v>
+        <v>20.71</v>
       </c>
       <c r="J1073" t="n">
-        <v>20.65</v>
+        <v>20.71</v>
       </c>
       <c r="K1073" t="n">
         <v>100</v>
@@ -48318,12 +48374,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1074" t="inlineStr"/>
+      <c r="I1074" t="n">
+        <v>7.79</v>
+      </c>
       <c r="J1074" t="n">
         <v>7.79</v>
       </c>
       <c r="K1074" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1075">
@@ -48801,7 +48859,7 @@
       </c>
       <c r="G1085" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1085" t="inlineStr">
@@ -48846,7 +48904,7 @@
       </c>
       <c r="G1086" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1086" t="inlineStr">
@@ -48889,7 +48947,7 @@
       </c>
       <c r="G1087" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1087" t="inlineStr">
@@ -48934,7 +48992,7 @@
       </c>
       <c r="G1088" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1088" t="inlineStr">
@@ -48977,7 +49035,7 @@
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1089" t="inlineStr">
@@ -49067,7 +49125,7 @@
       </c>
       <c r="G1091" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1091" t="inlineStr">
@@ -49112,7 +49170,7 @@
       </c>
       <c r="G1092" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1092" t="inlineStr">
@@ -49157,7 +49215,7 @@
       </c>
       <c r="G1093" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1093" t="inlineStr">
@@ -49202,7 +49260,7 @@
       </c>
       <c r="G1094" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1094" t="inlineStr">
@@ -49247,7 +49305,7 @@
       </c>
       <c r="G1095" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1095" t="inlineStr">
@@ -49292,7 +49350,7 @@
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1096" t="inlineStr">
@@ -49337,7 +49395,7 @@
       </c>
       <c r="G1097" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1097" t="inlineStr">
@@ -50006,7 +50064,7 @@
       </c>
       <c r="G1112" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1112" t="inlineStr">
@@ -50951,12 +51009,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1133" t="inlineStr"/>
+      <c r="I1133" t="n">
+        <v>250.24</v>
+      </c>
       <c r="J1133" t="n">
         <v>250.24</v>
       </c>
       <c r="K1133" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1134">
@@ -50994,12 +51054,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1134" t="inlineStr"/>
+      <c r="I1134" t="n">
+        <v>21.03</v>
+      </c>
       <c r="J1134" t="n">
-        <v>21.22</v>
+        <v>21.03</v>
       </c>
       <c r="K1134" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1135">
@@ -51037,12 +51099,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1135" t="inlineStr"/>
+      <c r="I1135" t="n">
+        <v>56.92</v>
+      </c>
       <c r="J1135" t="n">
-        <v>58.41</v>
+        <v>56.92</v>
       </c>
       <c r="K1135" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1136">
@@ -53217,13 +53281,13 @@
         </is>
       </c>
       <c r="I1184" t="n">
-        <v>30.58</v>
+        <v>30.63</v>
       </c>
       <c r="J1184" t="n">
         <v>30.38</v>
       </c>
       <c r="K1184" t="n">
-        <v>100.66</v>
+        <v>100.84</v>
       </c>
     </row>
     <row r="1185">
@@ -53306,12 +53370,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1186" t="inlineStr"/>
+      <c r="I1186" t="n">
+        <v>26.77</v>
+      </c>
       <c r="J1186" t="n">
-        <v>25.5</v>
+        <v>25.98</v>
       </c>
       <c r="K1186" t="n">
-        <v>0</v>
+        <v>103.05</v>
       </c>
     </row>
     <row r="1187">
@@ -53440,10 +53506,10 @@
         </is>
       </c>
       <c r="I1189" t="n">
-        <v>14.69</v>
+        <v>14.65</v>
       </c>
       <c r="J1189" t="n">
-        <v>14.69</v>
+        <v>14.65</v>
       </c>
       <c r="K1189" t="n">
         <v>100</v>
@@ -53484,12 +53550,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1190" t="inlineStr"/>
+      <c r="I1190" t="n">
+        <v>41.17</v>
+      </c>
       <c r="J1190" t="n">
-        <v>42.02</v>
+        <v>40.66</v>
       </c>
       <c r="K1190" t="n">
-        <v>0</v>
+        <v>101.26</v>
       </c>
     </row>
     <row r="1191">
@@ -53527,12 +53595,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1191" t="inlineStr"/>
+      <c r="I1191" t="n">
+        <v>37.79</v>
+      </c>
       <c r="J1191" t="n">
-        <v>36.12</v>
+        <v>37.13</v>
       </c>
       <c r="K1191" t="n">
-        <v>0</v>
+        <v>101.78</v>
       </c>
     </row>
     <row r="1192">
@@ -53570,12 +53640,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1192" t="inlineStr"/>
+      <c r="I1192" t="n">
+        <v>149.26</v>
+      </c>
       <c r="J1192" t="n">
         <v>148.64</v>
       </c>
       <c r="K1192" t="n">
-        <v>0</v>
+        <v>100.42</v>
       </c>
     </row>
     <row r="1193">
@@ -53613,12 +53685,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1193" t="inlineStr"/>
+      <c r="I1193" t="n">
+        <v>14.29</v>
+      </c>
       <c r="J1193" t="n">
-        <v>14.27</v>
+        <v>14.31</v>
       </c>
       <c r="K1193" t="n">
-        <v>0</v>
+        <v>99.86</v>
       </c>
     </row>
     <row r="1194">
@@ -53656,12 +53730,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1194" t="inlineStr"/>
+      <c r="I1194" t="n">
+        <v>43.91</v>
+      </c>
       <c r="J1194" t="n">
-        <v>44.13</v>
+        <v>43.12</v>
       </c>
       <c r="K1194" t="n">
-        <v>0</v>
+        <v>101.82</v>
       </c>
     </row>
     <row r="1195">
@@ -55350,7 +55426,7 @@
       </c>
       <c r="G1232" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1232" t="inlineStr">
@@ -55395,7 +55471,7 @@
       </c>
       <c r="G1233" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1233" t="inlineStr">
@@ -55534,7 +55610,7 @@
       </c>
       <c r="I1236" t="inlineStr"/>
       <c r="J1236" t="n">
-        <v>165</v>
+        <v>159.45</v>
       </c>
       <c r="K1236" t="n">
         <v>0</v>
@@ -55576,13 +55652,13 @@
         </is>
       </c>
       <c r="I1237" t="n">
-        <v>20.98</v>
+        <v>19.91</v>
       </c>
       <c r="J1237" t="n">
-        <v>20.99</v>
+        <v>19.91</v>
       </c>
       <c r="K1237" t="n">
-        <v>99.98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1238">
@@ -55665,12 +55741,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1239" t="inlineStr"/>
+      <c r="I1239" t="n">
+        <v>34.93</v>
+      </c>
       <c r="J1239" t="n">
-        <v>35.04</v>
+        <v>35.65</v>
       </c>
       <c r="K1239" t="n">
-        <v>0</v>
+        <v>97.98</v>
       </c>
     </row>
     <row r="1240">
@@ -55709,13 +55787,13 @@
         </is>
       </c>
       <c r="I1240" t="n">
-        <v>76.08</v>
+        <v>47.21</v>
       </c>
       <c r="J1240" t="n">
-        <v>77.37</v>
+        <v>47.85</v>
       </c>
       <c r="K1240" t="n">
-        <v>98.33</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="1241">
@@ -58420,13 +58498,13 @@
         </is>
       </c>
       <c r="I1301" t="n">
-        <v>149.82</v>
+        <v>143.34</v>
       </c>
       <c r="J1301" t="n">
-        <v>151.72</v>
+        <v>145.45</v>
       </c>
       <c r="K1301" t="n">
-        <v>98.75</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="1302">
@@ -59143,10 +59221,10 @@
         <v>17.1</v>
       </c>
       <c r="J1317" t="n">
-        <v>14.7</v>
+        <v>17.1</v>
       </c>
       <c r="K1317" t="n">
-        <v>116.29</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1318">
@@ -59625,10 +59703,10 @@
         </is>
       </c>
       <c r="I1328" t="n">
-        <v>28.11</v>
+        <v>28.51</v>
       </c>
       <c r="J1328" t="n">
-        <v>28.05</v>
+        <v>28.45</v>
       </c>
       <c r="K1328" t="n">
         <v>100.21</v>
@@ -60610,10 +60688,10 @@
         <v>89.48</v>
       </c>
       <c r="J1350" t="n">
-        <v>88.84999999999999</v>
+        <v>88.41</v>
       </c>
       <c r="K1350" t="n">
-        <v>100.71</v>
+        <v>101.21</v>
       </c>
     </row>
     <row r="1351">
@@ -60790,10 +60868,10 @@
         <v>99.42</v>
       </c>
       <c r="J1354" t="n">
-        <v>102.59</v>
+        <v>102.17</v>
       </c>
       <c r="K1354" t="n">
-        <v>96.92</v>
+        <v>97.31</v>
       </c>
     </row>
     <row r="1355">
@@ -61229,11 +61307,13 @@
         </is>
       </c>
       <c r="I1364" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1364" t="inlineStr"/>
+        <v>33.99</v>
+      </c>
+      <c r="J1364" t="n">
+        <v>33.99</v>
+      </c>
       <c r="K1364" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1365">
@@ -61272,10 +61352,10 @@
         </is>
       </c>
       <c r="I1365" t="n">
-        <v>286.03</v>
+        <v>212.69</v>
       </c>
       <c r="J1365" t="n">
-        <v>286.03</v>
+        <v>212.69</v>
       </c>
       <c r="K1365" t="n">
         <v>100</v>
@@ -61317,10 +61397,10 @@
         </is>
       </c>
       <c r="I1366" t="n">
-        <v>327.4</v>
+        <v>326.46</v>
       </c>
       <c r="J1366" t="n">
-        <v>327.4</v>
+        <v>326.46</v>
       </c>
       <c r="K1366" t="n">
         <v>100</v>
@@ -61362,10 +61442,10 @@
         </is>
       </c>
       <c r="I1367" t="n">
-        <v>117.3</v>
+        <v>122.09</v>
       </c>
       <c r="J1367" t="n">
-        <v>117.3</v>
+        <v>122.09</v>
       </c>
       <c r="K1367" t="n">
         <v>100</v>
@@ -61497,10 +61577,10 @@
         </is>
       </c>
       <c r="I1370" t="n">
-        <v>399.67</v>
+        <v>435.43</v>
       </c>
       <c r="J1370" t="n">
-        <v>399.67</v>
+        <v>435.43</v>
       </c>
       <c r="K1370" t="n">
         <v>100</v>
@@ -61545,10 +61625,10 @@
         <v>630.4299999999999</v>
       </c>
       <c r="J1371" t="n">
-        <v>632.2</v>
+        <v>630.4299999999999</v>
       </c>
       <c r="K1371" t="n">
-        <v>99.72</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1372">
@@ -61587,13 +61667,13 @@
         </is>
       </c>
       <c r="I1372" t="n">
-        <v>58.78</v>
+        <v>63.52</v>
       </c>
       <c r="J1372" t="n">
-        <v>61.8</v>
+        <v>63.34</v>
       </c>
       <c r="K1372" t="n">
-        <v>95.12</v>
+        <v>100.29</v>
       </c>
     </row>
     <row r="1373">
@@ -61680,10 +61760,10 @@
         <v>79.64</v>
       </c>
       <c r="J1374" t="n">
-        <v>79.17</v>
+        <v>81.05</v>
       </c>
       <c r="K1374" t="n">
-        <v>100.59</v>
+        <v>98.26000000000001</v>
       </c>
     </row>
     <row r="1375">
@@ -61860,10 +61940,10 @@
         <v>56</v>
       </c>
       <c r="J1378" t="n">
-        <v>56.08</v>
+        <v>56</v>
       </c>
       <c r="K1378" t="n">
-        <v>99.84999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1379">
@@ -63442,9 +63522,15 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1414" t="inlineStr"/>
-      <c r="J1414" t="inlineStr"/>
-      <c r="K1414" t="inlineStr"/>
+      <c r="I1414" t="n">
+        <v>198.42</v>
+      </c>
+      <c r="J1414" t="n">
+        <v>198.42</v>
+      </c>
+      <c r="K1414" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="1415">
       <c r="A1415" t="n">
@@ -63616,9 +63702,15 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1418" t="inlineStr"/>
-      <c r="J1418" t="inlineStr"/>
-      <c r="K1418" t="inlineStr"/>
+      <c r="I1418" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J1418" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="K1418" t="n">
+        <v>90.06999999999999</v>
+      </c>
     </row>
     <row r="1419">
       <c r="A1419" t="n">
@@ -64961,13 +65053,13 @@
         </is>
       </c>
       <c r="I1448" t="n">
-        <v>83.67</v>
+        <v>84.2</v>
       </c>
       <c r="J1448" t="n">
         <v>80.25</v>
       </c>
       <c r="K1448" t="n">
-        <v>104.26</v>
+        <v>104.92</v>
       </c>
     </row>
     <row r="1449">
@@ -65718,10 +65810,10 @@
         </is>
       </c>
       <c r="I1465" t="n">
-        <v>79.04000000000001</v>
+        <v>79.16</v>
       </c>
       <c r="J1465" t="n">
-        <v>79.81999999999999</v>
+        <v>79.94</v>
       </c>
       <c r="K1465" t="n">
         <v>99.02</v>
@@ -66258,10 +66350,10 @@
         </is>
       </c>
       <c r="I1477" t="n">
-        <v>347.96</v>
+        <v>346.7</v>
       </c>
       <c r="J1477" t="n">
-        <v>363.97</v>
+        <v>362.65</v>
       </c>
       <c r="K1477" t="n">
         <v>95.59999999999999</v>
@@ -66754,10 +66846,10 @@
         <v>49.68</v>
       </c>
       <c r="J1488" t="n">
-        <v>50.13</v>
+        <v>49.47</v>
       </c>
       <c r="K1488" t="n">
-        <v>99.11</v>
+        <v>100.42</v>
       </c>
     </row>
     <row r="1489">
@@ -66795,12 +66887,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1489" t="inlineStr"/>
+      <c r="I1489" t="n">
+        <v>51.58</v>
+      </c>
       <c r="J1489" t="n">
         <v>51.58</v>
       </c>
       <c r="K1489" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1490">
@@ -66929,10 +67023,10 @@
         </is>
       </c>
       <c r="I1492" t="n">
-        <v>41.57</v>
+        <v>41.71</v>
       </c>
       <c r="J1492" t="n">
-        <v>41.57</v>
+        <v>41.71</v>
       </c>
       <c r="K1492" t="n">
         <v>100</v>
@@ -67109,10 +67203,10 @@
         </is>
       </c>
       <c r="I1496" t="n">
-        <v>160.53</v>
+        <v>160.81</v>
       </c>
       <c r="J1496" t="n">
-        <v>160.53</v>
+        <v>160.81</v>
       </c>
       <c r="K1496" t="n">
         <v>100</v>
@@ -67334,10 +67428,10 @@
         </is>
       </c>
       <c r="I1501" t="n">
-        <v>32.8</v>
+        <v>32.95</v>
       </c>
       <c r="J1501" t="n">
-        <v>32.82</v>
+        <v>32.97</v>
       </c>
       <c r="K1501" t="n">
         <v>99.93000000000001</v>
@@ -67378,12 +67472,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1502" t="inlineStr"/>
+      <c r="I1502" t="n">
+        <v>21.48</v>
+      </c>
       <c r="J1502" t="n">
-        <v>21.36</v>
+        <v>21.48</v>
       </c>
       <c r="K1502" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1503">
@@ -67953,7 +68049,7 @@
       </c>
       <c r="G1515" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1515" t="inlineStr">
@@ -67998,7 +68094,7 @@
       </c>
       <c r="G1516" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1516" t="inlineStr">
@@ -68043,7 +68139,7 @@
       </c>
       <c r="G1517" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1517" t="inlineStr">
@@ -68088,7 +68184,7 @@
       </c>
       <c r="G1518" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1518" t="inlineStr">
@@ -68133,7 +68229,7 @@
       </c>
       <c r="G1519" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1519" t="inlineStr">
@@ -68178,7 +68274,7 @@
       </c>
       <c r="G1520" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1520" t="inlineStr">
@@ -68223,7 +68319,7 @@
       </c>
       <c r="G1521" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1521" t="inlineStr">
@@ -68268,7 +68364,7 @@
       </c>
       <c r="G1522" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1522" t="inlineStr">
@@ -68313,7 +68409,7 @@
       </c>
       <c r="G1523" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1523" t="inlineStr">
@@ -68358,7 +68454,7 @@
       </c>
       <c r="G1524" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1524" t="inlineStr">
@@ -68403,7 +68499,7 @@
       </c>
       <c r="G1525" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1525" t="inlineStr">
@@ -68448,7 +68544,7 @@
       </c>
       <c r="G1526" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1526" t="inlineStr">
@@ -68493,7 +68589,7 @@
       </c>
       <c r="G1527" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1527" t="inlineStr">
@@ -68538,7 +68634,7 @@
       </c>
       <c r="G1528" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1528" t="inlineStr">
@@ -69213,7 +69309,7 @@
       </c>
       <c r="G1543" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1543" t="inlineStr">
@@ -70392,10 +70488,10 @@
         </is>
       </c>
       <c r="I1569" t="n">
-        <v>21.5</v>
+        <v>24.59</v>
       </c>
       <c r="J1569" t="n">
-        <v>21.5</v>
+        <v>24.59</v>
       </c>
       <c r="K1569" t="n">
         <v>100</v>
@@ -71288,13 +71384,13 @@
         </is>
       </c>
       <c r="I1589" t="n">
-        <v>464.8</v>
+        <v>465.17</v>
       </c>
       <c r="J1589" t="n">
-        <v>466.02</v>
+        <v>465.17</v>
       </c>
       <c r="K1589" t="n">
-        <v>99.73999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1590">
@@ -71378,10 +71474,10 @@
         </is>
       </c>
       <c r="I1591" t="n">
-        <v>9.619999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="J1591" t="n">
-        <v>9.619999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="K1591" t="n">
         <v>100</v>
@@ -71423,13 +71519,13 @@
         </is>
       </c>
       <c r="I1592" t="n">
-        <v>13.76</v>
+        <v>16.05</v>
       </c>
       <c r="J1592" t="n">
         <v>13.76</v>
       </c>
       <c r="K1592" t="n">
-        <v>100</v>
+        <v>116.65</v>
       </c>
     </row>
     <row r="1593">
@@ -71692,12 +71788,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1598" t="inlineStr"/>
+      <c r="I1598" t="n">
+        <v>239.93</v>
+      </c>
       <c r="J1598" t="n">
-        <v>251.17</v>
+        <v>239.93</v>
       </c>
       <c r="K1598" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1599">
@@ -71780,12 +71878,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1600" t="inlineStr"/>
+      <c r="I1600" t="n">
+        <v>98.3</v>
+      </c>
       <c r="J1600" t="n">
-        <v>101.24</v>
+        <v>98.3</v>
       </c>
       <c r="K1600" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1601">
@@ -71823,12 +71923,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1601" t="inlineStr"/>
+      <c r="I1601" t="n">
+        <v>244.65</v>
+      </c>
       <c r="J1601" t="n">
-        <v>227.44</v>
+        <v>244.65</v>
       </c>
       <c r="K1601" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1602">
@@ -72542,13 +72644,13 @@
         </is>
       </c>
       <c r="I1617" t="n">
-        <v>26.15</v>
+        <v>26.11</v>
       </c>
       <c r="J1617" t="n">
         <v>26.18</v>
       </c>
       <c r="K1617" t="n">
-        <v>99.89</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="1618">
@@ -72902,10 +73004,10 @@
         </is>
       </c>
       <c r="I1625" t="n">
-        <v>164.88</v>
+        <v>164.89</v>
       </c>
       <c r="J1625" t="n">
-        <v>164.88</v>
+        <v>164.89</v>
       </c>
       <c r="K1625" t="n">
         <v>100</v>
@@ -72995,10 +73097,10 @@
         <v>46.21</v>
       </c>
       <c r="J1627" t="n">
-        <v>48.86</v>
+        <v>46.21</v>
       </c>
       <c r="K1627" t="n">
-        <v>94.58</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1628">
@@ -74732,7 +74834,7 @@
       </c>
       <c r="G1666" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1666" t="inlineStr">
@@ -74777,7 +74879,7 @@
       </c>
       <c r="G1667" t="inlineStr">
         <is>
-          <t>มารียา</t>
+          <t>แคท</t>
         </is>
       </c>
       <c r="H1667" t="inlineStr">
@@ -74785,12 +74887,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1667" t="inlineStr"/>
+      <c r="I1667" t="n">
+        <v>52.37</v>
+      </c>
       <c r="J1667" t="n">
         <v>55.03</v>
       </c>
       <c r="K1667" t="n">
-        <v>0</v>
+        <v>95.18000000000001</v>
       </c>
     </row>
     <row r="1668">
@@ -74828,12 +74932,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1668" t="inlineStr"/>
+      <c r="I1668" t="n">
+        <v>81.27</v>
+      </c>
       <c r="J1668" t="n">
-        <v>78.34</v>
+        <v>77.02</v>
       </c>
       <c r="K1668" t="n">
-        <v>0</v>
+        <v>105.52</v>
       </c>
     </row>
     <row r="1669">
@@ -75010,10 +75116,10 @@
         <v>59.69</v>
       </c>
       <c r="J1672" t="n">
-        <v>59.64</v>
+        <v>60.5</v>
       </c>
       <c r="K1672" t="n">
-        <v>100.08</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="1673">
@@ -75055,10 +75161,10 @@
         <v>39.17</v>
       </c>
       <c r="J1673" t="n">
-        <v>39.22</v>
+        <v>39.11</v>
       </c>
       <c r="K1673" t="n">
-        <v>99.88</v>
+        <v>100.17</v>
       </c>
     </row>
     <row r="1674">
@@ -75097,13 +75203,13 @@
         </is>
       </c>
       <c r="I1674" t="n">
-        <v>43.46</v>
+        <v>43.88</v>
       </c>
       <c r="J1674" t="n">
-        <v>45.2</v>
+        <v>44.53</v>
       </c>
       <c r="K1674" t="n">
-        <v>96.15000000000001</v>
+        <v>98.54000000000001</v>
       </c>
     </row>
     <row r="1675">
@@ -77605,10 +77711,10 @@
         </is>
       </c>
       <c r="I1730" t="n">
-        <v>53.21</v>
+        <v>47.88</v>
       </c>
       <c r="J1730" t="n">
-        <v>53.21</v>
+        <v>47.88</v>
       </c>
       <c r="K1730" t="n">
         <v>100</v>
@@ -78055,13 +78161,13 @@
         </is>
       </c>
       <c r="I1740" t="n">
-        <v>149.13</v>
+        <v>161.92</v>
       </c>
       <c r="J1740" t="n">
-        <v>150.41</v>
+        <v>162.26</v>
       </c>
       <c r="K1740" t="n">
-        <v>99.15000000000001</v>
+        <v>99.79000000000001</v>
       </c>
     </row>
     <row r="1741">
@@ -78190,10 +78296,10 @@
         </is>
       </c>
       <c r="I1743" t="n">
-        <v>28.37</v>
+        <v>25.67</v>
       </c>
       <c r="J1743" t="n">
-        <v>28.37</v>
+        <v>25.67</v>
       </c>
       <c r="K1743" t="n">
         <v>100</v>
@@ -78955,10 +79061,10 @@
         </is>
       </c>
       <c r="I1760" t="n">
-        <v>6.29</v>
+        <v>6.14</v>
       </c>
       <c r="J1760" t="n">
-        <v>6.29</v>
+        <v>6.14</v>
       </c>
       <c r="K1760" t="n">
         <v>100</v>
@@ -79000,10 +79106,10 @@
         </is>
       </c>
       <c r="I1761" t="n">
-        <v>7.23</v>
+        <v>7.03</v>
       </c>
       <c r="J1761" t="n">
-        <v>7.23</v>
+        <v>7.03</v>
       </c>
       <c r="K1761" t="n">
         <v>100</v>

--- a/ReportforHeaderU/ReportforHeaderU.xlsx
+++ b/ReportforHeaderU/ReportforHeaderU.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6984,10 +6984,10 @@
         <v>22.73</v>
       </c>
       <c r="J146" t="n">
-        <v>22.67</v>
+        <v>22.92</v>
       </c>
       <c r="K146" t="n">
-        <v>100.25</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="147">
@@ -7026,13 +7026,13 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>50.49</v>
+        <v>50.93</v>
       </c>
       <c r="J147" t="n">
-        <v>51.11</v>
+        <v>51.57</v>
       </c>
       <c r="K147" t="n">
-        <v>98.79000000000001</v>
+        <v>98.76000000000001</v>
       </c>
     </row>
     <row r="148">
@@ -7389,10 +7389,10 @@
         <v>415.81</v>
       </c>
       <c r="J155" t="n">
-        <v>418.07</v>
+        <v>417.01</v>
       </c>
       <c r="K155" t="n">
-        <v>99.45999999999999</v>
+        <v>99.70999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -27255,13 +27255,13 @@
         </is>
       </c>
       <c r="I600" t="n">
-        <v>72.15000000000001</v>
+        <v>71.62</v>
       </c>
       <c r="J600" t="n">
         <v>71.5</v>
       </c>
       <c r="K600" t="n">
-        <v>100.9</v>
+        <v>100.17</v>
       </c>
     </row>
     <row r="601">
@@ -27300,13 +27300,13 @@
         </is>
       </c>
       <c r="I601" t="n">
-        <v>149.69</v>
+        <v>149.57</v>
       </c>
       <c r="J601" t="n">
-        <v>149.77</v>
+        <v>149.49</v>
       </c>
       <c r="K601" t="n">
-        <v>99.94</v>
+        <v>100.05</v>
       </c>
     </row>
     <row r="602">
@@ -27393,10 +27393,10 @@
         <v>22.32</v>
       </c>
       <c r="J603" t="n">
-        <v>22.4</v>
+        <v>22.34</v>
       </c>
       <c r="K603" t="n">
-        <v>99.64</v>
+        <v>99.87</v>
       </c>
     </row>
     <row r="604">
@@ -27525,10 +27525,10 @@
         </is>
       </c>
       <c r="I606" t="n">
-        <v>10.53</v>
+        <v>10.14</v>
       </c>
       <c r="J606" t="n">
-        <v>10.53</v>
+        <v>10.14</v>
       </c>
       <c r="K606" t="n">
         <v>100</v>
@@ -27795,13 +27795,13 @@
         </is>
       </c>
       <c r="I612" t="n">
-        <v>376.53</v>
+        <v>381.05</v>
       </c>
       <c r="J612" t="n">
-        <v>389.44</v>
+        <v>387.03</v>
       </c>
       <c r="K612" t="n">
-        <v>96.68000000000001</v>
+        <v>98.45</v>
       </c>
     </row>
     <row r="613">
@@ -46833,13 +46833,13 @@
         </is>
       </c>
       <c r="I1038" t="n">
-        <v>23.18</v>
+        <v>23.23</v>
       </c>
       <c r="J1038" t="n">
         <v>23.39</v>
       </c>
       <c r="K1038" t="n">
-        <v>99.12</v>
+        <v>99.33</v>
       </c>
     </row>
     <row r="1039">
@@ -65927,10 +65927,10 @@
         <v>134.49</v>
       </c>
       <c r="J1465" t="n">
-        <v>133.93</v>
+        <v>133.57</v>
       </c>
       <c r="K1465" t="n">
-        <v>100.42</v>
+        <v>100.69</v>
       </c>
     </row>
     <row r="1466">
@@ -66062,10 +66062,10 @@
         <v>47.1</v>
       </c>
       <c r="J1468" t="n">
-        <v>47.64</v>
+        <v>47.37</v>
       </c>
       <c r="K1468" t="n">
-        <v>98.86</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="1469">
@@ -66107,10 +66107,10 @@
         <v>66.76000000000001</v>
       </c>
       <c r="J1469" t="n">
-        <v>67.20999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K1469" t="n">
-        <v>99.33</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="1470">
@@ -66287,10 +66287,10 @@
         <v>11.35</v>
       </c>
       <c r="J1473" t="n">
-        <v>11.35</v>
+        <v>11.21</v>
       </c>
       <c r="K1473" t="n">
-        <v>100</v>
+        <v>101.27</v>
       </c>
     </row>
     <row r="1474">
@@ -66374,13 +66374,13 @@
         </is>
       </c>
       <c r="I1475" t="n">
-        <v>18.79</v>
+        <v>18.59</v>
       </c>
       <c r="J1475" t="n">
-        <v>18.79</v>
+        <v>18.44</v>
       </c>
       <c r="K1475" t="n">
-        <v>100</v>
+        <v>100.83</v>
       </c>
     </row>
     <row r="1476">
@@ -66419,13 +66419,13 @@
         </is>
       </c>
       <c r="I1476" t="n">
-        <v>351.06</v>
+        <v>366.94</v>
       </c>
       <c r="J1476" t="n">
-        <v>368.18</v>
+        <v>370.53</v>
       </c>
       <c r="K1476" t="n">
-        <v>95.34999999999999</v>
+        <v>99.03</v>
       </c>
     </row>
     <row r="1477">

--- a/ReportforHeaderU/ReportforHeaderU.xlsx
+++ b/ReportforHeaderU/ReportforHeaderU.xlsx
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>88.53</v>
+        <v>88.36</v>
       </c>
       <c r="J17" t="n">
-        <v>88.81999999999999</v>
+        <v>88.63</v>
       </c>
       <c r="K17" t="n">
-        <v>99.68000000000001</v>
+        <v>99.69</v>
       </c>
     </row>
     <row r="18">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>78.68000000000001</v>
+        <v>79.87</v>
       </c>
       <c r="J19" t="n">
-        <v>78.58</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>100.13</v>
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>106.52</v>
+        <v>108.44</v>
       </c>
       <c r="J22" t="n">
-        <v>106.4</v>
+        <v>110.22</v>
       </c>
       <c r="K22" t="n">
-        <v>100.11</v>
+        <v>98.38</v>
       </c>
     </row>
     <row r="23">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>91.02</v>
+        <v>91.22</v>
       </c>
       <c r="J23" t="n">
         <v>89.63</v>
       </c>
       <c r="K23" t="n">
-        <v>101.55</v>
+        <v>101.77</v>
       </c>
     </row>
     <row r="24">
@@ -6404,13 +6404,13 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>42.64</v>
+        <v>44.07</v>
       </c>
       <c r="J133" t="n">
         <v>44.76</v>
       </c>
       <c r="K133" t="n">
-        <v>95.27</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="134">
@@ -13727,13 +13727,13 @@
         </is>
       </c>
       <c r="I296" t="n">
-        <v>64.16</v>
+        <v>64.37</v>
       </c>
       <c r="J296" t="n">
         <v>59.74</v>
       </c>
       <c r="K296" t="n">
-        <v>107.4</v>
+        <v>107.76</v>
       </c>
     </row>
     <row r="297">
@@ -13772,13 +13772,13 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>29.53</v>
+        <v>29.57</v>
       </c>
       <c r="J297" t="n">
         <v>29.17</v>
       </c>
       <c r="K297" t="n">
-        <v>101.21</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="298">
@@ -14312,13 +14312,13 @@
         </is>
       </c>
       <c r="I309" t="n">
-        <v>26.79</v>
+        <v>27.07</v>
       </c>
       <c r="J309" t="n">
         <v>25.19</v>
       </c>
       <c r="K309" t="n">
-        <v>106.35</v>
+        <v>107.48</v>
       </c>
     </row>
     <row r="310">
@@ -16337,13 +16337,13 @@
         </is>
       </c>
       <c r="I354" t="n">
-        <v>79.26000000000001</v>
+        <v>75.94</v>
       </c>
       <c r="J354" t="n">
         <v>69.28</v>
       </c>
       <c r="K354" t="n">
-        <v>114.41</v>
+        <v>109.62</v>
       </c>
     </row>
     <row r="355">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="I355" t="n">
-        <v>187.98</v>
+        <v>190.6</v>
       </c>
       <c r="J355" t="n">
-        <v>189.94</v>
+        <v>190.83</v>
       </c>
       <c r="K355" t="n">
-        <v>98.97</v>
+        <v>99.88</v>
       </c>
     </row>
     <row r="356">
@@ -16562,13 +16562,13 @@
         </is>
       </c>
       <c r="I359" t="n">
-        <v>52.01</v>
+        <v>51.79</v>
       </c>
       <c r="J359" t="n">
         <v>51.16</v>
       </c>
       <c r="K359" t="n">
-        <v>101.66</v>
+        <v>101.23</v>
       </c>
     </row>
     <row r="360">
@@ -17236,12 +17236,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr"/>
+      <c r="I374" t="n">
+        <v>111.55</v>
+      </c>
       <c r="J374" t="n">
-        <v>115.71</v>
+        <v>115.77</v>
       </c>
       <c r="K374" t="n">
-        <v>0</v>
+        <v>96.34999999999999</v>
       </c>
     </row>
     <row r="375">
@@ -17279,12 +17281,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I375" t="inlineStr"/>
+      <c r="I375" t="n">
+        <v>34.04</v>
+      </c>
       <c r="J375" t="n">
         <v>34.51</v>
       </c>
       <c r="K375" t="n">
-        <v>0</v>
+        <v>98.64</v>
       </c>
     </row>
     <row r="376">
@@ -17367,12 +17371,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr"/>
+      <c r="I377" t="n">
+        <v>96.58</v>
+      </c>
       <c r="J377" t="n">
         <v>93.44</v>
       </c>
       <c r="K377" t="n">
-        <v>0</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="378">
@@ -18311,13 +18317,13 @@
         </is>
       </c>
       <c r="I398" t="n">
-        <v>56309.59</v>
+        <v>56063.17</v>
       </c>
       <c r="J398" t="n">
         <v>56063.17</v>
       </c>
       <c r="K398" t="n">
-        <v>100.44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="399">
@@ -18716,13 +18722,13 @@
         </is>
       </c>
       <c r="I407" t="n">
-        <v>25.57</v>
+        <v>16.08</v>
       </c>
       <c r="J407" t="n">
         <v>16.08</v>
       </c>
       <c r="K407" t="n">
-        <v>159.05</v>
+        <v>100</v>
       </c>
     </row>
     <row r="408">
@@ -19481,10 +19487,10 @@
         </is>
       </c>
       <c r="I424" t="n">
-        <v>977.09</v>
+        <v>1167.56</v>
       </c>
       <c r="J424" t="n">
-        <v>977.09</v>
+        <v>1167.56</v>
       </c>
       <c r="K424" t="n">
         <v>100</v>
@@ -19570,12 +19576,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I426" t="inlineStr"/>
+      <c r="I426" t="n">
+        <v>4823.27</v>
+      </c>
       <c r="J426" t="n">
         <v>4823.27</v>
       </c>
       <c r="K426" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="427">
@@ -19929,13 +19937,13 @@
         </is>
       </c>
       <c r="I434" t="n">
-        <v>6875.68</v>
+        <v>6941.21</v>
       </c>
       <c r="J434" t="n">
         <v>7137.47</v>
       </c>
       <c r="K434" t="n">
-        <v>96.33</v>
+        <v>97.25</v>
       </c>
     </row>
     <row r="435">
@@ -21774,13 +21782,13 @@
         </is>
       </c>
       <c r="I475" t="n">
-        <v>96.45999999999999</v>
+        <v>102.48</v>
       </c>
       <c r="J475" t="n">
-        <v>96.87</v>
+        <v>102.93</v>
       </c>
       <c r="K475" t="n">
-        <v>99.58</v>
+        <v>99.56</v>
       </c>
     </row>
     <row r="476">
@@ -21819,13 +21827,13 @@
         </is>
       </c>
       <c r="I476" t="n">
-        <v>102.67</v>
+        <v>99.69</v>
       </c>
       <c r="J476" t="n">
-        <v>103.51</v>
+        <v>100.44</v>
       </c>
       <c r="K476" t="n">
-        <v>99.19</v>
+        <v>99.25</v>
       </c>
     </row>
     <row r="477">
@@ -22043,9 +22051,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I481" t="inlineStr"/>
-      <c r="J481" t="inlineStr"/>
-      <c r="K481" t="inlineStr"/>
+      <c r="I481" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="J481" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="K481" t="n">
+        <v>100.92</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -23703,13 +23717,13 @@
         </is>
       </c>
       <c r="I518" t="n">
-        <v>72.79000000000001</v>
+        <v>72.62</v>
       </c>
       <c r="J518" t="n">
         <v>72.45</v>
       </c>
       <c r="K518" t="n">
-        <v>100.46</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="519">
@@ -23972,9 +23986,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I524" t="inlineStr"/>
-      <c r="J524" t="inlineStr"/>
-      <c r="K524" t="inlineStr"/>
+      <c r="I524" t="n">
+        <v>103.38</v>
+      </c>
+      <c r="J524" t="n">
+        <v>104.83</v>
+      </c>
+      <c r="K524" t="n">
+        <v>98.62</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -24146,9 +24166,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I528" t="inlineStr"/>
-      <c r="J528" t="inlineStr"/>
-      <c r="K528" t="inlineStr"/>
+      <c r="I528" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="J528" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="K528" t="n">
+        <v>96.43000000000001</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -24230,9 +24256,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I530" t="inlineStr"/>
-      <c r="J530" t="inlineStr"/>
-      <c r="K530" t="inlineStr"/>
+      <c r="I530" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="J530" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="K530" t="n">
+        <v>93.63</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -24359,9 +24391,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I533" t="inlineStr"/>
-      <c r="J533" t="inlineStr"/>
-      <c r="K533" t="inlineStr"/>
+      <c r="I533" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="J533" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="K533" t="n">
+        <v>93.09999999999999</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -24402,10 +24440,10 @@
         <v>4.24</v>
       </c>
       <c r="J534" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="K534" t="n">
-        <v>148.93</v>
+        <v>142.55</v>
       </c>
     </row>
     <row r="535">
@@ -26676,13 +26714,13 @@
         </is>
       </c>
       <c r="I585" t="n">
-        <v>48.93</v>
+        <v>48.85</v>
       </c>
       <c r="J585" t="n">
         <v>47.9</v>
       </c>
       <c r="K585" t="n">
-        <v>102.15</v>
+        <v>101.98</v>
       </c>
     </row>
     <row r="586">
@@ -28881,13 +28919,13 @@
         </is>
       </c>
       <c r="I634" t="n">
-        <v>18.96</v>
+        <v>18.91</v>
       </c>
       <c r="J634" t="n">
         <v>18.96</v>
       </c>
       <c r="K634" t="n">
-        <v>99.98</v>
+        <v>99.70999999999999</v>
       </c>
     </row>
     <row r="635">
@@ -34686,13 +34724,13 @@
         </is>
       </c>
       <c r="I763" t="n">
-        <v>23.84</v>
+        <v>23.62</v>
       </c>
       <c r="J763" t="n">
         <v>22.9</v>
       </c>
       <c r="K763" t="n">
-        <v>104.11</v>
+        <v>103.15</v>
       </c>
     </row>
     <row r="764">
@@ -36396,13 +36434,13 @@
         </is>
       </c>
       <c r="I801" t="n">
-        <v>97.19</v>
+        <v>96.63</v>
       </c>
       <c r="J801" t="n">
-        <v>92.2</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="K801" t="n">
-        <v>105.41</v>
+        <v>105.12</v>
       </c>
     </row>
     <row r="802">
@@ -36529,13 +36567,13 @@
         </is>
       </c>
       <c r="I804" t="n">
-        <v>72.26000000000001</v>
+        <v>73.83</v>
       </c>
       <c r="J804" t="n">
         <v>69.87</v>
       </c>
       <c r="K804" t="n">
-        <v>103.42</v>
+        <v>105.66</v>
       </c>
     </row>
     <row r="805">
@@ -36574,13 +36612,13 @@
         </is>
       </c>
       <c r="I805" t="n">
-        <v>187.45</v>
+        <v>187.56</v>
       </c>
       <c r="J805" t="n">
         <v>203.61</v>
       </c>
       <c r="K805" t="n">
-        <v>92.06</v>
+        <v>92.11</v>
       </c>
     </row>
     <row r="806">
@@ -37024,13 +37062,13 @@
         </is>
       </c>
       <c r="I815" t="n">
-        <v>65.47</v>
+        <v>64.66</v>
       </c>
       <c r="J815" t="n">
         <v>65.98999999999999</v>
       </c>
       <c r="K815" t="n">
-        <v>99.22</v>
+        <v>98</v>
       </c>
     </row>
     <row r="816">
@@ -37158,12 +37196,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I818" t="inlineStr"/>
+      <c r="I818" t="n">
+        <v>114.74</v>
+      </c>
       <c r="J818" t="n">
-        <v>117.11</v>
+        <v>117.63</v>
       </c>
       <c r="K818" t="n">
-        <v>0</v>
+        <v>97.55</v>
       </c>
     </row>
     <row r="819">
@@ -37202,13 +37242,13 @@
         </is>
       </c>
       <c r="I819" t="n">
-        <v>29.02</v>
+        <v>30.04</v>
       </c>
       <c r="J819" t="n">
-        <v>29.12</v>
+        <v>30.38</v>
       </c>
       <c r="K819" t="n">
-        <v>99.65000000000001</v>
+        <v>98.87</v>
       </c>
     </row>
     <row r="820">
@@ -37336,12 +37376,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I822" t="inlineStr"/>
+      <c r="I822" t="n">
+        <v>90.17</v>
+      </c>
       <c r="J822" t="n">
         <v>94.76000000000001</v>
       </c>
       <c r="K822" t="n">
-        <v>0</v>
+        <v>95.15000000000001</v>
       </c>
     </row>
     <row r="823">
@@ -38144,12 +38186,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I840" t="inlineStr"/>
+      <c r="I840" t="n">
+        <v>53161.67</v>
+      </c>
       <c r="J840" t="n">
         <v>53161.67</v>
       </c>
       <c r="K840" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="841">
@@ -39537,12 +39581,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I871" t="inlineStr"/>
+      <c r="I871" t="n">
+        <v>6020.07</v>
+      </c>
       <c r="J871" t="n">
         <v>6242.8</v>
       </c>
       <c r="K871" t="n">
-        <v>0</v>
+        <v>96.43000000000001</v>
       </c>
     </row>
     <row r="872">
@@ -41291,13 +41337,13 @@
         </is>
       </c>
       <c r="I910" t="n">
-        <v>78.08</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="J910" t="n">
-        <v>77.98</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="K910" t="n">
-        <v>100.14</v>
+        <v>100.07</v>
       </c>
     </row>
     <row r="911">
@@ -41515,9 +41561,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I915" t="inlineStr"/>
-      <c r="J915" t="inlineStr"/>
-      <c r="K915" t="inlineStr"/>
+      <c r="I915" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="J915" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="K915" t="n">
+        <v>99.75</v>
+      </c>
     </row>
     <row r="916">
       <c r="A916" t="n">
@@ -43309,9 +43361,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I955" t="inlineStr"/>
-      <c r="J955" t="inlineStr"/>
-      <c r="K955" t="inlineStr"/>
+      <c r="I955" t="n">
+        <v>104.27</v>
+      </c>
+      <c r="J955" t="n">
+        <v>103.37</v>
+      </c>
+      <c r="K955" t="n">
+        <v>100.87</v>
+      </c>
     </row>
     <row r="956">
       <c r="A956" t="n">
@@ -43397,10 +43455,10 @@
         <v>89.05</v>
       </c>
       <c r="J957" t="n">
-        <v>65.54000000000001</v>
+        <v>68.11</v>
       </c>
       <c r="K957" t="n">
-        <v>135.88</v>
+        <v>130.75</v>
       </c>
     </row>
     <row r="958">
@@ -43754,13 +43812,13 @@
         </is>
       </c>
       <c r="I965" t="n">
-        <v>4.85</v>
+        <v>4.91</v>
       </c>
       <c r="J965" t="n">
         <v>3.57</v>
       </c>
       <c r="K965" t="n">
-        <v>135.98</v>
+        <v>137.77</v>
       </c>
     </row>
     <row r="966">
@@ -48383,13 +48441,13 @@
         </is>
       </c>
       <c r="I1068" t="n">
-        <v>17.89</v>
+        <v>17.84</v>
       </c>
       <c r="J1068" t="n">
         <v>17.99</v>
       </c>
       <c r="K1068" t="n">
-        <v>99.45</v>
+        <v>99.19</v>
       </c>
     </row>
     <row r="1069">
@@ -49687,12 +49745,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1097" t="inlineStr"/>
+      <c r="I1097" t="n">
+        <v>1462.16</v>
+      </c>
       <c r="J1097" t="n">
-        <v>1381.9</v>
+        <v>1462.16</v>
       </c>
       <c r="K1097" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1098">
@@ -49865,12 +49925,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1101" t="inlineStr"/>
+      <c r="I1101" t="n">
+        <v>521.3099999999999</v>
+      </c>
       <c r="J1101" t="n">
         <v>521.3099999999999</v>
       </c>
       <c r="K1101" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1102">
@@ -49908,12 +49970,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1102" t="inlineStr"/>
+      <c r="I1102" t="n">
+        <v>137.95</v>
+      </c>
       <c r="J1102" t="n">
         <v>137.95</v>
       </c>
       <c r="K1102" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1103">
@@ -50135,10 +50199,10 @@
         <v>291.71</v>
       </c>
       <c r="J1107" t="n">
-        <v>285.11</v>
+        <v>291.71</v>
       </c>
       <c r="K1107" t="n">
-        <v>102.32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1108">
@@ -50177,10 +50241,10 @@
         </is>
       </c>
       <c r="I1108" t="n">
-        <v>122.8</v>
+        <v>125.05</v>
       </c>
       <c r="J1108" t="n">
-        <v>122.8</v>
+        <v>125.05</v>
       </c>
       <c r="K1108" t="n">
         <v>100</v>
@@ -50401,12 +50465,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1113" t="inlineStr"/>
+      <c r="I1113" t="n">
+        <v>159.84</v>
+      </c>
       <c r="J1113" t="n">
         <v>159.84</v>
       </c>
       <c r="K1113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1114">
@@ -50444,12 +50510,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1114" t="inlineStr"/>
+      <c r="I1114" t="n">
+        <v>222.27</v>
+      </c>
       <c r="J1114" t="n">
         <v>222.27</v>
       </c>
       <c r="K1114" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1115">
@@ -53996,13 +54064,13 @@
         </is>
       </c>
       <c r="I1193" t="n">
-        <v>25.32</v>
+        <v>25.17</v>
       </c>
       <c r="J1193" t="n">
         <v>24.05</v>
       </c>
       <c r="K1193" t="n">
-        <v>105.27</v>
+        <v>104.65</v>
       </c>
     </row>
     <row r="1194">
@@ -55615,12 +55683,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1229" t="inlineStr"/>
+      <c r="I1229" t="n">
+        <v>98.33</v>
+      </c>
       <c r="J1229" t="n">
-        <v>87.41</v>
+        <v>91.69</v>
       </c>
       <c r="K1229" t="n">
-        <v>0</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="1230">
@@ -55749,13 +55819,13 @@
         </is>
       </c>
       <c r="I1232" t="n">
-        <v>76.58</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="J1232" t="n">
-        <v>74.15000000000001</v>
+        <v>75.53</v>
       </c>
       <c r="K1232" t="n">
-        <v>103.28</v>
+        <v>102.85</v>
       </c>
     </row>
     <row r="1233">
@@ -56058,13 +56128,13 @@
         </is>
       </c>
       <c r="I1239" t="n">
-        <v>87.90000000000001</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="J1239" t="n">
         <v>86.11</v>
       </c>
       <c r="K1239" t="n">
-        <v>102.08</v>
+        <v>104.19</v>
       </c>
     </row>
     <row r="1240">
@@ -56373,13 +56443,13 @@
         </is>
       </c>
       <c r="I1246" t="n">
-        <v>81.16</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="J1246" t="n">
         <v>85.66</v>
       </c>
       <c r="K1246" t="n">
-        <v>94.75</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="1247">
@@ -56463,10 +56533,10 @@
         </is>
       </c>
       <c r="I1248" t="n">
-        <v>38.05</v>
+        <v>37.92</v>
       </c>
       <c r="J1248" t="n">
-        <v>38.03</v>
+        <v>37.91</v>
       </c>
       <c r="K1248" t="n">
         <v>100.03</v>
@@ -56507,12 +56577,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1249" t="inlineStr"/>
+      <c r="I1249" t="n">
+        <v>117.59</v>
+      </c>
       <c r="J1249" t="n">
-        <v>126.7</v>
+        <v>123.85</v>
       </c>
       <c r="K1249" t="n">
-        <v>0</v>
+        <v>94.94</v>
       </c>
     </row>
     <row r="1250">
@@ -56550,12 +56622,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1250" t="inlineStr"/>
+      <c r="I1250" t="n">
+        <v>31.72</v>
+      </c>
       <c r="J1250" t="n">
-        <v>31.91</v>
+        <v>32.14</v>
       </c>
       <c r="K1250" t="n">
-        <v>0</v>
+        <v>98.70999999999999</v>
       </c>
     </row>
     <row r="1251">
@@ -56638,12 +56712,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1252" t="inlineStr"/>
+      <c r="I1252" t="n">
+        <v>91.33</v>
+      </c>
       <c r="J1252" t="n">
-        <v>95.38</v>
+        <v>92.56</v>
       </c>
       <c r="K1252" t="n">
-        <v>0</v>
+        <v>98.67</v>
       </c>
     </row>
     <row r="1253">
@@ -57446,12 +57522,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1270" t="inlineStr"/>
+      <c r="I1270" t="n">
+        <v>55118.81</v>
+      </c>
       <c r="J1270" t="n">
         <v>55118.81</v>
       </c>
       <c r="K1270" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1271">
@@ -59592,12 +59670,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1318" t="inlineStr"/>
+      <c r="I1318" t="n">
+        <v>51.35</v>
+      </c>
       <c r="J1318" t="n">
-        <v>50.84</v>
+        <v>51.95</v>
       </c>
       <c r="K1318" t="n">
-        <v>0</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="1319">
@@ -59684,10 +59764,10 @@
         <v>97.19</v>
       </c>
       <c r="J1320" t="n">
-        <v>96.92</v>
+        <v>97.19</v>
       </c>
       <c r="K1320" t="n">
-        <v>100.27</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1321">
@@ -59725,12 +59805,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1321" t="inlineStr"/>
+      <c r="I1321" t="n">
+        <v>63.73</v>
+      </c>
       <c r="J1321" t="n">
         <v>63.73</v>
       </c>
       <c r="K1321" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1322">
@@ -59772,10 +59854,10 @@
         <v>41.02</v>
       </c>
       <c r="J1322" t="n">
-        <v>40.93</v>
+        <v>41.02</v>
       </c>
       <c r="K1322" t="n">
-        <v>100.22</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1323">
@@ -59817,10 +59899,10 @@
         <v>303.49</v>
       </c>
       <c r="J1323" t="n">
-        <v>303.5</v>
+        <v>303.49</v>
       </c>
       <c r="K1323" t="n">
-        <v>99.98999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1324">
@@ -59904,10 +59986,10 @@
         </is>
       </c>
       <c r="I1325" t="n">
-        <v>354.65</v>
+        <v>370.05</v>
       </c>
       <c r="J1325" t="n">
-        <v>354.96</v>
+        <v>370.4</v>
       </c>
       <c r="K1325" t="n">
         <v>99.91</v>
@@ -60534,13 +60616,13 @@
         </is>
       </c>
       <c r="I1339" t="n">
-        <v>63.32</v>
+        <v>62.69</v>
       </c>
       <c r="J1339" t="n">
-        <v>64.15000000000001</v>
+        <v>63.49</v>
       </c>
       <c r="K1339" t="n">
-        <v>98.7</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="1340">
@@ -60759,13 +60841,13 @@
         </is>
       </c>
       <c r="I1344" t="n">
-        <v>82.77</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="J1344" t="n">
-        <v>87.17</v>
+        <v>82.7</v>
       </c>
       <c r="K1344" t="n">
-        <v>94.94</v>
+        <v>96.95</v>
       </c>
     </row>
     <row r="1345">
@@ -61299,13 +61381,13 @@
         </is>
       </c>
       <c r="I1356" t="n">
-        <v>188.48</v>
+        <v>186</v>
       </c>
       <c r="J1356" t="n">
         <v>187.27</v>
       </c>
       <c r="K1356" t="n">
-        <v>100.64</v>
+        <v>99.31999999999999</v>
       </c>
     </row>
     <row r="1357">
@@ -61389,10 +61471,10 @@
         </is>
       </c>
       <c r="I1358" t="n">
-        <v>85.29000000000001</v>
+        <v>84.87</v>
       </c>
       <c r="J1358" t="n">
-        <v>85.29000000000001</v>
+        <v>84.87</v>
       </c>
       <c r="K1358" t="n">
         <v>100</v>
@@ -61434,11 +61516,13 @@
         </is>
       </c>
       <c r="I1359" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1359" t="inlineStr"/>
+        <v>49.74</v>
+      </c>
+      <c r="J1359" t="n">
+        <v>49.74</v>
+      </c>
       <c r="K1359" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1360">
@@ -61476,9 +61560,15 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1360" t="inlineStr"/>
-      <c r="J1360" t="inlineStr"/>
-      <c r="K1360" t="inlineStr"/>
+      <c r="I1360" t="n">
+        <v>324.29</v>
+      </c>
+      <c r="J1360" t="n">
+        <v>323.14</v>
+      </c>
+      <c r="K1360" t="n">
+        <v>100.36</v>
+      </c>
     </row>
     <row r="1361">
       <c r="A1361" t="n">
@@ -62371,13 +62461,13 @@
         </is>
       </c>
       <c r="I1380" t="n">
-        <v>71.91</v>
+        <v>71.36</v>
       </c>
       <c r="J1380" t="n">
         <v>71.06999999999999</v>
       </c>
       <c r="K1380" t="n">
-        <v>101.19</v>
+        <v>100.41</v>
       </c>
     </row>
     <row r="1381">
@@ -62685,9 +62775,15 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1387" t="inlineStr"/>
-      <c r="J1387" t="inlineStr"/>
-      <c r="K1387" t="inlineStr"/>
+      <c r="I1387" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="J1387" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="K1387" t="n">
+        <v>90.72</v>
+      </c>
     </row>
     <row r="1388">
       <c r="A1388" t="n">
@@ -62725,13 +62821,13 @@
         </is>
       </c>
       <c r="I1388" t="n">
-        <v>133.41</v>
+        <v>136.12</v>
       </c>
       <c r="J1388" t="n">
         <v>115.89</v>
       </c>
       <c r="K1388" t="n">
-        <v>115.12</v>
+        <v>117.46</v>
       </c>
     </row>
     <row r="1389">
@@ -62949,9 +63045,15 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1393" t="inlineStr"/>
-      <c r="J1393" t="inlineStr"/>
-      <c r="K1393" t="inlineStr"/>
+      <c r="I1393" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="J1393" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="K1393" t="n">
+        <v>102.17</v>
+      </c>
     </row>
     <row r="1394">
       <c r="A1394" t="n">
@@ -65314,10 +65416,10 @@
         <v>84.2</v>
       </c>
       <c r="J1446" t="n">
-        <v>80.25</v>
+        <v>80.06</v>
       </c>
       <c r="K1446" t="n">
-        <v>104.92</v>
+        <v>105.16</v>
       </c>
     </row>
     <row r="1447">
@@ -65584,10 +65686,10 @@
         <v>26.05</v>
       </c>
       <c r="J1452" t="n">
-        <v>25.9</v>
+        <v>25.88</v>
       </c>
       <c r="K1452" t="n">
-        <v>100.56</v>
+        <v>100.65</v>
       </c>
     </row>
     <row r="1453">
@@ -65625,12 +65727,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1453" t="inlineStr"/>
+      <c r="I1453" t="n">
+        <v>44.11</v>
+      </c>
       <c r="J1453" t="n">
-        <v>42.66</v>
+        <v>42.58</v>
       </c>
       <c r="K1453" t="n">
-        <v>0</v>
+        <v>103.61</v>
       </c>
     </row>
     <row r="1454">
@@ -65672,10 +65776,10 @@
         <v>42.03</v>
       </c>
       <c r="J1454" t="n">
-        <v>41.42</v>
+        <v>41.22</v>
       </c>
       <c r="K1454" t="n">
-        <v>101.46</v>
+        <v>101.97</v>
       </c>
     </row>
     <row r="1455">
@@ -65713,12 +65817,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1455" t="inlineStr"/>
+      <c r="I1455" t="n">
+        <v>22.4</v>
+      </c>
       <c r="J1455" t="n">
-        <v>21.99</v>
+        <v>21.85</v>
       </c>
       <c r="K1455" t="n">
-        <v>0</v>
+        <v>102.52</v>
       </c>
     </row>
     <row r="1456">
@@ -65756,12 +65862,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1456" t="inlineStr"/>
+      <c r="I1456" t="n">
+        <v>24.7</v>
+      </c>
       <c r="J1456" t="n">
-        <v>23.75</v>
+        <v>24.13</v>
       </c>
       <c r="K1456" t="n">
-        <v>0</v>
+        <v>102.36</v>
       </c>
     </row>
     <row r="1457">
@@ -65799,12 +65907,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1457" t="inlineStr"/>
+      <c r="I1457" t="n">
+        <v>52.83</v>
+      </c>
       <c r="J1457" t="n">
         <v>53.2</v>
       </c>
       <c r="K1457" t="n">
-        <v>0</v>
+        <v>99.31</v>
       </c>
     </row>
     <row r="1458">
@@ -65933,10 +66043,10 @@
         </is>
       </c>
       <c r="I1460" t="n">
-        <v>11.95</v>
+        <v>13.72</v>
       </c>
       <c r="J1460" t="n">
-        <v>11.95</v>
+        <v>13.72</v>
       </c>
       <c r="K1460" t="n">
         <v>100</v>
@@ -66026,10 +66136,10 @@
         <v>32.96</v>
       </c>
       <c r="J1462" t="n">
-        <v>34.13</v>
+        <v>32.78</v>
       </c>
       <c r="K1462" t="n">
-        <v>96.56</v>
+        <v>100.55</v>
       </c>
     </row>
     <row r="1463">
@@ -68996,10 +69106,10 @@
         <v>1237.78</v>
       </c>
       <c r="J1528" t="n">
-        <v>1220.38</v>
+        <v>1237.78</v>
       </c>
       <c r="K1528" t="n">
-        <v>101.43</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1529">
@@ -69761,10 +69871,10 @@
         <v>274.56</v>
       </c>
       <c r="J1545" t="n">
-        <v>254.92</v>
+        <v>274.56</v>
       </c>
       <c r="K1545" t="n">
-        <v>107.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1546">
@@ -69983,13 +70093,13 @@
         </is>
       </c>
       <c r="I1550" t="n">
-        <v>137.27</v>
+        <v>138.63</v>
       </c>
       <c r="J1550" t="n">
-        <v>144.51</v>
+        <v>138.63</v>
       </c>
       <c r="K1550" t="n">
-        <v>94.98999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1551">
@@ -70028,13 +70138,13 @@
         </is>
       </c>
       <c r="I1551" t="n">
-        <v>280.99</v>
+        <v>275.63</v>
       </c>
       <c r="J1551" t="n">
         <v>275.63</v>
       </c>
       <c r="K1551" t="n">
-        <v>101.95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1552">
@@ -75022,12 +75132,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1662" t="inlineStr"/>
+      <c r="I1662" t="n">
+        <v>61</v>
+      </c>
       <c r="J1662" t="n">
-        <v>48.7</v>
+        <v>61.89</v>
       </c>
       <c r="K1662" t="n">
-        <v>0</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="1663">
@@ -75065,12 +75177,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1663" t="inlineStr"/>
+      <c r="I1663" t="n">
+        <v>93.03</v>
+      </c>
       <c r="J1663" t="n">
-        <v>64.48</v>
+        <v>89.42</v>
       </c>
       <c r="K1663" t="n">
-        <v>0</v>
+        <v>104.04</v>
       </c>
     </row>
     <row r="1664">
@@ -75289,13 +75403,13 @@
         </is>
       </c>
       <c r="I1668" t="n">
-        <v>184.03</v>
+        <v>186.29</v>
       </c>
       <c r="J1668" t="n">
         <v>202.47</v>
       </c>
       <c r="K1668" t="n">
-        <v>90.89</v>
+        <v>92.01000000000001</v>
       </c>
     </row>
     <row r="1669">
@@ -75964,13 +76078,13 @@
         </is>
       </c>
       <c r="I1683" t="n">
-        <v>118.3</v>
+        <v>116.81</v>
       </c>
       <c r="J1683" t="n">
         <v>125.75</v>
       </c>
       <c r="K1683" t="n">
-        <v>94.08</v>
+        <v>92.89</v>
       </c>
     </row>
     <row r="1684">
@@ -76009,13 +76123,13 @@
         </is>
       </c>
       <c r="I1684" t="n">
-        <v>28.86</v>
+        <v>30.05</v>
       </c>
       <c r="J1684" t="n">
-        <v>29.23</v>
+        <v>30.4</v>
       </c>
       <c r="K1684" t="n">
-        <v>98.73999999999999</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="1685">
@@ -76143,12 +76257,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1687" t="inlineStr"/>
+      <c r="I1687" t="n">
+        <v>73.63</v>
+      </c>
       <c r="J1687" t="n">
         <v>73.38</v>
       </c>
       <c r="K1687" t="n">
-        <v>0</v>
+        <v>100.35</v>
       </c>
     </row>
     <row r="1688">
@@ -77131,12 +77247,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1709" t="inlineStr"/>
+      <c r="I1709" t="n">
+        <v>49488.25</v>
+      </c>
       <c r="J1709" t="n">
         <v>49488.25</v>
       </c>
       <c r="K1709" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1710">
@@ -78615,13 +78733,13 @@
         </is>
       </c>
       <c r="I1742" t="n">
-        <v>6986.67</v>
+        <v>6554.47</v>
       </c>
       <c r="J1742" t="n">
         <v>6580.11</v>
       </c>
       <c r="K1742" t="n">
-        <v>106.18</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="1743">

--- a/ReportforHeaderU/ReportforHeaderU.xlsx
+++ b/ReportforHeaderU/ReportforHeaderU.xlsx
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="I355" t="n">
-        <v>190.6</v>
+        <v>189.57</v>
       </c>
       <c r="J355" t="n">
         <v>190.83</v>
       </c>
       <c r="K355" t="n">
-        <v>99.88</v>
+        <v>99.34</v>
       </c>
     </row>
     <row r="356">
@@ -19757,13 +19757,13 @@
         </is>
       </c>
       <c r="I430" t="n">
-        <v>189.29</v>
+        <v>188.96</v>
       </c>
       <c r="J430" t="n">
         <v>188.93</v>
       </c>
       <c r="K430" t="n">
-        <v>100.19</v>
+        <v>100.02</v>
       </c>
     </row>
     <row r="431">
@@ -36478,12 +36478,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I802" t="inlineStr"/>
+      <c r="I802" t="n">
+        <v>88.77</v>
+      </c>
       <c r="J802" t="n">
-        <v>86.19</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="K802" t="n">
-        <v>0</v>
+        <v>99.34999999999999</v>
       </c>
     </row>
     <row r="803">
@@ -45876,13 +45878,13 @@
         </is>
       </c>
       <c r="I1011" t="n">
-        <v>60.73</v>
+        <v>60.89</v>
       </c>
       <c r="J1011" t="n">
         <v>61.3</v>
       </c>
       <c r="K1011" t="n">
-        <v>99.06999999999999</v>
+        <v>99.34</v>
       </c>
     </row>
     <row r="1012">
@@ -46146,13 +46148,13 @@
         </is>
       </c>
       <c r="I1017" t="n">
-        <v>85.2</v>
+        <v>85.13</v>
       </c>
       <c r="J1017" t="n">
         <v>82.47</v>
       </c>
       <c r="K1017" t="n">
-        <v>103.31</v>
+        <v>103.23</v>
       </c>
     </row>
     <row r="1018">
@@ -47631,13 +47633,13 @@
         </is>
       </c>
       <c r="I1050" t="n">
-        <v>28.27</v>
+        <v>28.24</v>
       </c>
       <c r="J1050" t="n">
         <v>28.27</v>
       </c>
       <c r="K1050" t="n">
-        <v>99.97</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="1051">
@@ -53525,12 +53527,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1181" t="inlineStr"/>
+      <c r="I1181" t="n">
+        <v>64.95</v>
+      </c>
       <c r="J1181" t="n">
         <v>63.86</v>
       </c>
       <c r="K1181" t="n">
-        <v>0</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="1182">
@@ -60031,13 +60035,13 @@
         </is>
       </c>
       <c r="I1326" t="n">
-        <v>28.51</v>
+        <v>28.47</v>
       </c>
       <c r="J1326" t="n">
         <v>28.45</v>
       </c>
       <c r="K1326" t="n">
-        <v>100.21</v>
+        <v>100.08</v>
       </c>
     </row>
     <row r="1327">
@@ -65413,13 +65417,13 @@
         </is>
       </c>
       <c r="I1446" t="n">
-        <v>84.2</v>
+        <v>84.13</v>
       </c>
       <c r="J1446" t="n">
         <v>80.06</v>
       </c>
       <c r="K1446" t="n">
-        <v>105.16</v>
+        <v>105.08</v>
       </c>
     </row>
     <row r="1447">
@@ -75403,13 +75407,13 @@
         </is>
       </c>
       <c r="I1668" t="n">
-        <v>186.29</v>
+        <v>187.1</v>
       </c>
       <c r="J1668" t="n">
         <v>202.47</v>
       </c>
       <c r="K1668" t="n">
-        <v>92.01000000000001</v>
+        <v>92.41</v>
       </c>
     </row>
     <row r="1669">
@@ -78553,13 +78557,13 @@
         </is>
       </c>
       <c r="I1738" t="n">
-        <v>161.92</v>
+        <v>161.43</v>
       </c>
       <c r="J1738" t="n">
         <v>162.26</v>
       </c>
       <c r="K1738" t="n">
-        <v>99.79000000000001</v>
+        <v>99.48999999999999</v>
       </c>
     </row>
     <row r="1739">

--- a/ReportforHeaderU/ReportforHeaderU.xlsx
+++ b/ReportforHeaderU/ReportforHeaderU.xlsx
@@ -610,12 +610,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>26.5</v>
+      </c>
       <c r="J4" t="n">
-        <v>25.19</v>
+        <v>26.55</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="5">
@@ -789,10 +791,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>49.35</v>
+        <v>50.66</v>
       </c>
       <c r="J8" t="n">
-        <v>49.01</v>
+        <v>50.31</v>
       </c>
       <c r="K8" t="n">
         <v>100.69</v>
@@ -834,13 +836,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>38.38</v>
+        <v>39.85</v>
       </c>
       <c r="J9" t="n">
-        <v>38.44</v>
+        <v>39.91</v>
       </c>
       <c r="K9" t="n">
-        <v>99.84</v>
+        <v>99.84999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1509,13 +1511,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>136.9</v>
+        <v>137.79</v>
       </c>
       <c r="J24" t="n">
-        <v>136.62</v>
+        <v>137.53</v>
       </c>
       <c r="K24" t="n">
-        <v>100.21</v>
+        <v>100.19</v>
       </c>
     </row>
     <row r="25">
@@ -1554,13 +1556,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>69.06999999999999</v>
+        <v>69.31</v>
       </c>
       <c r="J25" t="n">
-        <v>69.22</v>
+        <v>69.44</v>
       </c>
       <c r="K25" t="n">
-        <v>99.79000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="26">
@@ -1599,13 +1601,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>71.61</v>
+        <v>71.69</v>
       </c>
       <c r="J26" t="n">
-        <v>71.81999999999999</v>
+        <v>71.88</v>
       </c>
       <c r="K26" t="n">
-        <v>99.70999999999999</v>
+        <v>99.73999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1644,13 +1646,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>118.3</v>
+        <v>118.89</v>
       </c>
       <c r="J27" t="n">
-        <v>118.68</v>
+        <v>119.25</v>
       </c>
       <c r="K27" t="n">
-        <v>99.68000000000001</v>
+        <v>99.69</v>
       </c>
     </row>
     <row r="28">
@@ -1688,9 +1690,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>168.29</v>
+      </c>
+      <c r="J28" t="n">
+        <v>166.34</v>
+      </c>
+      <c r="K28" t="n">
+        <v>101.17</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1817,9 +1825,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>305.22</v>
+      </c>
+      <c r="J31" t="n">
+        <v>304.08</v>
+      </c>
+      <c r="K31" t="n">
+        <v>100.37</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4207,9 +4221,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>107.52</v>
+      </c>
+      <c r="J85" t="n">
+        <v>111.04</v>
+      </c>
+      <c r="K85" t="n">
+        <v>96.83</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6915,13 +6935,13 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>22.72</v>
+        <v>22.73</v>
       </c>
       <c r="J146" t="n">
         <v>22.73</v>
       </c>
       <c r="K146" t="n">
-        <v>99.94</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="147">
@@ -8402,7 +8422,7 @@
         <v>31.92</v>
       </c>
       <c r="K179" t="n">
-        <v>100.34</v>
+        <v>100.32</v>
       </c>
     </row>
     <row r="180">
@@ -8441,10 +8461,10 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>20.51</v>
+        <v>20.45</v>
       </c>
       <c r="J180" t="n">
-        <v>20.54</v>
+        <v>20.47</v>
       </c>
       <c r="K180" t="n">
         <v>99.90000000000001</v>
@@ -9521,10 +9541,10 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>70.79000000000001</v>
+        <v>74.16</v>
       </c>
       <c r="J204" t="n">
-        <v>70.79000000000001</v>
+        <v>74.16</v>
       </c>
       <c r="K204" t="n">
         <v>100</v>
@@ -11490,10 +11510,10 @@
         <v>300.51</v>
       </c>
       <c r="J248" t="n">
-        <v>297.68</v>
+        <v>299.94</v>
       </c>
       <c r="K248" t="n">
-        <v>100.95</v>
+        <v>100.19</v>
       </c>
     </row>
     <row r="249">
@@ -13237,10 +13257,10 @@
         <v>6413.87</v>
       </c>
       <c r="J287" t="n">
-        <v>6407.63</v>
+        <v>6418.47</v>
       </c>
       <c r="K287" t="n">
-        <v>100.1</v>
+        <v>99.93000000000001</v>
       </c>
     </row>
     <row r="288">
@@ -13368,12 +13388,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
+      <c r="I290" t="n">
+        <v>844</v>
+      </c>
       <c r="J290" t="n">
         <v>842.72</v>
       </c>
       <c r="K290" t="n">
-        <v>0</v>
+        <v>100.15</v>
       </c>
     </row>
     <row r="291">
@@ -13718,12 +13740,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
+      <c r="I298" t="n">
+        <v>48.63</v>
+      </c>
       <c r="J298" t="n">
         <v>48.25</v>
       </c>
       <c r="K298" t="n">
-        <v>0</v>
+        <v>100.78</v>
       </c>
     </row>
     <row r="299">
@@ -13761,12 +13785,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
+      <c r="I299" t="n">
+        <v>24.51</v>
+      </c>
       <c r="J299" t="n">
-        <v>24.39</v>
+        <v>24.55</v>
       </c>
       <c r="K299" t="n">
-        <v>0</v>
+        <v>99.87</v>
       </c>
     </row>
     <row r="300">
@@ -13939,12 +13965,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
+      <c r="I303" t="n">
+        <v>13.75</v>
+      </c>
       <c r="J303" t="n">
         <v>13.56</v>
       </c>
       <c r="K303" t="n">
-        <v>0</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="304">
@@ -13982,12 +14010,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr"/>
+      <c r="I304" t="n">
+        <v>44.22</v>
+      </c>
       <c r="J304" t="n">
-        <v>46.04</v>
+        <v>45.6</v>
       </c>
       <c r="K304" t="n">
-        <v>0</v>
+        <v>96.98</v>
       </c>
     </row>
     <row r="305">
@@ -14026,13 +14056,13 @@
         </is>
       </c>
       <c r="I305" t="n">
-        <v>38.99</v>
+        <v>38.57</v>
       </c>
       <c r="J305" t="n">
-        <v>38.61</v>
+        <v>38.21</v>
       </c>
       <c r="K305" t="n">
-        <v>100.97</v>
+        <v>100.95</v>
       </c>
     </row>
     <row r="306">
@@ -14292,10 +14322,10 @@
         </is>
       </c>
       <c r="I311" t="n">
-        <v>28.04</v>
+        <v>28.3</v>
       </c>
       <c r="J311" t="n">
-        <v>28.04</v>
+        <v>28.3</v>
       </c>
       <c r="K311" t="n">
         <v>100</v>
@@ -16044,12 +16074,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I350" t="inlineStr"/>
+      <c r="I350" t="n">
+        <v>47.17</v>
+      </c>
       <c r="J350" t="n">
-        <v>47.46</v>
+        <v>47.39</v>
       </c>
       <c r="K350" t="n">
-        <v>0</v>
+        <v>99.55</v>
       </c>
     </row>
     <row r="351">
@@ -18154,12 +18186,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I398" t="inlineStr"/>
+      <c r="I398" t="n">
+        <v>55704.6</v>
+      </c>
       <c r="J398" t="n">
-        <v>56063.17</v>
+        <v>55490.33</v>
       </c>
       <c r="K398" t="n">
-        <v>0</v>
+        <v>100.39</v>
       </c>
     </row>
     <row r="399">
@@ -19030,12 +19064,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I418" t="inlineStr"/>
+      <c r="I418" t="n">
+        <v>2021.55</v>
+      </c>
       <c r="J418" t="n">
         <v>2021.55</v>
       </c>
       <c r="K418" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="419">
@@ -19118,12 +19154,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I420" t="inlineStr"/>
+      <c r="I420" t="n">
+        <v>59.5</v>
+      </c>
       <c r="J420" t="n">
         <v>59.5</v>
       </c>
       <c r="K420" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="421">
@@ -19206,12 +19244,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I422" t="inlineStr"/>
+      <c r="I422" t="n">
+        <v>33.43</v>
+      </c>
       <c r="J422" t="n">
         <v>32.25</v>
       </c>
       <c r="K422" t="n">
-        <v>0</v>
+        <v>103.65</v>
       </c>
     </row>
     <row r="423">
@@ -19425,12 +19465,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I427" t="inlineStr"/>
+      <c r="I427" t="n">
+        <v>134.16</v>
+      </c>
       <c r="J427" t="n">
         <v>134.16</v>
       </c>
       <c r="K427" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="428">
@@ -19513,12 +19555,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I429" t="inlineStr"/>
+      <c r="I429" t="n">
+        <v>89.36</v>
+      </c>
       <c r="J429" t="n">
         <v>89.36</v>
       </c>
       <c r="K429" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="430">
@@ -19557,13 +19601,13 @@
         </is>
       </c>
       <c r="I430" t="n">
-        <v>191.97</v>
+        <v>192.9</v>
       </c>
       <c r="J430" t="n">
-        <v>188.96</v>
+        <v>193.49</v>
       </c>
       <c r="K430" t="n">
-        <v>101.59</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="431">
@@ -19601,12 +19645,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I431" t="inlineStr"/>
+      <c r="I431" t="n">
+        <v>290.39</v>
+      </c>
       <c r="J431" t="n">
         <v>290.39</v>
       </c>
       <c r="K431" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="432">
@@ -19644,12 +19690,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I432" t="inlineStr"/>
+      <c r="I432" t="n">
+        <v>143.58</v>
+      </c>
       <c r="J432" t="n">
         <v>143.58</v>
       </c>
       <c r="K432" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="433">
@@ -19687,12 +19735,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I433" t="inlineStr"/>
+      <c r="I433" t="n">
+        <v>22.08</v>
+      </c>
       <c r="J433" t="n">
         <v>22.08</v>
       </c>
       <c r="K433" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="434">
@@ -20430,7 +20480,7 @@
       </c>
       <c r="I450" t="inlineStr"/>
       <c r="J450" t="n">
-        <v>12.51</v>
+        <v>12.09</v>
       </c>
       <c r="K450" t="n">
         <v>0</v>
@@ -20472,10 +20522,10 @@
         </is>
       </c>
       <c r="I451" t="n">
-        <v>9.31</v>
+        <v>10.15</v>
       </c>
       <c r="J451" t="n">
-        <v>9.31</v>
+        <v>10.15</v>
       </c>
       <c r="K451" t="n">
         <v>100</v>
@@ -20952,12 +21002,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I462" t="inlineStr"/>
+      <c r="I462" t="n">
+        <v>28.02</v>
+      </c>
       <c r="J462" t="n">
-        <v>27.34</v>
+        <v>28.02</v>
       </c>
       <c r="K462" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="463">
@@ -21131,13 +21183,13 @@
         </is>
       </c>
       <c r="I466" t="n">
-        <v>34.52</v>
+        <v>34.66</v>
       </c>
       <c r="J466" t="n">
-        <v>34.29</v>
+        <v>34.43</v>
       </c>
       <c r="K466" t="n">
-        <v>100.68</v>
+        <v>100.66</v>
       </c>
     </row>
     <row r="467">
@@ -25269,9 +25321,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I561" t="inlineStr"/>
-      <c r="J561" t="inlineStr"/>
-      <c r="K561" t="inlineStr"/>
+      <c r="I561" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="J561" t="n">
+        <v>49</v>
+      </c>
+      <c r="K561" t="n">
+        <v>104.56</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -25308,9 +25366,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I562" t="inlineStr"/>
-      <c r="J562" t="inlineStr"/>
-      <c r="K562" t="inlineStr"/>
+      <c r="I562" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="J562" t="n">
+        <v>44.32</v>
+      </c>
+      <c r="K562" t="n">
+        <v>99.61</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -25347,9 +25411,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I563" t="inlineStr"/>
-      <c r="J563" t="inlineStr"/>
-      <c r="K563" t="inlineStr"/>
+      <c r="I563" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="J563" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="K563" t="n">
+        <v>100.4</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -25386,9 +25456,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I564" t="inlineStr"/>
-      <c r="J564" t="inlineStr"/>
-      <c r="K564" t="inlineStr"/>
+      <c r="I564" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="J564" t="n">
+        <v>46.39</v>
+      </c>
+      <c r="K564" t="n">
+        <v>100.46</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -25425,9 +25501,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I565" t="inlineStr"/>
-      <c r="J565" t="inlineStr"/>
-      <c r="K565" t="inlineStr"/>
+      <c r="I565" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="J565" t="n">
+        <v>35</v>
+      </c>
+      <c r="K565" t="n">
+        <v>86.81</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -25464,9 +25546,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I566" t="inlineStr"/>
-      <c r="J566" t="inlineStr"/>
-      <c r="K566" t="inlineStr"/>
+      <c r="I566" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="J566" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K566" t="n">
+        <v>103.16</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -25503,9 +25591,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I567" t="inlineStr"/>
-      <c r="J567" t="inlineStr"/>
-      <c r="K567" t="inlineStr"/>
+      <c r="I567" t="n">
+        <v>143.2</v>
+      </c>
+      <c r="J567" t="n">
+        <v>140.28</v>
+      </c>
+      <c r="K567" t="n">
+        <v>102.08</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -25543,13 +25637,13 @@
         </is>
       </c>
       <c r="I568" t="n">
-        <v>95.63</v>
+        <v>96.25</v>
       </c>
       <c r="J568" t="n">
-        <v>91.34</v>
+        <v>93.8</v>
       </c>
       <c r="K568" t="n">
-        <v>104.69</v>
+        <v>102.61</v>
       </c>
     </row>
     <row r="569">
@@ -25588,11 +25682,13 @@
         </is>
       </c>
       <c r="I569" t="n">
-        <v>0</v>
-      </c>
-      <c r="J569" t="inlineStr"/>
+        <v>12.58</v>
+      </c>
+      <c r="J569" t="n">
+        <v>12.47</v>
+      </c>
       <c r="K569" t="n">
-        <v>0</v>
+        <v>100.82</v>
       </c>
     </row>
     <row r="570">
@@ -25630,9 +25726,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I570" t="inlineStr"/>
-      <c r="J570" t="inlineStr"/>
-      <c r="K570" t="inlineStr"/>
+      <c r="I570" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="J570" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="K570" t="n">
+        <v>97.11</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -25669,9 +25771,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I571" t="inlineStr"/>
-      <c r="J571" t="inlineStr"/>
-      <c r="K571" t="inlineStr"/>
+      <c r="I571" t="n">
+        <v>61.66</v>
+      </c>
+      <c r="J571" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="K571" t="n">
+        <v>101.16</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -25708,9 +25816,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I572" t="inlineStr"/>
-      <c r="J572" t="inlineStr"/>
-      <c r="K572" t="inlineStr"/>
+      <c r="I572" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="J572" t="n">
+        <v>46.95</v>
+      </c>
+      <c r="K572" t="n">
+        <v>99.45</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -25747,9 +25861,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I573" t="inlineStr"/>
-      <c r="J573" t="inlineStr"/>
-      <c r="K573" t="inlineStr"/>
+      <c r="I573" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="J573" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="K573" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -25786,9 +25906,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I574" t="inlineStr"/>
-      <c r="J574" t="inlineStr"/>
-      <c r="K574" t="inlineStr"/>
+      <c r="I574" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="J574" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="K574" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -25825,9 +25951,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I575" t="inlineStr"/>
-      <c r="J575" t="inlineStr"/>
-      <c r="K575" t="inlineStr"/>
+      <c r="I575" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="J575" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="K575" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -25864,9 +25996,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I576" t="inlineStr"/>
-      <c r="J576" t="inlineStr"/>
-      <c r="K576" t="inlineStr"/>
+      <c r="I576" t="n">
+        <v>65.06999999999999</v>
+      </c>
+      <c r="J576" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="K576" t="n">
+        <v>99.64</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -25903,9 +26041,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I577" t="inlineStr"/>
-      <c r="J577" t="inlineStr"/>
-      <c r="K577" t="inlineStr"/>
+      <c r="I577" t="n">
+        <v>73.34</v>
+      </c>
+      <c r="J577" t="n">
+        <v>74.33</v>
+      </c>
+      <c r="K577" t="n">
+        <v>98.67</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -25942,9 +26086,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I578" t="inlineStr"/>
-      <c r="J578" t="inlineStr"/>
-      <c r="K578" t="inlineStr"/>
+      <c r="I578" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="J578" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="K578" t="n">
+        <v>98.12</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -25981,9 +26131,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I579" t="inlineStr"/>
-      <c r="J579" t="inlineStr"/>
-      <c r="K579" t="inlineStr"/>
+      <c r="I579" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="J579" t="n">
+        <v>33.12</v>
+      </c>
+      <c r="K579" t="n">
+        <v>101.97</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -26066,13 +26222,13 @@
         </is>
       </c>
       <c r="I581" t="n">
-        <v>24.63</v>
+        <v>24.27</v>
       </c>
       <c r="J581" t="n">
         <v>23.45</v>
       </c>
       <c r="K581" t="n">
-        <v>105.02</v>
+        <v>103.49</v>
       </c>
     </row>
     <row r="582">
@@ -26110,9 +26266,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I582" t="inlineStr"/>
-      <c r="J582" t="inlineStr"/>
-      <c r="K582" t="inlineStr"/>
+      <c r="I582" t="n">
+        <v>77.53</v>
+      </c>
+      <c r="J582" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="K582" t="n">
+        <v>101.48</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -26192,9 +26354,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I584" t="inlineStr"/>
-      <c r="J584" t="inlineStr"/>
-      <c r="K584" t="inlineStr"/>
+      <c r="I584" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="J584" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="K584" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -28542,13 +28710,13 @@
         </is>
       </c>
       <c r="I637" t="n">
-        <v>20.23</v>
+        <v>20.25</v>
       </c>
       <c r="J637" t="n">
         <v>20.24</v>
       </c>
       <c r="K637" t="n">
-        <v>99.97</v>
+        <v>100.08</v>
       </c>
     </row>
     <row r="638">
@@ -29530,13 +29698,13 @@
         </is>
       </c>
       <c r="I659" t="n">
-        <v>78.87</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="J659" t="n">
-        <v>77.61</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="K659" t="n">
-        <v>101.62</v>
+        <v>100.56</v>
       </c>
     </row>
     <row r="660">
@@ -30340,10 +30508,10 @@
         </is>
       </c>
       <c r="I677" t="n">
-        <v>260.58</v>
+        <v>261.54</v>
       </c>
       <c r="J677" t="n">
-        <v>260.21</v>
+        <v>261.17</v>
       </c>
       <c r="K677" t="n">
         <v>100.14</v>
@@ -33241,13 +33409,13 @@
         </is>
       </c>
       <c r="I742" t="n">
-        <v>6454.95</v>
+        <v>6456.02</v>
       </c>
       <c r="J742" t="n">
-        <v>6442.17</v>
+        <v>6430.43</v>
       </c>
       <c r="K742" t="n">
-        <v>100.2</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="743">
@@ -33332,7 +33500,7 @@
       </c>
       <c r="I744" t="inlineStr"/>
       <c r="J744" t="n">
-        <v>531.52</v>
+        <v>527.2</v>
       </c>
       <c r="K744" t="n">
         <v>0</v>
@@ -33377,10 +33545,10 @@
         <v>813.64</v>
       </c>
       <c r="J745" t="n">
-        <v>789.98</v>
+        <v>817.39</v>
       </c>
       <c r="K745" t="n">
-        <v>102.99</v>
+        <v>99.54000000000001</v>
       </c>
     </row>
     <row r="746">
@@ -33557,10 +33725,10 @@
         <v>8132.47</v>
       </c>
       <c r="J749" t="n">
-        <v>7905.8</v>
+        <v>7875.66</v>
       </c>
       <c r="K749" t="n">
-        <v>102.87</v>
+        <v>103.26</v>
       </c>
     </row>
     <row r="750">
@@ -33598,12 +33766,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I750" t="inlineStr"/>
+      <c r="I750" t="n">
+        <v>857.9400000000001</v>
+      </c>
       <c r="J750" t="n">
-        <v>857.83</v>
+        <v>850.76</v>
       </c>
       <c r="K750" t="n">
-        <v>0</v>
+        <v>100.84</v>
       </c>
     </row>
     <row r="751">
@@ -33645,10 +33815,10 @@
         <v>69.68000000000001</v>
       </c>
       <c r="J751" t="n">
-        <v>71.67</v>
+        <v>72.05</v>
       </c>
       <c r="K751" t="n">
-        <v>97.22</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="752">
@@ -33780,10 +33950,10 @@
         <v>25.97</v>
       </c>
       <c r="J754" t="n">
-        <v>26.04</v>
+        <v>25.9</v>
       </c>
       <c r="K754" t="n">
-        <v>99.7</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="755">
@@ -33956,12 +34126,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I758" t="inlineStr"/>
+      <c r="I758" t="n">
+        <v>42.98</v>
+      </c>
       <c r="J758" t="n">
         <v>43.12</v>
       </c>
       <c r="K758" t="n">
-        <v>0</v>
+        <v>99.69</v>
       </c>
     </row>
     <row r="759">
@@ -34003,10 +34175,10 @@
         <v>44.33</v>
       </c>
       <c r="J759" t="n">
-        <v>44.78</v>
+        <v>44.68</v>
       </c>
       <c r="K759" t="n">
-        <v>99</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="760">
@@ -34089,12 +34261,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I761" t="inlineStr"/>
+      <c r="I761" t="n">
+        <v>23.1</v>
+      </c>
       <c r="J761" t="n">
         <v>23.35</v>
       </c>
       <c r="K761" t="n">
-        <v>0</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="762">
@@ -34269,10 +34443,10 @@
         <v>27.57</v>
       </c>
       <c r="J765" t="n">
-        <v>27.04</v>
+        <v>26.85</v>
       </c>
       <c r="K765" t="n">
-        <v>101.98</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="766">
@@ -35482,10 +35656,10 @@
         <v>1542.53</v>
       </c>
       <c r="J792" t="n">
-        <v>1521.88</v>
+        <v>1542.53</v>
       </c>
       <c r="K792" t="n">
-        <v>101.36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="793">
@@ -35930,10 +36104,10 @@
         <v>87.37</v>
       </c>
       <c r="J802" t="n">
-        <v>88.77</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="K802" t="n">
-        <v>98.42</v>
+        <v>99.02</v>
       </c>
     </row>
     <row r="803">
@@ -35972,10 +36146,10 @@
         </is>
       </c>
       <c r="I803" t="n">
-        <v>59.03</v>
+        <v>57.35</v>
       </c>
       <c r="J803" t="n">
-        <v>59.42</v>
+        <v>57.73</v>
       </c>
       <c r="K803" t="n">
         <v>99.34999999999999</v>
@@ -37228,13 +37402,13 @@
         </is>
       </c>
       <c r="I831" t="n">
-        <v>627.48</v>
+        <v>616.95</v>
       </c>
       <c r="J831" t="n">
         <v>610.37</v>
       </c>
       <c r="K831" t="n">
-        <v>102.8</v>
+        <v>101.08</v>
       </c>
     </row>
     <row r="832">
@@ -37407,12 +37581,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I835" t="inlineStr"/>
+      <c r="I835" t="n">
+        <v>11.73</v>
+      </c>
       <c r="J835" t="n">
         <v>11.2</v>
       </c>
       <c r="K835" t="n">
-        <v>0</v>
+        <v>104.66</v>
       </c>
     </row>
     <row r="836">
@@ -37631,13 +37807,13 @@
         </is>
       </c>
       <c r="I840" t="n">
-        <v>53161.67</v>
+        <v>54462.14</v>
       </c>
       <c r="J840" t="n">
-        <v>53161.67</v>
+        <v>54006.27</v>
       </c>
       <c r="K840" t="n">
-        <v>100</v>
+        <v>100.84</v>
       </c>
     </row>
     <row r="841">
@@ -38621,10 +38797,10 @@
         </is>
       </c>
       <c r="I862" t="n">
-        <v>973.3200000000001</v>
+        <v>904.1</v>
       </c>
       <c r="J862" t="n">
-        <v>973.3200000000001</v>
+        <v>904.1</v>
       </c>
       <c r="K862" t="n">
         <v>100</v>
@@ -38845,12 +39021,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I867" t="inlineStr"/>
+      <c r="I867" t="n">
+        <v>154.35</v>
+      </c>
       <c r="J867" t="n">
         <v>153.42</v>
       </c>
       <c r="K867" t="n">
-        <v>0</v>
+        <v>100.61</v>
       </c>
     </row>
     <row r="868">
@@ -40321,10 +40499,10 @@
         </is>
       </c>
       <c r="I900" t="n">
-        <v>34.05</v>
+        <v>34.36</v>
       </c>
       <c r="J900" t="n">
-        <v>34.05</v>
+        <v>34.36</v>
       </c>
       <c r="K900" t="n">
         <v>100</v>
@@ -40365,12 +40543,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I901" t="inlineStr"/>
+      <c r="I901" t="n">
+        <v>43.59</v>
+      </c>
       <c r="J901" t="n">
-        <v>41.97</v>
+        <v>43.07</v>
       </c>
       <c r="K901" t="n">
-        <v>0</v>
+        <v>101.22</v>
       </c>
     </row>
     <row r="902">
@@ -40723,9 +40903,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I909" t="inlineStr"/>
-      <c r="J909" t="inlineStr"/>
-      <c r="K909" t="inlineStr"/>
+      <c r="I909" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="J909" t="n">
+        <v>60.49</v>
+      </c>
+      <c r="K909" t="n">
+        <v>101.33</v>
+      </c>
     </row>
     <row r="910">
       <c r="A910" t="n">
@@ -43139,9 +43325,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I965" t="inlineStr"/>
-      <c r="J965" t="inlineStr"/>
-      <c r="K965" t="inlineStr"/>
+      <c r="I965" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="J965" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="K965" t="n">
+        <v>113.41</v>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="n">
@@ -44609,9 +44801,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I999" t="inlineStr"/>
-      <c r="J999" t="inlineStr"/>
-      <c r="K999" t="inlineStr"/>
+      <c r="I999" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="J999" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="K999" t="n">
+        <v>88.03</v>
+      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="n">
@@ -44648,9 +44846,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1000" t="inlineStr"/>
-      <c r="J1000" t="inlineStr"/>
-      <c r="K1000" t="inlineStr"/>
+      <c r="I1000" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="J1000" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="K1000" t="n">
+        <v>97.66</v>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" t="n">
@@ -44687,9 +44891,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1001" t="inlineStr"/>
-      <c r="J1001" t="inlineStr"/>
-      <c r="K1001" t="inlineStr"/>
+      <c r="I1001" t="n">
+        <v>137.92</v>
+      </c>
+      <c r="J1001" t="n">
+        <v>135.9</v>
+      </c>
+      <c r="K1001" t="n">
+        <v>101.49</v>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" t="n">
@@ -44726,9 +44936,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1002" t="inlineStr"/>
-      <c r="J1002" t="inlineStr"/>
-      <c r="K1002" t="inlineStr"/>
+      <c r="I1002" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="J1002" t="n">
+        <v>96.93000000000001</v>
+      </c>
+      <c r="K1002" t="n">
+        <v>100.23</v>
+      </c>
     </row>
     <row r="1003">
       <c r="A1003" t="n">
@@ -44765,9 +44981,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1003" t="inlineStr"/>
-      <c r="J1003" t="inlineStr"/>
-      <c r="K1003" t="inlineStr"/>
+      <c r="I1003" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="J1003" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="K1003" t="n">
+        <v>100.66</v>
+      </c>
     </row>
     <row r="1004">
       <c r="A1004" t="n">
@@ -44804,9 +45026,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1004" t="inlineStr"/>
-      <c r="J1004" t="inlineStr"/>
-      <c r="K1004" t="inlineStr"/>
+      <c r="I1004" t="n">
+        <v>35.59</v>
+      </c>
+      <c r="J1004" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="K1004" t="n">
+        <v>99.51000000000001</v>
+      </c>
     </row>
     <row r="1005">
       <c r="A1005" t="n">
@@ -44843,9 +45071,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1005" t="inlineStr"/>
-      <c r="J1005" t="inlineStr"/>
-      <c r="K1005" t="inlineStr"/>
+      <c r="I1005" t="n">
+        <v>60.44</v>
+      </c>
+      <c r="J1005" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="K1005" t="n">
+        <v>99.83</v>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="n">
@@ -44882,9 +45116,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1006" t="inlineStr"/>
-      <c r="J1006" t="inlineStr"/>
-      <c r="K1006" t="inlineStr"/>
+      <c r="I1006" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="J1006" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="K1006" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" t="n">
@@ -44921,9 +45161,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1007" t="inlineStr"/>
-      <c r="J1007" t="inlineStr"/>
-      <c r="K1007" t="inlineStr"/>
+      <c r="I1007" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="J1007" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="K1007" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" t="n">
@@ -44960,9 +45206,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1008" t="inlineStr"/>
-      <c r="J1008" t="inlineStr"/>
-      <c r="K1008" t="inlineStr"/>
+      <c r="I1008" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="J1008" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K1008" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" t="n">
@@ -44999,9 +45251,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1009" t="inlineStr"/>
-      <c r="J1009" t="inlineStr"/>
-      <c r="K1009" t="inlineStr"/>
+      <c r="I1009" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="J1009" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="K1009" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="1010">
       <c r="A1010" t="n">
@@ -46285,13 +46543,13 @@
         </is>
       </c>
       <c r="I1038" t="n">
-        <v>48.64</v>
+        <v>48.61</v>
       </c>
       <c r="J1038" t="n">
         <v>48.08</v>
       </c>
       <c r="K1038" t="n">
-        <v>101.17</v>
+        <v>101.1</v>
       </c>
     </row>
     <row r="1039">
@@ -47715,13 +47973,13 @@
         </is>
       </c>
       <c r="I1070" t="n">
-        <v>29.97</v>
+        <v>30.54</v>
       </c>
       <c r="J1070" t="n">
-        <v>29.84</v>
+        <v>30.4</v>
       </c>
       <c r="K1070" t="n">
-        <v>100.45</v>
+        <v>100.44</v>
       </c>
     </row>
     <row r="1071">
@@ -47763,10 +48021,10 @@
         <v>20.63</v>
       </c>
       <c r="J1071" t="n">
-        <v>20.71</v>
+        <v>20.7</v>
       </c>
       <c r="K1071" t="n">
-        <v>99.62</v>
+        <v>99.69</v>
       </c>
     </row>
     <row r="1072">
@@ -47808,10 +48066,10 @@
         <v>7.73</v>
       </c>
       <c r="J1072" t="n">
-        <v>7.79</v>
+        <v>7.73</v>
       </c>
       <c r="K1072" t="n">
-        <v>99.25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1073">
@@ -48792,12 +49050,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1094" t="inlineStr"/>
+      <c r="I1094" t="n">
+        <v>27.67</v>
+      </c>
       <c r="J1094" t="n">
-        <v>28.05</v>
+        <v>27.67</v>
       </c>
       <c r="K1094" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1095">
@@ -51660,12 +51920,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1158" t="inlineStr"/>
+      <c r="I1158" t="n">
+        <v>476.9</v>
+      </c>
       <c r="J1158" t="n">
         <v>476.9</v>
       </c>
       <c r="K1158" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1159">
@@ -51793,12 +52055,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1161" t="inlineStr"/>
+      <c r="I1161" t="n">
+        <v>364.45</v>
+      </c>
       <c r="J1161" t="n">
         <v>364.45</v>
       </c>
       <c r="K1161" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1162">
@@ -52958,13 +53222,13 @@
         </is>
       </c>
       <c r="I1187" t="n">
-        <v>41</v>
+        <v>41.16</v>
       </c>
       <c r="J1187" t="n">
-        <v>40.6</v>
+        <v>40.78</v>
       </c>
       <c r="K1187" t="n">
-        <v>100.97</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="1188">
@@ -53452,12 +53716,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1198" t="inlineStr"/>
+      <c r="I1198" t="n">
+        <v>58.12</v>
+      </c>
       <c r="J1198" t="n">
         <v>58.12</v>
       </c>
       <c r="K1198" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1199">
@@ -53589,10 +53855,10 @@
         <v>101.95</v>
       </c>
       <c r="J1201" t="n">
-        <v>105.56</v>
+        <v>101.95</v>
       </c>
       <c r="K1201" t="n">
-        <v>96.56999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1202">
@@ -53679,10 +53945,10 @@
         <v>26.75</v>
       </c>
       <c r="J1203" t="n">
-        <v>27.33</v>
+        <v>26.75</v>
       </c>
       <c r="K1203" t="n">
-        <v>97.88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1204">
@@ -54260,12 +54526,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1216" t="inlineStr"/>
+      <c r="I1216" t="n">
+        <v>428.03</v>
+      </c>
       <c r="J1216" t="n">
         <v>428.03</v>
       </c>
       <c r="K1216" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1217">
@@ -54484,13 +54752,13 @@
         </is>
       </c>
       <c r="I1221" t="n">
-        <v>1406.31</v>
+        <v>1433.96</v>
       </c>
       <c r="J1221" t="n">
         <v>1433.96</v>
       </c>
       <c r="K1221" t="n">
-        <v>98.06999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1222">
@@ -55361,12 +55629,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1241" t="inlineStr"/>
+      <c r="I1241" t="n">
+        <v>250.09</v>
+      </c>
       <c r="J1241" t="n">
         <v>250.09</v>
       </c>
       <c r="K1241" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1242">
@@ -55405,10 +55675,10 @@
         </is>
       </c>
       <c r="I1242" t="n">
-        <v>1310.39</v>
+        <v>1332.06</v>
       </c>
       <c r="J1242" t="n">
-        <v>1310.39</v>
+        <v>1332.06</v>
       </c>
       <c r="K1242" t="n">
         <v>100</v>
@@ -55494,12 +55764,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1244" t="inlineStr"/>
+      <c r="I1244" t="n">
+        <v>349.6</v>
+      </c>
       <c r="J1244" t="n">
         <v>349.6</v>
       </c>
       <c r="K1244" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1245">
@@ -56188,12 +56460,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1260" t="inlineStr"/>
+      <c r="I1260" t="n">
+        <v>475.59</v>
+      </c>
       <c r="J1260" t="n">
-        <v>473.46</v>
+        <v>475.59</v>
       </c>
       <c r="K1260" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1261">
@@ -56232,10 +56506,10 @@
         </is>
       </c>
       <c r="I1261" t="n">
-        <v>1122.45</v>
+        <v>1088.58</v>
       </c>
       <c r="J1261" t="n">
-        <v>1122.45</v>
+        <v>1088.58</v>
       </c>
       <c r="K1261" t="n">
         <v>100</v>
@@ -56457,13 +56731,13 @@
         </is>
       </c>
       <c r="I1266" t="n">
-        <v>551.1</v>
+        <v>547.01</v>
       </c>
       <c r="J1266" t="n">
-        <v>468.89</v>
+        <v>450.61</v>
       </c>
       <c r="K1266" t="n">
-        <v>117.53</v>
+        <v>121.39</v>
       </c>
     </row>
     <row r="1267">
@@ -56478,17 +56752,17 @@
       </c>
       <c r="D1267" t="inlineStr">
         <is>
-          <t>5120006</t>
+          <t>5120002</t>
         </is>
       </c>
       <c r="E1267" t="inlineStr">
         <is>
-          <t>ค่าโดยสารรถไฟ</t>
+          <t>ค่าโดยสารรถประจำทางปรับอากาศชั้น 1</t>
         </is>
       </c>
       <c r="F1267" t="inlineStr">
         <is>
-          <t>เดือน_นอกเขต</t>
+          <t>เดือน_นอกเขตไม่คำนวณ</t>
         </is>
       </c>
       <c r="G1267" t="inlineStr">
@@ -56501,15 +56775,9 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1267" t="n">
-        <v>199</v>
-      </c>
-      <c r="J1267" t="n">
-        <v>199</v>
-      </c>
-      <c r="K1267" t="n">
-        <v>100</v>
-      </c>
+      <c r="I1267" t="inlineStr"/>
+      <c r="J1267" t="inlineStr"/>
+      <c r="K1267" t="inlineStr"/>
     </row>
     <row r="1268">
       <c r="A1268" t="n">
@@ -56523,12 +56791,12 @@
       </c>
       <c r="D1268" t="inlineStr">
         <is>
-          <t>5211002</t>
+          <t>5120006</t>
         </is>
       </c>
       <c r="E1268" t="inlineStr">
         <is>
-          <t>รถยนต์</t>
+          <t>ค่าโดยสารรถไฟ</t>
         </is>
       </c>
       <c r="F1268" t="inlineStr">
@@ -56538,7 +56806,7 @@
       </c>
       <c r="G1268" t="inlineStr">
         <is>
-          <t>ต้า</t>
+          <t>ตุ๊กตา</t>
         </is>
       </c>
       <c r="H1268" t="inlineStr">
@@ -56547,13 +56815,13 @@
         </is>
       </c>
       <c r="I1268" t="n">
-        <v>101.63</v>
+        <v>199</v>
       </c>
       <c r="J1268" t="n">
-        <v>101.56</v>
+        <v>199</v>
       </c>
       <c r="K1268" t="n">
-        <v>100.07</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1269">
@@ -56568,12 +56836,12 @@
       </c>
       <c r="D1269" t="inlineStr">
         <is>
-          <t>5211003</t>
+          <t>5211002</t>
         </is>
       </c>
       <c r="E1269" t="inlineStr">
         <is>
-          <t>รถจักรยานยนต์</t>
+          <t>รถยนต์</t>
         </is>
       </c>
       <c r="F1269" t="inlineStr">
@@ -56583,7 +56851,7 @@
       </c>
       <c r="G1269" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ต้า</t>
         </is>
       </c>
       <c r="H1269" t="inlineStr">
@@ -56591,12 +56859,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1269" t="inlineStr"/>
+      <c r="I1269" t="n">
+        <v>101.63</v>
+      </c>
       <c r="J1269" t="n">
-        <v>55118.81</v>
+        <v>101.56</v>
       </c>
       <c r="K1269" t="n">
-        <v>0</v>
+        <v>100.07</v>
       </c>
     </row>
     <row r="1270">
@@ -56611,12 +56881,12 @@
       </c>
       <c r="D1270" t="inlineStr">
         <is>
-          <t>5211004</t>
+          <t>5211003</t>
         </is>
       </c>
       <c r="E1270" t="inlineStr">
         <is>
-          <t>รถจักรยานสองล้อ</t>
+          <t>รถจักรยานยนต์</t>
         </is>
       </c>
       <c r="F1270" t="inlineStr">
@@ -56626,7 +56896,7 @@
       </c>
       <c r="G1270" t="inlineStr">
         <is>
-          <t>ต้า</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H1270" t="inlineStr">
@@ -56635,13 +56905,13 @@
         </is>
       </c>
       <c r="I1270" t="n">
-        <v>2576.31</v>
+        <v>56038.56</v>
       </c>
       <c r="J1270" t="n">
-        <v>2576.31</v>
+        <v>55681.15</v>
       </c>
       <c r="K1270" t="n">
-        <v>100</v>
+        <v>100.64</v>
       </c>
     </row>
     <row r="1271">
@@ -56656,12 +56926,12 @@
       </c>
       <c r="D1271" t="inlineStr">
         <is>
-          <t>5211005</t>
+          <t>5211004</t>
         </is>
       </c>
       <c r="E1271" t="inlineStr">
         <is>
-          <t>รถปิคอัพ</t>
+          <t>รถจักรยานสองล้อ</t>
         </is>
       </c>
       <c r="F1271" t="inlineStr">
@@ -56680,10 +56950,10 @@
         </is>
       </c>
       <c r="I1271" t="n">
-        <v>100</v>
+        <v>2576.31</v>
       </c>
       <c r="J1271" t="n">
-        <v>100</v>
+        <v>2576.31</v>
       </c>
       <c r="K1271" t="n">
         <v>100</v>
@@ -56701,12 +56971,12 @@
       </c>
       <c r="D1272" t="inlineStr">
         <is>
-          <t>5212001</t>
+          <t>5211005</t>
         </is>
       </c>
       <c r="E1272" t="inlineStr">
         <is>
-          <t>ยางรถยนต์</t>
+          <t>รถปิคอัพ</t>
         </is>
       </c>
       <c r="F1272" t="inlineStr">
@@ -56725,13 +56995,13 @@
         </is>
       </c>
       <c r="I1272" t="n">
-        <v>2211.59</v>
+        <v>100</v>
       </c>
       <c r="J1272" t="n">
-        <v>2180.63</v>
+        <v>100</v>
       </c>
       <c r="K1272" t="n">
-        <v>101.42</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1273">
@@ -56746,12 +57016,12 @@
       </c>
       <c r="D1273" t="inlineStr">
         <is>
-          <t>5212002</t>
+          <t>5212001</t>
         </is>
       </c>
       <c r="E1273" t="inlineStr">
         <is>
-          <t>ยางนอกรถจักรยานยนต์</t>
+          <t>ยางรถยนต์</t>
         </is>
       </c>
       <c r="F1273" t="inlineStr">
@@ -56770,13 +57040,13 @@
         </is>
       </c>
       <c r="I1273" t="n">
-        <v>283.5</v>
+        <v>2211.59</v>
       </c>
       <c r="J1273" t="n">
-        <v>279.47</v>
+        <v>2180.63</v>
       </c>
       <c r="K1273" t="n">
-        <v>101.44</v>
+        <v>101.42</v>
       </c>
     </row>
     <row r="1274">
@@ -56791,12 +57061,12 @@
       </c>
       <c r="D1274" t="inlineStr">
         <is>
-          <t>5212004</t>
+          <t>5212002</t>
         </is>
       </c>
       <c r="E1274" t="inlineStr">
         <is>
-          <t>แบตเตอรี่รถยนต์</t>
+          <t>ยางนอกรถจักรยานยนต์</t>
         </is>
       </c>
       <c r="F1274" t="inlineStr">
@@ -56815,13 +57085,13 @@
         </is>
       </c>
       <c r="I1274" t="n">
-        <v>2410.45</v>
+        <v>283.5</v>
       </c>
       <c r="J1274" t="n">
-        <v>2410.45</v>
+        <v>279.47</v>
       </c>
       <c r="K1274" t="n">
-        <v>100</v>
+        <v>101.44</v>
       </c>
     </row>
     <row r="1275">
@@ -56836,12 +57106,12 @@
       </c>
       <c r="D1275" t="inlineStr">
         <is>
-          <t>5212005</t>
+          <t>5212004</t>
         </is>
       </c>
       <c r="E1275" t="inlineStr">
         <is>
-          <t>ยางในรถจักรยาน</t>
+          <t>แบตเตอรี่รถยนต์</t>
         </is>
       </c>
       <c r="F1275" t="inlineStr">
@@ -56860,13 +57130,13 @@
         </is>
       </c>
       <c r="I1275" t="n">
-        <v>100.28</v>
+        <v>2410.45</v>
       </c>
       <c r="J1275" t="n">
-        <v>97.14</v>
+        <v>2410.45</v>
       </c>
       <c r="K1275" t="n">
-        <v>103.24</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1276">
@@ -56881,12 +57151,12 @@
       </c>
       <c r="D1276" t="inlineStr">
         <is>
-          <t>5220005</t>
+          <t>5212005</t>
         </is>
       </c>
       <c r="E1276" t="inlineStr">
         <is>
-          <t>น้ำมันหล่อลื่น</t>
+          <t>ยางในรถจักรยาน</t>
         </is>
       </c>
       <c r="F1276" t="inlineStr">
@@ -56896,7 +57166,7 @@
       </c>
       <c r="G1276" t="inlineStr">
         <is>
-          <t>วิรัตน์</t>
+          <t>ต้า</t>
         </is>
       </c>
       <c r="H1276" t="inlineStr">
@@ -56905,13 +57175,13 @@
         </is>
       </c>
       <c r="I1276" t="n">
-        <v>532.89</v>
+        <v>100.28</v>
       </c>
       <c r="J1276" t="n">
-        <v>510.51</v>
+        <v>97.14</v>
       </c>
       <c r="K1276" t="n">
-        <v>104.38</v>
+        <v>103.24</v>
       </c>
     </row>
     <row r="1277">
@@ -56926,17 +57196,17 @@
       </c>
       <c r="D1277" t="inlineStr">
         <is>
-          <t>5220008</t>
+          <t>5220005</t>
         </is>
       </c>
       <c r="E1277" t="inlineStr">
         <is>
-          <t>ก๊าซธรรมชาติ (NGV)</t>
+          <t>น้ำมันหล่อลื่น</t>
         </is>
       </c>
       <c r="F1277" t="inlineStr">
         <is>
-          <t>เดือน_นอกเขตไม่คำนวณ</t>
+          <t>เดือน_นอกเขต</t>
         </is>
       </c>
       <c r="G1277" t="inlineStr">
@@ -56950,13 +57220,13 @@
         </is>
       </c>
       <c r="I1277" t="n">
-        <v>18.35</v>
+        <v>532.89</v>
       </c>
       <c r="J1277" t="n">
-        <v>18.35</v>
+        <v>510.51</v>
       </c>
       <c r="K1277" t="n">
-        <v>100</v>
+        <v>104.38</v>
       </c>
     </row>
     <row r="1278">
@@ -56971,17 +57241,17 @@
       </c>
       <c r="D1278" t="inlineStr">
         <is>
-          <t>5220009</t>
+          <t>5220008</t>
         </is>
       </c>
       <c r="E1278" t="inlineStr">
         <is>
-          <t>ก๊าชยานพาหนะ (LPG)</t>
+          <t>ก๊าซธรรมชาติ (NGV)</t>
         </is>
       </c>
       <c r="F1278" t="inlineStr">
         <is>
-          <t>สัปดาห์_นอกเขต</t>
+          <t>เดือน_นอกเขตไม่คำนวณ</t>
         </is>
       </c>
       <c r="G1278" t="inlineStr">
@@ -56995,13 +57265,13 @@
         </is>
       </c>
       <c r="I1278" t="n">
-        <v>18.16</v>
+        <v>18.35</v>
       </c>
       <c r="J1278" t="n">
-        <v>18.06</v>
+        <v>18.35</v>
       </c>
       <c r="K1278" t="n">
-        <v>100.58</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1279">
@@ -57016,22 +57286,22 @@
       </c>
       <c r="D1279" t="inlineStr">
         <is>
-          <t>5230001</t>
+          <t>5220009</t>
         </is>
       </c>
       <c r="E1279" t="inlineStr">
         <is>
-          <t>ค่าบริการล้างรถยนต์</t>
+          <t>ก๊าชยานพาหนะ (LPG)</t>
         </is>
       </c>
       <c r="F1279" t="inlineStr">
         <is>
-          <t>เดือน_นอกเขต</t>
+          <t>สัปดาห์_นอกเขต</t>
         </is>
       </c>
       <c r="G1279" t="inlineStr">
         <is>
-          <t>พีท</t>
+          <t>วิรัตน์</t>
         </is>
       </c>
       <c r="H1279" t="inlineStr">
@@ -57040,13 +57310,13 @@
         </is>
       </c>
       <c r="I1279" t="n">
-        <v>189.87</v>
+        <v>18.16</v>
       </c>
       <c r="J1279" t="n">
-        <v>183.9</v>
+        <v>18.06</v>
       </c>
       <c r="K1279" t="n">
-        <v>103.25</v>
+        <v>100.58</v>
       </c>
     </row>
     <row r="1280">
@@ -57061,12 +57331,12 @@
       </c>
       <c r="D1280" t="inlineStr">
         <is>
-          <t>5230002</t>
+          <t>5230001</t>
         </is>
       </c>
       <c r="E1280" t="inlineStr">
         <is>
-          <t>ค่าบริการปะยางรถยนต์</t>
+          <t>ค่าบริการล้างรถยนต์</t>
         </is>
       </c>
       <c r="F1280" t="inlineStr">
@@ -57085,13 +57355,13 @@
         </is>
       </c>
       <c r="I1280" t="n">
-        <v>136.19</v>
+        <v>189.87</v>
       </c>
       <c r="J1280" t="n">
-        <v>129.76</v>
+        <v>183.9</v>
       </c>
       <c r="K1280" t="n">
-        <v>104.95</v>
+        <v>103.25</v>
       </c>
     </row>
     <row r="1281">
@@ -57106,12 +57376,12 @@
       </c>
       <c r="D1281" t="inlineStr">
         <is>
-          <t>5230004</t>
+          <t>5230002</t>
         </is>
       </c>
       <c r="E1281" t="inlineStr">
         <is>
-          <t>ค่าบริการบำรุงรักษารถยนต์</t>
+          <t>ค่าบริการปะยางรถยนต์</t>
         </is>
       </c>
       <c r="F1281" t="inlineStr">
@@ -57130,13 +57400,13 @@
         </is>
       </c>
       <c r="I1281" t="n">
-        <v>340.24</v>
+        <v>136.19</v>
       </c>
       <c r="J1281" t="n">
-        <v>340.24</v>
+        <v>129.76</v>
       </c>
       <c r="K1281" t="n">
-        <v>100</v>
+        <v>104.95</v>
       </c>
     </row>
     <row r="1282">
@@ -57151,22 +57421,22 @@
       </c>
       <c r="D1282" t="inlineStr">
         <is>
-          <t>5230005</t>
+          <t>5230004</t>
         </is>
       </c>
       <c r="E1282" t="inlineStr">
         <is>
-          <t>ค่าบริการบำรุงรักษารถจักรยานยนต์</t>
+          <t>ค่าบริการบำรุงรักษารถยนต์</t>
         </is>
       </c>
       <c r="F1282" t="inlineStr">
         <is>
-          <t>เดือน_นอกเขตไม่คำนวณ</t>
+          <t>เดือน_นอกเขต</t>
         </is>
       </c>
       <c r="G1282" t="inlineStr">
         <is>
-          <t>ก้อง</t>
+          <t>พีท</t>
         </is>
       </c>
       <c r="H1282" t="inlineStr">
@@ -57175,10 +57445,10 @@
         </is>
       </c>
       <c r="I1282" t="n">
-        <v>139.42</v>
+        <v>340.24</v>
       </c>
       <c r="J1282" t="n">
-        <v>139.42</v>
+        <v>340.24</v>
       </c>
       <c r="K1282" t="n">
         <v>100</v>
@@ -57196,22 +57466,22 @@
       </c>
       <c r="D1283" t="inlineStr">
         <is>
-          <t>5230007</t>
+          <t>5230005</t>
         </is>
       </c>
       <c r="E1283" t="inlineStr">
         <is>
-          <t>ค่าบริการจอดรถ</t>
+          <t>ค่าบริการบำรุงรักษารถจักรยานยนต์</t>
         </is>
       </c>
       <c r="F1283" t="inlineStr">
         <is>
-          <t>เดือน_นอกเขต</t>
+          <t>เดือน_นอกเขตไม่คำนวณ</t>
         </is>
       </c>
       <c r="G1283" t="inlineStr">
         <is>
-          <t>เนย</t>
+          <t>ก้อง</t>
         </is>
       </c>
       <c r="H1283" t="inlineStr">
@@ -57220,10 +57490,10 @@
         </is>
       </c>
       <c r="I1283" t="n">
-        <v>20</v>
+        <v>139.42</v>
       </c>
       <c r="J1283" t="n">
-        <v>20</v>
+        <v>139.42</v>
       </c>
       <c r="K1283" t="n">
         <v>100</v>
@@ -57241,12 +57511,12 @@
       </c>
       <c r="D1284" t="inlineStr">
         <is>
-          <t>5230009</t>
+          <t>5230007</t>
         </is>
       </c>
       <c r="E1284" t="inlineStr">
         <is>
-          <t>ค่าบริการเปลี่ยนผ้าเบรค</t>
+          <t>ค่าบริการจอดรถ</t>
         </is>
       </c>
       <c r="F1284" t="inlineStr">
@@ -57265,10 +57535,10 @@
         </is>
       </c>
       <c r="I1284" t="n">
-        <v>1549.19</v>
+        <v>20</v>
       </c>
       <c r="J1284" t="n">
-        <v>1549.19</v>
+        <v>20</v>
       </c>
       <c r="K1284" t="n">
         <v>100</v>
@@ -57286,22 +57556,22 @@
       </c>
       <c r="D1285" t="inlineStr">
         <is>
-          <t>5320001</t>
+          <t>5230009</t>
         </is>
       </c>
       <c r="E1285" t="inlineStr">
         <is>
-          <t>ค่าเบี้ยประกันคุ้มครองผู้ประสพภัยจากรถ (พรบ.)</t>
+          <t>ค่าบริการเปลี่ยนผ้าเบรค</t>
         </is>
       </c>
       <c r="F1285" t="inlineStr">
         <is>
-          <t>เดือน_นอกเขตไม่คำนวณ</t>
+          <t>เดือน_นอกเขต</t>
         </is>
       </c>
       <c r="G1285" t="inlineStr">
         <is>
-          <t>ก้อง</t>
+          <t>เนย</t>
         </is>
       </c>
       <c r="H1285" t="inlineStr">
@@ -57310,10 +57580,10 @@
         </is>
       </c>
       <c r="I1285" t="n">
-        <v>245.21</v>
+        <v>1549.19</v>
       </c>
       <c r="J1285" t="n">
-        <v>245.21</v>
+        <v>1549.19</v>
       </c>
       <c r="K1285" t="n">
         <v>100</v>
@@ -57331,22 +57601,22 @@
       </c>
       <c r="D1286" t="inlineStr">
         <is>
-          <t>5330003</t>
+          <t>5320001</t>
         </is>
       </c>
       <c r="E1286" t="inlineStr">
         <is>
-          <t>กล้องติดรถยนต์</t>
+          <t>ค่าเบี้ยประกันคุ้มครองผู้ประสพภัยจากรถ (พรบ.)</t>
         </is>
       </c>
       <c r="F1286" t="inlineStr">
         <is>
-          <t>เดือน_นอกเขต</t>
+          <t>เดือน_นอกเขตไม่คำนวณ</t>
         </is>
       </c>
       <c r="G1286" t="inlineStr">
         <is>
-          <t>พราว</t>
+          <t>ก้อง</t>
         </is>
       </c>
       <c r="H1286" t="inlineStr">
@@ -57355,10 +57625,10 @@
         </is>
       </c>
       <c r="I1286" t="n">
-        <v>1886.29</v>
+        <v>245.21</v>
       </c>
       <c r="J1286" t="n">
-        <v>1886.29</v>
+        <v>245.21</v>
       </c>
       <c r="K1286" t="n">
         <v>100</v>
@@ -57376,12 +57646,12 @@
       </c>
       <c r="D1287" t="inlineStr">
         <is>
-          <t>5410002</t>
+          <t>5330003</t>
         </is>
       </c>
       <c r="E1287" t="inlineStr">
         <is>
-          <t>ค่าบริการใช้โทรศัพท์มือถือ</t>
+          <t>กล้องติดรถยนต์</t>
         </is>
       </c>
       <c r="F1287" t="inlineStr">
@@ -57391,7 +57661,7 @@
       </c>
       <c r="G1287" t="inlineStr">
         <is>
-          <t>ตุ๊กตา</t>
+          <t>พราว</t>
         </is>
       </c>
       <c r="H1287" t="inlineStr">
@@ -57400,10 +57670,10 @@
         </is>
       </c>
       <c r="I1287" t="n">
-        <v>399</v>
+        <v>1886.29</v>
       </c>
       <c r="J1287" t="n">
-        <v>399</v>
+        <v>1886.29</v>
       </c>
       <c r="K1287" t="n">
         <v>100</v>
@@ -57431,7 +57701,7 @@
       </c>
       <c r="F1288" t="inlineStr">
         <is>
-          <t>เดือน_นอกเขตไม่คำนวณ</t>
+          <t>เดือน_นอกเขต</t>
         </is>
       </c>
       <c r="G1288" t="inlineStr">
@@ -57444,9 +57714,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1288" t="inlineStr"/>
-      <c r="J1288" t="inlineStr"/>
-      <c r="K1288" t="inlineStr"/>
+      <c r="I1288" t="n">
+        <v>399</v>
+      </c>
+      <c r="J1288" t="n">
+        <v>399</v>
+      </c>
+      <c r="K1288" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="1289">
       <c r="A1289" t="n">
@@ -57460,22 +57736,22 @@
       </c>
       <c r="D1289" t="inlineStr">
         <is>
-          <t>5410003</t>
+          <t>5410002</t>
         </is>
       </c>
       <c r="E1289" t="inlineStr">
         <is>
-          <t>ค่าบริการใช้อินเทอร์เน็ต</t>
+          <t>ค่าบริการใช้โทรศัพท์มือถือ</t>
         </is>
       </c>
       <c r="F1289" t="inlineStr">
         <is>
-          <t>เดือน_นอกเขต</t>
+          <t>เดือน_นอกเขตไม่คำนวณ</t>
         </is>
       </c>
       <c r="G1289" t="inlineStr">
         <is>
-          <t>พราว</t>
+          <t>ตุ๊กตา</t>
         </is>
       </c>
       <c r="H1289" t="inlineStr">
@@ -57483,15 +57759,9 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1289" t="n">
-        <v>82.93000000000001</v>
-      </c>
-      <c r="J1289" t="n">
-        <v>82.93000000000001</v>
-      </c>
-      <c r="K1289" t="n">
-        <v>100</v>
-      </c>
+      <c r="I1289" t="inlineStr"/>
+      <c r="J1289" t="inlineStr"/>
+      <c r="K1289" t="inlineStr"/>
     </row>
     <row r="1290">
       <c r="A1290" t="n">
@@ -57515,7 +57785,7 @@
       </c>
       <c r="F1290" t="inlineStr">
         <is>
-          <t>เดือน_นอกเขตไม่คำนวณ</t>
+          <t>เดือน_นอกเขต</t>
         </is>
       </c>
       <c r="G1290" t="inlineStr">
@@ -57528,9 +57798,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1290" t="inlineStr"/>
-      <c r="J1290" t="inlineStr"/>
-      <c r="K1290" t="inlineStr"/>
+      <c r="I1290" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="J1290" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="K1290" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="1291">
       <c r="A1291" t="n">
@@ -57882,12 +58158,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1298" t="inlineStr"/>
+      <c r="I1298" t="n">
+        <v>143.86</v>
+      </c>
       <c r="J1298" t="n">
         <v>143.34</v>
       </c>
       <c r="K1298" t="n">
-        <v>0</v>
+        <v>100.37</v>
       </c>
     </row>
     <row r="1299">
@@ -58553,7 +58831,7 @@
       </c>
       <c r="I1313" t="inlineStr"/>
       <c r="J1313" t="n">
-        <v>10.73</v>
+        <v>11.14</v>
       </c>
       <c r="K1313" t="n">
         <v>0</v>
@@ -59074,13 +59352,13 @@
         </is>
       </c>
       <c r="I1325" t="n">
-        <v>28.33</v>
+        <v>28.3</v>
       </c>
       <c r="J1325" t="n">
         <v>28.47</v>
       </c>
       <c r="K1325" t="n">
-        <v>99.51000000000001</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="1326">
@@ -59203,13 +59481,13 @@
         </is>
       </c>
       <c r="I1328" t="n">
-        <v>34.86</v>
+        <v>33.66</v>
       </c>
       <c r="J1328" t="n">
-        <v>34.93</v>
+        <v>33.72</v>
       </c>
       <c r="K1328" t="n">
-        <v>99.81</v>
+        <v>99.81999999999999</v>
       </c>
     </row>
     <row r="1329">
@@ -59292,12 +59570,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1330" t="inlineStr"/>
+      <c r="I1330" t="n">
+        <v>27.19</v>
+      </c>
       <c r="J1330" t="n">
         <v>27.16</v>
       </c>
       <c r="K1330" t="n">
-        <v>0</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="1331">
@@ -62169,10 +62449,10 @@
         <v>14.13</v>
       </c>
       <c r="J1395" t="n">
-        <v>4.39</v>
+        <v>10.33</v>
       </c>
       <c r="K1395" t="n">
-        <v>321.83</v>
+        <v>136.76</v>
       </c>
     </row>
     <row r="1396">
@@ -65368,13 +65648,13 @@
         </is>
       </c>
       <c r="I1467" t="n">
-        <v>66.53</v>
+        <v>66.91</v>
       </c>
       <c r="J1467" t="n">
         <v>66.76000000000001</v>
       </c>
       <c r="K1467" t="n">
-        <v>99.66</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="1468">
@@ -68692,10 +68972,10 @@
         </is>
       </c>
       <c r="I1541" t="n">
-        <v>210.4</v>
+        <v>209.5</v>
       </c>
       <c r="J1541" t="n">
-        <v>210.4</v>
+        <v>209.5</v>
       </c>
       <c r="K1541" t="n">
         <v>100</v>
@@ -69768,13 +70048,13 @@
         </is>
       </c>
       <c r="I1565" t="n">
-        <v>290.08</v>
+        <v>283.02</v>
       </c>
       <c r="J1565" t="n">
-        <v>283.52</v>
+        <v>282.37</v>
       </c>
       <c r="K1565" t="n">
-        <v>102.31</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="1566">
@@ -69812,12 +70092,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1566" t="inlineStr"/>
+      <c r="I1566" t="n">
+        <v>25.27</v>
+      </c>
       <c r="J1566" t="n">
         <v>24.59</v>
       </c>
       <c r="K1566" t="n">
-        <v>0</v>
+        <v>102.74</v>
       </c>
     </row>
     <row r="1567">
@@ -69859,10 +70141,10 @@
         <v>51.37</v>
       </c>
       <c r="J1567" t="n">
-        <v>51</v>
+        <v>50.02</v>
       </c>
       <c r="K1567" t="n">
-        <v>100.71</v>
+        <v>102.69</v>
       </c>
     </row>
     <row r="1568">
@@ -70973,10 +71255,10 @@
         </is>
       </c>
       <c r="I1592" t="n">
-        <v>160.91</v>
+        <v>167.46</v>
       </c>
       <c r="J1592" t="n">
-        <v>160.91</v>
+        <v>167.46</v>
       </c>
       <c r="K1592" t="n">
         <v>100</v>
@@ -72050,12 +72332,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1616" t="inlineStr"/>
+      <c r="I1616" t="n">
+        <v>21.7</v>
+      </c>
       <c r="J1616" t="n">
-        <v>21.39</v>
+        <v>21.27</v>
       </c>
       <c r="K1616" t="n">
-        <v>0</v>
+        <v>102.05</v>
       </c>
     </row>
     <row r="1617">
@@ -72228,12 +72512,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1620" t="inlineStr"/>
+      <c r="I1620" t="n">
+        <v>40.85</v>
+      </c>
       <c r="J1620" t="n">
         <v>42.49</v>
       </c>
       <c r="K1620" t="n">
-        <v>0</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="1621">
@@ -72942,12 +73228,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1636" t="inlineStr"/>
+      <c r="I1636" t="n">
+        <v>19.37</v>
+      </c>
       <c r="J1636" t="n">
-        <v>18.99</v>
+        <v>19.37</v>
       </c>
       <c r="K1636" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1637">
@@ -73391,13 +73679,13 @@
         </is>
       </c>
       <c r="I1646" t="n">
-        <v>66.64</v>
+        <v>62.96</v>
       </c>
       <c r="J1646" t="n">
-        <v>84.31999999999999</v>
+        <v>62.96</v>
       </c>
       <c r="K1646" t="n">
-        <v>79.03</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1647">
@@ -74643,10 +74931,10 @@
         </is>
       </c>
       <c r="I1674" t="n">
-        <v>181.06</v>
+        <v>169.5</v>
       </c>
       <c r="J1674" t="n">
-        <v>181.06</v>
+        <v>169.5</v>
       </c>
       <c r="K1674" t="n">
         <v>100</v>
@@ -75982,12 +76270,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1704" t="inlineStr"/>
+      <c r="I1704" t="n">
+        <v>777.11</v>
+      </c>
       <c r="J1704" t="n">
-        <v>652.37</v>
+        <v>653.85</v>
       </c>
       <c r="K1704" t="n">
-        <v>0</v>
+        <v>118.85</v>
       </c>
     </row>
     <row r="1705">
@@ -76026,13 +76316,13 @@
         </is>
       </c>
       <c r="I1705" t="n">
-        <v>237.84</v>
+        <v>238.72</v>
       </c>
       <c r="J1705" t="n">
         <v>238.72</v>
       </c>
       <c r="K1705" t="n">
-        <v>99.64</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1706">
@@ -76115,12 +76405,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1707" t="inlineStr"/>
+      <c r="I1707" t="n">
+        <v>53262.53</v>
+      </c>
       <c r="J1707" t="n">
-        <v>49488.25</v>
+        <v>51737.37</v>
       </c>
       <c r="K1707" t="n">
-        <v>0</v>
+        <v>102.95</v>
       </c>
     </row>
     <row r="1708">
@@ -76834,10 +77126,10 @@
         </is>
       </c>
       <c r="I1723" t="n">
-        <v>3364.68</v>
+        <v>2317.9</v>
       </c>
       <c r="J1723" t="n">
-        <v>3364.68</v>
+        <v>2317.9</v>
       </c>
       <c r="K1723" t="n">
         <v>100</v>
@@ -76969,13 +77261,13 @@
         </is>
       </c>
       <c r="I1726" t="n">
-        <v>58.01</v>
+        <v>47.88</v>
       </c>
       <c r="J1726" t="n">
         <v>47.88</v>
       </c>
       <c r="K1726" t="n">
-        <v>121.15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1727">
@@ -77419,13 +77711,13 @@
         </is>
       </c>
       <c r="I1736" t="n">
-        <v>163.5</v>
+        <v>167.85</v>
       </c>
       <c r="J1736" t="n">
-        <v>161.43</v>
+        <v>166.38</v>
       </c>
       <c r="K1736" t="n">
-        <v>101.28</v>
+        <v>100.88</v>
       </c>
     </row>
     <row r="1737">
@@ -78403,10 +78695,10 @@
         </is>
       </c>
       <c r="I1758" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="J1758" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="K1758" t="n">
         <v>100</v>

--- a/ReportforHeaderU/ReportforHeaderU.xlsx
+++ b/ReportforHeaderU/ReportforHeaderU.xlsx
@@ -604,12 +604,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>25.84</v>
+      </c>
       <c r="J4" t="n">
         <v>26.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>97.48999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -4987,9 +4989,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="J103" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="K103" t="n">
+        <v>101.52</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5026,9 +5034,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="I104" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="J104" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="K104" t="n">
+        <v>102.58</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5066,13 +5080,13 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>30.7</v>
+        <v>31.39</v>
       </c>
       <c r="J105" t="n">
-        <v>30.47</v>
+        <v>31.17</v>
       </c>
       <c r="K105" t="n">
-        <v>100.74</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="106">
@@ -5110,9 +5124,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="I106" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="J106" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="K106" t="n">
+        <v>105.71</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5149,9 +5169,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="J107" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="K107" t="n">
+        <v>101.43</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5188,9 +5214,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="I108" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="J108" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="K108" t="n">
+        <v>100.98</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5227,9 +5259,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="I109" t="n">
+        <v>140.82</v>
+      </c>
+      <c r="J109" t="n">
+        <v>135.54</v>
+      </c>
+      <c r="K109" t="n">
+        <v>103.89</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5266,9 +5304,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="J110" t="n">
+        <v>107.97</v>
+      </c>
+      <c r="K110" t="n">
+        <v>100.31</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5305,9 +5349,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="I111" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="J111" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K111" t="n">
+        <v>99.22</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5344,9 +5394,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="I112" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="J112" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="K112" t="n">
+        <v>97.23</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5383,9 +5439,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="I113" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="J113" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="K113" t="n">
+        <v>97.16</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5422,9 +5484,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="I114" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="J114" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="K114" t="n">
+        <v>100.87</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5461,9 +5529,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="I115" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="J115" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="K115" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5500,9 +5574,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="J116" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="K116" t="n">
+        <v>114.49</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5539,9 +5619,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="I117" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="J117" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="K117" t="n">
+        <v>95.98999999999999</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5578,9 +5664,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="J118" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="K118" t="n">
+        <v>99.98999999999999</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5707,9 +5799,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+      <c r="I121" t="n">
+        <v>53.91</v>
+      </c>
+      <c r="J121" t="n">
+        <v>54.36</v>
+      </c>
+      <c r="K121" t="n">
+        <v>99.17</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5746,9 +5844,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="J122" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="K122" t="n">
+        <v>107.07</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5785,9 +5889,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+      <c r="I123" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="J123" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="K123" t="n">
+        <v>98.18000000000001</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5824,9 +5934,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
+      <c r="I124" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="J124" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="K124" t="n">
+        <v>100.84</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5863,9 +5979,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="J125" t="n">
+        <v>84.83</v>
+      </c>
+      <c r="K125" t="n">
+        <v>105.77</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5946,13 +6068,13 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>57.11</v>
+        <v>56.22</v>
       </c>
       <c r="J127" t="n">
-        <v>56.55</v>
+        <v>55.83</v>
       </c>
       <c r="K127" t="n">
-        <v>100.99</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="128">
@@ -6699,13 +6821,13 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>129.97</v>
+        <v>131.94</v>
       </c>
       <c r="J144" t="n">
-        <v>132.33</v>
+        <v>133.35</v>
       </c>
       <c r="K144" t="n">
-        <v>98.20999999999999</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="145">
@@ -6744,13 +6866,13 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>10.8</v>
+        <v>10.69</v>
       </c>
       <c r="J145" t="n">
-        <v>10.81</v>
+        <v>10.71</v>
       </c>
       <c r="K145" t="n">
-        <v>99.89</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -6837,10 +6959,10 @@
         <v>52.52</v>
       </c>
       <c r="J147" t="n">
-        <v>52.88</v>
+        <v>52.82</v>
       </c>
       <c r="K147" t="n">
-        <v>99.31</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="148">
@@ -6924,10 +7046,10 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>15.81</v>
+        <v>15.86</v>
       </c>
       <c r="J149" t="n">
-        <v>15.81</v>
+        <v>15.86</v>
       </c>
       <c r="K149" t="n">
         <v>100</v>
@@ -7194,13 +7316,13 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>427.69</v>
+        <v>427.32</v>
       </c>
       <c r="J155" t="n">
-        <v>423.57</v>
+        <v>423.33</v>
       </c>
       <c r="K155" t="n">
-        <v>100.97</v>
+        <v>100.94</v>
       </c>
     </row>
     <row r="156">
@@ -7329,13 +7451,13 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>17.64</v>
+        <v>17.63</v>
       </c>
       <c r="J158" t="n">
-        <v>17.54</v>
+        <v>17.52</v>
       </c>
       <c r="K158" t="n">
-        <v>100.61</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="159">
@@ -8265,12 +8387,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" t="n">
+        <v>31.9</v>
+      </c>
       <c r="J179" t="n">
         <v>32.03</v>
       </c>
       <c r="K179" t="n">
-        <v>0</v>
+        <v>99.62</v>
       </c>
     </row>
     <row r="180">
@@ -12563,10 +12687,10 @@
         <v>146.67</v>
       </c>
       <c r="J275" t="n">
-        <v>149.83</v>
+        <v>146.67</v>
       </c>
       <c r="K275" t="n">
-        <v>97.89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="276">
@@ -14514,10 +14638,10 @@
         </is>
       </c>
       <c r="I319" t="n">
-        <v>19.44</v>
+        <v>19.74</v>
       </c>
       <c r="J319" t="n">
-        <v>19.44</v>
+        <v>19.74</v>
       </c>
       <c r="K319" t="n">
         <v>100</v>
@@ -16127,12 +16251,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I355" t="inlineStr"/>
+      <c r="I355" t="n">
+        <v>190.75</v>
+      </c>
       <c r="J355" t="n">
-        <v>184.31</v>
+        <v>185.84</v>
       </c>
       <c r="K355" t="n">
-        <v>0</v>
+        <v>102.64</v>
       </c>
     </row>
     <row r="356">
@@ -16617,13 +16743,13 @@
         </is>
       </c>
       <c r="I366" t="n">
-        <v>230.56</v>
+        <v>229.14</v>
       </c>
       <c r="J366" t="n">
-        <v>228.66</v>
+        <v>229.14</v>
       </c>
       <c r="K366" t="n">
-        <v>100.83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="367">
@@ -19473,13 +19599,13 @@
         </is>
       </c>
       <c r="I430" t="n">
-        <v>195.51</v>
+        <v>197.33</v>
       </c>
       <c r="J430" t="n">
-        <v>192.9</v>
+        <v>195.21</v>
       </c>
       <c r="K430" t="n">
-        <v>101.35</v>
+        <v>101.09</v>
       </c>
     </row>
     <row r="431">
@@ -19611,10 +19737,10 @@
         <v>21.12</v>
       </c>
       <c r="J433" t="n">
-        <v>22.08</v>
+        <v>21.12</v>
       </c>
       <c r="K433" t="n">
-        <v>95.64</v>
+        <v>100</v>
       </c>
     </row>
     <row r="434">
@@ -20365,10 +20491,10 @@
         </is>
       </c>
       <c r="I450" t="n">
-        <v>12.64</v>
+        <v>13.42</v>
       </c>
       <c r="J450" t="n">
-        <v>12.64</v>
+        <v>13.42</v>
       </c>
       <c r="K450" t="n">
         <v>100</v>
@@ -20902,12 +21028,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I462" t="inlineStr"/>
+      <c r="I462" t="n">
+        <v>29.38</v>
+      </c>
       <c r="J462" t="n">
         <v>29.77</v>
       </c>
       <c r="K462" t="n">
-        <v>0</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="463">
@@ -25248,9 +25376,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I562" t="inlineStr"/>
-      <c r="J562" t="inlineStr"/>
-      <c r="K562" t="inlineStr"/>
+      <c r="I562" t="n">
+        <v>44.73</v>
+      </c>
+      <c r="J562" t="n">
+        <v>44.96</v>
+      </c>
+      <c r="K562" t="n">
+        <v>99.48999999999999</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -25287,9 +25421,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I563" t="inlineStr"/>
-      <c r="J563" t="inlineStr"/>
-      <c r="K563" t="inlineStr"/>
+      <c r="I563" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="J563" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="K563" t="n">
+        <v>99.26000000000001</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -25326,9 +25466,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I564" t="inlineStr"/>
-      <c r="J564" t="inlineStr"/>
-      <c r="K564" t="inlineStr"/>
+      <c r="I564" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="J564" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="K564" t="n">
+        <v>118.14</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -25365,9 +25511,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I565" t="inlineStr"/>
-      <c r="J565" t="inlineStr"/>
-      <c r="K565" t="inlineStr"/>
+      <c r="I565" t="n">
+        <v>29.44</v>
+      </c>
+      <c r="J565" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="K565" t="n">
+        <v>96.90000000000001</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -25404,9 +25556,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I566" t="inlineStr"/>
-      <c r="J566" t="inlineStr"/>
-      <c r="K566" t="inlineStr"/>
+      <c r="I566" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="J566" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="K566" t="n">
+        <v>100.14</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -25443,9 +25601,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I567" t="inlineStr"/>
-      <c r="J567" t="inlineStr"/>
-      <c r="K567" t="inlineStr"/>
+      <c r="I567" t="n">
+        <v>145.65</v>
+      </c>
+      <c r="J567" t="n">
+        <v>143.85</v>
+      </c>
+      <c r="K567" t="n">
+        <v>101.25</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -25482,9 +25646,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I568" t="inlineStr"/>
-      <c r="J568" t="inlineStr"/>
-      <c r="K568" t="inlineStr"/>
+      <c r="I568" t="n">
+        <v>101.62</v>
+      </c>
+      <c r="J568" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="K568" t="n">
+        <v>104.36</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -25521,9 +25691,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I569" t="inlineStr"/>
-      <c r="J569" t="inlineStr"/>
-      <c r="K569" t="inlineStr"/>
+      <c r="I569" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="J569" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="K569" t="n">
+        <v>100.23</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -25560,9 +25736,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I570" t="inlineStr"/>
-      <c r="J570" t="inlineStr"/>
-      <c r="K570" t="inlineStr"/>
+      <c r="I570" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="J570" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="K570" t="n">
+        <v>98.31999999999999</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -25599,9 +25781,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I571" t="inlineStr"/>
-      <c r="J571" t="inlineStr"/>
-      <c r="K571" t="inlineStr"/>
+      <c r="I571" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="J571" t="n">
+        <v>61.66</v>
+      </c>
+      <c r="K571" t="n">
+        <v>103.2</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -25638,9 +25826,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I572" t="inlineStr"/>
-      <c r="J572" t="inlineStr"/>
-      <c r="K572" t="inlineStr"/>
+      <c r="I572" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="J572" t="n">
+        <v>48.36</v>
+      </c>
+      <c r="K572" t="n">
+        <v>99.58</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -25677,9 +25871,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I573" t="inlineStr"/>
-      <c r="J573" t="inlineStr"/>
-      <c r="K573" t="inlineStr"/>
+      <c r="I573" t="n">
+        <v>44</v>
+      </c>
+      <c r="J573" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="K573" t="n">
+        <v>100.56</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -25716,9 +25916,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I574" t="inlineStr"/>
-      <c r="J574" t="inlineStr"/>
-      <c r="K574" t="inlineStr"/>
+      <c r="I574" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="J574" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="K574" t="n">
+        <v>108.88</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -25755,9 +25961,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I575" t="inlineStr"/>
-      <c r="J575" t="inlineStr"/>
-      <c r="K575" t="inlineStr"/>
+      <c r="I575" t="n">
+        <v>46.59</v>
+      </c>
+      <c r="J575" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="K575" t="n">
+        <v>98.98</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -25794,9 +26006,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I576" t="inlineStr"/>
-      <c r="J576" t="inlineStr"/>
-      <c r="K576" t="inlineStr"/>
+      <c r="I576" t="n">
+        <v>58.58</v>
+      </c>
+      <c r="J576" t="n">
+        <v>65.06999999999999</v>
+      </c>
+      <c r="K576" t="n">
+        <v>90.03</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -25833,9 +26051,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I577" t="inlineStr"/>
-      <c r="J577" t="inlineStr"/>
-      <c r="K577" t="inlineStr"/>
+      <c r="I577" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="J577" t="n">
+        <v>73.34</v>
+      </c>
+      <c r="K577" t="n">
+        <v>98.25</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -25872,9 +26096,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I578" t="inlineStr"/>
-      <c r="J578" t="inlineStr"/>
-      <c r="K578" t="inlineStr"/>
+      <c r="I578" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="J578" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="K578" t="n">
+        <v>101.24</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -25911,9 +26141,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I579" t="inlineStr"/>
-      <c r="J579" t="inlineStr"/>
-      <c r="K579" t="inlineStr"/>
+      <c r="I579" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="J579" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="K579" t="n">
+        <v>98.16</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -25995,9 +26231,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I581" t="inlineStr"/>
-      <c r="J581" t="inlineStr"/>
-      <c r="K581" t="inlineStr"/>
+      <c r="I581" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="J581" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="K581" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -26034,9 +26276,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I582" t="inlineStr"/>
-      <c r="J582" t="inlineStr"/>
-      <c r="K582" t="inlineStr"/>
+      <c r="I582" t="n">
+        <v>84.77</v>
+      </c>
+      <c r="J582" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="K582" t="n">
+        <v>102.31</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -26116,9 +26364,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I584" t="inlineStr"/>
-      <c r="J584" t="inlineStr"/>
-      <c r="K584" t="inlineStr"/>
+      <c r="I584" t="n">
+        <v>61.93</v>
+      </c>
+      <c r="J584" t="n">
+        <v>61.93</v>
+      </c>
+      <c r="K584" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -26862,13 +27116,13 @@
         </is>
       </c>
       <c r="I601" t="n">
-        <v>149.08</v>
+        <v>149.16</v>
       </c>
       <c r="J601" t="n">
         <v>150.23</v>
       </c>
       <c r="K601" t="n">
-        <v>99.23</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="602">
@@ -26952,13 +27206,13 @@
         </is>
       </c>
       <c r="I603" t="n">
-        <v>22.51</v>
+        <v>22.53</v>
       </c>
       <c r="J603" t="n">
         <v>22.3</v>
       </c>
       <c r="K603" t="n">
-        <v>100.93</v>
+        <v>101.04</v>
       </c>
     </row>
     <row r="604">
@@ -27357,13 +27611,13 @@
         </is>
       </c>
       <c r="I612" t="n">
-        <v>394.79</v>
+        <v>399.58</v>
       </c>
       <c r="J612" t="n">
-        <v>389.63</v>
+        <v>392.78</v>
       </c>
       <c r="K612" t="n">
-        <v>101.32</v>
+        <v>101.73</v>
       </c>
     </row>
     <row r="613">
@@ -28472,13 +28726,13 @@
         </is>
       </c>
       <c r="I637" t="n">
-        <v>20.23</v>
+        <v>20.25</v>
       </c>
       <c r="J637" t="n">
         <v>20.25</v>
       </c>
       <c r="K637" t="n">
-        <v>99.89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="638">
@@ -34255,10 +34509,10 @@
         </is>
       </c>
       <c r="I766" t="n">
-        <v>10.01</v>
+        <v>10.62</v>
       </c>
       <c r="J766" t="n">
-        <v>10.01</v>
+        <v>10.62</v>
       </c>
       <c r="K766" t="n">
         <v>100</v>
@@ -34435,10 +34689,10 @@
         </is>
       </c>
       <c r="I770" t="n">
-        <v>53.63</v>
+        <v>53.09</v>
       </c>
       <c r="J770" t="n">
-        <v>53.63</v>
+        <v>53.09</v>
       </c>
       <c r="K770" t="n">
         <v>100</v>
@@ -36002,13 +36256,13 @@
         </is>
       </c>
       <c r="I805" t="n">
-        <v>190.27</v>
+        <v>191.99</v>
       </c>
       <c r="J805" t="n">
-        <v>191.18</v>
+        <v>193.07</v>
       </c>
       <c r="K805" t="n">
-        <v>99.52</v>
+        <v>99.44</v>
       </c>
     </row>
     <row r="806">
@@ -38776,13 +39030,13 @@
         </is>
       </c>
       <c r="I867" t="n">
-        <v>152.78</v>
+        <v>152.91</v>
       </c>
       <c r="J867" t="n">
-        <v>154.35</v>
+        <v>153.1</v>
       </c>
       <c r="K867" t="n">
-        <v>98.98</v>
+        <v>99.87</v>
       </c>
     </row>
     <row r="868">
@@ -39447,10 +39701,10 @@
         </is>
       </c>
       <c r="I882" t="n">
-        <v>2153.57</v>
+        <v>2208.3</v>
       </c>
       <c r="J882" t="n">
-        <v>2153.57</v>
+        <v>2208.3</v>
       </c>
       <c r="K882" t="n">
         <v>100</v>
@@ -46163,13 +46417,13 @@
         </is>
       </c>
       <c r="I1034" t="n">
-        <v>85.56999999999999</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="J1034" t="n">
-        <v>84.08</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="K1034" t="n">
-        <v>101.77</v>
+        <v>101.12</v>
       </c>
     </row>
     <row r="1035">
@@ -46211,10 +46465,10 @@
         <v>127.34</v>
       </c>
       <c r="J1035" t="n">
-        <v>128.27</v>
+        <v>127.97</v>
       </c>
       <c r="K1035" t="n">
-        <v>99.28</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row r="1036">
@@ -46253,13 +46507,13 @@
         </is>
       </c>
       <c r="I1036" t="n">
-        <v>10.96</v>
+        <v>10.65</v>
       </c>
       <c r="J1036" t="n">
-        <v>10.8</v>
+        <v>10.51</v>
       </c>
       <c r="K1036" t="n">
-        <v>101.51</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="1037">
@@ -46298,13 +46552,13 @@
         </is>
       </c>
       <c r="I1037" t="n">
-        <v>23.21</v>
+        <v>22.4</v>
       </c>
       <c r="J1037" t="n">
-        <v>23.23</v>
+        <v>22.39</v>
       </c>
       <c r="K1037" t="n">
-        <v>99.91</v>
+        <v>100.02</v>
       </c>
     </row>
     <row r="1038">
@@ -46343,13 +46597,13 @@
         </is>
       </c>
       <c r="I1038" t="n">
-        <v>48.55</v>
+        <v>49.12</v>
       </c>
       <c r="J1038" t="n">
-        <v>48.61</v>
+        <v>49.17</v>
       </c>
       <c r="K1038" t="n">
-        <v>99.89</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="1039">
@@ -46433,10 +46687,10 @@
         </is>
       </c>
       <c r="I1040" t="n">
-        <v>11.4</v>
+        <v>12.12</v>
       </c>
       <c r="J1040" t="n">
-        <v>11.39</v>
+        <v>12.11</v>
       </c>
       <c r="K1040" t="n">
         <v>100.12</v>
@@ -46616,10 +46870,10 @@
         <v>16.68</v>
       </c>
       <c r="J1044" t="n">
-        <v>16.68</v>
+        <v>16.65</v>
       </c>
       <c r="K1044" t="n">
-        <v>100</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="1045">
@@ -46658,10 +46912,10 @@
         </is>
       </c>
       <c r="I1045" t="n">
-        <v>19.81</v>
+        <v>19.68</v>
       </c>
       <c r="J1045" t="n">
-        <v>19.88</v>
+        <v>19.75</v>
       </c>
       <c r="K1045" t="n">
         <v>99.62</v>
@@ -46703,13 +46957,13 @@
         </is>
       </c>
       <c r="I1046" t="n">
-        <v>471.18</v>
+        <v>475.1</v>
       </c>
       <c r="J1046" t="n">
-        <v>465.88</v>
+        <v>465.5</v>
       </c>
       <c r="K1046" t="n">
-        <v>101.14</v>
+        <v>102.06</v>
       </c>
     </row>
     <row r="1047">
@@ -47815,10 +48069,10 @@
         <v>20.63</v>
       </c>
       <c r="J1071" t="n">
-        <v>20.63</v>
+        <v>20.59</v>
       </c>
       <c r="K1071" t="n">
-        <v>100</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="1072">
@@ -51839,12 +52093,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1161" t="inlineStr"/>
+      <c r="I1161" t="n">
+        <v>358.53</v>
+      </c>
       <c r="J1161" t="n">
-        <v>364.45</v>
+        <v>358.53</v>
       </c>
       <c r="K1161" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1162">
@@ -52731,12 +52987,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1181" t="inlineStr"/>
+      <c r="I1181" t="n">
+        <v>31.53</v>
+      </c>
       <c r="J1181" t="n">
-        <v>30.61</v>
+        <v>31.01</v>
       </c>
       <c r="K1181" t="n">
-        <v>0</v>
+        <v>101.69</v>
       </c>
     </row>
     <row r="1182">
@@ -53353,12 +53611,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1195" t="inlineStr"/>
+      <c r="I1195" t="n">
+        <v>20.59</v>
+      </c>
       <c r="J1195" t="n">
-        <v>15.38</v>
+        <v>20.59</v>
       </c>
       <c r="K1195" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1196">
@@ -53577,13 +53837,13 @@
         </is>
       </c>
       <c r="I1200" t="n">
-        <v>59.99</v>
+        <v>60.31</v>
       </c>
       <c r="J1200" t="n">
         <v>60.11</v>
       </c>
       <c r="K1200" t="n">
-        <v>99.8</v>
+        <v>100.34</v>
       </c>
     </row>
     <row r="1201">
@@ -54161,12 +54421,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1213" t="inlineStr"/>
+      <c r="I1213" t="n">
+        <v>50</v>
+      </c>
       <c r="J1213" t="n">
         <v>50</v>
       </c>
       <c r="K1213" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1214">
@@ -54294,12 +54556,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1216" t="inlineStr"/>
+      <c r="I1216" t="n">
+        <v>428.03</v>
+      </c>
       <c r="J1216" t="n">
         <v>428.03</v>
       </c>
       <c r="K1216" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1217">
@@ -54337,12 +54601,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1217" t="inlineStr"/>
+      <c r="I1217" t="n">
+        <v>4178.22</v>
+      </c>
       <c r="J1217" t="n">
         <v>4178.22</v>
       </c>
       <c r="K1217" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1218">
@@ -54425,12 +54691,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1219" t="inlineStr"/>
+      <c r="I1219" t="n">
+        <v>621.97</v>
+      </c>
       <c r="J1219" t="n">
         <v>621.97</v>
       </c>
       <c r="K1219" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1220">
@@ -55006,12 +55274,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1232" t="inlineStr"/>
+      <c r="I1232" t="n">
+        <v>163.68</v>
+      </c>
       <c r="J1232" t="n">
-        <v>163.56</v>
+        <v>163.92</v>
       </c>
       <c r="K1232" t="n">
-        <v>0</v>
+        <v>99.84999999999999</v>
       </c>
     </row>
     <row r="1233">
@@ -55363,13 +55633,13 @@
         </is>
       </c>
       <c r="I1240" t="n">
-        <v>268.9</v>
+        <v>268.86</v>
       </c>
       <c r="J1240" t="n">
-        <v>250.09</v>
+        <v>268.86</v>
       </c>
       <c r="K1240" t="n">
-        <v>107.52</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1241">
@@ -55544,7 +55814,7 @@
       </c>
       <c r="I1244" t="inlineStr"/>
       <c r="J1244" t="n">
-        <v>74.36</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="K1244" t="n">
         <v>0</v>
@@ -58125,10 +58395,10 @@
         </is>
       </c>
       <c r="I1302" t="n">
-        <v>141.2</v>
+        <v>146.28</v>
       </c>
       <c r="J1302" t="n">
-        <v>141.2</v>
+        <v>146.28</v>
       </c>
       <c r="K1302" t="n">
         <v>100</v>
@@ -58303,13 +58573,13 @@
         </is>
       </c>
       <c r="I1306" t="n">
-        <v>11.99</v>
+        <v>12.68</v>
       </c>
       <c r="J1306" t="n">
         <v>10</v>
       </c>
       <c r="K1306" t="n">
-        <v>119.93</v>
+        <v>126.83</v>
       </c>
     </row>
     <row r="1307">
@@ -58708,10 +58978,10 @@
         </is>
       </c>
       <c r="I1315" t="n">
-        <v>11.14</v>
+        <v>10.85</v>
       </c>
       <c r="J1315" t="n">
-        <v>11.14</v>
+        <v>10.85</v>
       </c>
       <c r="K1315" t="n">
         <v>100</v>
@@ -65436,10 +65706,10 @@
         <v>81.83</v>
       </c>
       <c r="J1466" t="n">
-        <v>81.41</v>
+        <v>81.5</v>
       </c>
       <c r="K1466" t="n">
-        <v>100.51</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="1467">
@@ -65568,13 +65838,13 @@
         </is>
       </c>
       <c r="I1469" t="n">
-        <v>21.07</v>
+        <v>21.23</v>
       </c>
       <c r="J1469" t="n">
-        <v>20.94</v>
+        <v>21.09</v>
       </c>
       <c r="K1469" t="n">
-        <v>100.64</v>
+        <v>100.63</v>
       </c>
     </row>
     <row r="1470">
@@ -65613,10 +65883,10 @@
         </is>
       </c>
       <c r="I1470" t="n">
-        <v>47.43</v>
+        <v>47.51</v>
       </c>
       <c r="J1470" t="n">
-        <v>48.14</v>
+        <v>48.22</v>
       </c>
       <c r="K1470" t="n">
         <v>98.52</v>
@@ -65973,13 +66243,13 @@
         </is>
       </c>
       <c r="I1478" t="n">
-        <v>382.69</v>
+        <v>382.04</v>
       </c>
       <c r="J1478" t="n">
         <v>377.19</v>
       </c>
       <c r="K1478" t="n">
-        <v>101.46</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="1479">
@@ -67051,13 +67321,13 @@
         </is>
       </c>
       <c r="I1502" t="n">
-        <v>33.04</v>
+        <v>33.27</v>
       </c>
       <c r="J1502" t="n">
-        <v>32.95</v>
+        <v>33.18</v>
       </c>
       <c r="K1502" t="n">
-        <v>100.27</v>
+        <v>100.26</v>
       </c>
     </row>
     <row r="1503">
@@ -67096,13 +67366,13 @@
         </is>
       </c>
       <c r="I1503" t="n">
-        <v>21.36</v>
+        <v>21.37</v>
       </c>
       <c r="J1503" t="n">
         <v>21.41</v>
       </c>
       <c r="K1503" t="n">
-        <v>99.77</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="1504">
@@ -72243,13 +72513,13 @@
         </is>
       </c>
       <c r="I1618" t="n">
-        <v>26.57</v>
+        <v>26.89</v>
       </c>
       <c r="J1618" t="n">
-        <v>26.09</v>
+        <v>26.38</v>
       </c>
       <c r="K1618" t="n">
-        <v>101.86</v>
+        <v>101.96</v>
       </c>
     </row>
     <row r="1619">
@@ -72824,13 +73094,13 @@
         </is>
       </c>
       <c r="I1631" t="n">
-        <v>32.1</v>
+        <v>32.21</v>
       </c>
       <c r="J1631" t="n">
-        <v>32.64</v>
+        <v>32.21</v>
       </c>
       <c r="K1631" t="n">
-        <v>98.33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1632">
@@ -72868,12 +73138,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1632" t="inlineStr"/>
+      <c r="I1632" t="n">
+        <v>14.06</v>
+      </c>
       <c r="J1632" t="n">
         <v>14.06</v>
       </c>
       <c r="K1632" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1633">
@@ -72911,12 +73183,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1633" t="inlineStr"/>
+      <c r="I1633" t="n">
+        <v>10.56</v>
+      </c>
       <c r="J1633" t="n">
-        <v>10.73</v>
+        <v>10.56</v>
       </c>
       <c r="K1633" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1634">
@@ -73134,12 +73408,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1638" t="inlineStr"/>
+      <c r="I1638" t="n">
+        <v>188.96</v>
+      </c>
       <c r="J1638" t="n">
         <v>188.96</v>
       </c>
       <c r="K1638" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1639">
@@ -73222,12 +73498,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1640" t="inlineStr"/>
+      <c r="I1640" t="n">
+        <v>19.38</v>
+      </c>
       <c r="J1640" t="n">
         <v>19.37</v>
       </c>
       <c r="K1640" t="n">
-        <v>0</v>
+        <v>100.08</v>
       </c>
     </row>
     <row r="1641">
@@ -73311,13 +73589,13 @@
         </is>
       </c>
       <c r="I1642" t="n">
-        <v>62.37</v>
+        <v>62.54</v>
       </c>
       <c r="J1642" t="n">
-        <v>63.31</v>
+        <v>62.54</v>
       </c>
       <c r="K1642" t="n">
-        <v>98.51000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1643">
@@ -73355,12 +73633,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1643" t="inlineStr"/>
+      <c r="I1643" t="n">
+        <v>88.34999999999999</v>
+      </c>
       <c r="J1643" t="n">
-        <v>89.39</v>
+        <v>89.13</v>
       </c>
       <c r="K1643" t="n">
-        <v>0</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="1644">
@@ -73488,12 +73768,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1646" t="inlineStr"/>
+      <c r="I1646" t="n">
+        <v>46.52</v>
+      </c>
       <c r="J1646" t="n">
         <v>46.4</v>
       </c>
       <c r="K1646" t="n">
-        <v>0</v>
+        <v>100.27</v>
       </c>
     </row>
     <row r="1647">
@@ -73533,7 +73815,7 @@
       </c>
       <c r="I1647" t="inlineStr"/>
       <c r="J1647" t="n">
-        <v>50.26</v>
+        <v>50.14</v>
       </c>
       <c r="K1647" t="n">
         <v>0</v>
@@ -73800,13 +74082,13 @@
         </is>
       </c>
       <c r="I1653" t="n">
-        <v>76.58</v>
+        <v>71.84</v>
       </c>
       <c r="J1653" t="n">
         <v>71.84</v>
       </c>
       <c r="K1653" t="n">
-        <v>106.59</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1654">
@@ -74205,13 +74487,13 @@
         </is>
       </c>
       <c r="I1662" t="n">
-        <v>86.36</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="J1662" t="n">
         <v>97.45999999999999</v>
       </c>
       <c r="K1662" t="n">
-        <v>88.62</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1663">
@@ -74609,12 +74891,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1671" t="inlineStr"/>
+      <c r="I1671" t="n">
+        <v>187.96</v>
+      </c>
       <c r="J1671" t="n">
-        <v>187.59</v>
+        <v>187.75</v>
       </c>
       <c r="K1671" t="n">
-        <v>0</v>
+        <v>100.11</v>
       </c>
     </row>
     <row r="1672">
@@ -74917,10 +75201,10 @@
         </is>
       </c>
       <c r="I1678" t="n">
-        <v>169.5</v>
+        <v>160.79</v>
       </c>
       <c r="J1678" t="n">
-        <v>169.5</v>
+        <v>160.79</v>
       </c>
       <c r="K1678" t="n">
         <v>100</v>
@@ -74965,10 +75249,10 @@
         <v>291.34</v>
       </c>
       <c r="J1679" t="n">
-        <v>291.22</v>
+        <v>291.34</v>
       </c>
       <c r="K1679" t="n">
-        <v>100.04</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1680">
@@ -75852,10 +76136,10 @@
         </is>
       </c>
       <c r="I1699" t="n">
-        <v>725.55</v>
+        <v>778.36</v>
       </c>
       <c r="J1699" t="n">
-        <v>725.55</v>
+        <v>778.36</v>
       </c>
       <c r="K1699" t="n">
         <v>100</v>
@@ -75942,10 +76226,10 @@
         </is>
       </c>
       <c r="I1701" t="n">
-        <v>547.74</v>
+        <v>591.59</v>
       </c>
       <c r="J1701" t="n">
-        <v>547.74</v>
+        <v>591.59</v>
       </c>
       <c r="K1701" t="n">
         <v>100</v>

--- a/ReportforHeaderU/ReportforHeaderU.xlsx
+++ b/ReportforHeaderU/ReportforHeaderU.xlsx
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>25.84</v>
+        <v>25.73</v>
       </c>
       <c r="J4" t="n">
         <v>26.5</v>
       </c>
       <c r="K4" t="n">
-        <v>97.48999999999999</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="5">
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>50.45</v>
+        <v>50.6</v>
       </c>
       <c r="J8" t="n">
         <v>50.66</v>
       </c>
       <c r="K8" t="n">
-        <v>99.59</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="9">
@@ -2996,13 +2996,13 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>26.26</v>
+        <v>26.28</v>
       </c>
       <c r="J57" t="n">
         <v>26.11</v>
       </c>
       <c r="K57" t="n">
-        <v>100.56</v>
+        <v>100.65</v>
       </c>
     </row>
     <row r="58">
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>27.91</v>
+        <v>27.95</v>
       </c>
       <c r="J161" t="n">
-        <v>28.86</v>
+        <v>28.9</v>
       </c>
       <c r="K161" t="n">
         <v>96.69</v>
@@ -10409,13 +10409,13 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>282.36</v>
+        <v>289.01</v>
       </c>
       <c r="J222" t="n">
         <v>282.51</v>
       </c>
       <c r="K222" t="n">
-        <v>99.95</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="223">
@@ -11843,13 +11843,13 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>127.56</v>
+        <v>128.22</v>
       </c>
       <c r="J254" t="n">
         <v>127.56</v>
       </c>
       <c r="K254" t="n">
-        <v>100</v>
+        <v>100.52</v>
       </c>
     </row>
     <row r="255">
@@ -11888,13 +11888,13 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>214.92</v>
+        <v>210.71</v>
       </c>
       <c r="J255" t="n">
         <v>213.66</v>
       </c>
       <c r="K255" t="n">
-        <v>100.59</v>
+        <v>98.62</v>
       </c>
     </row>
     <row r="256">
@@ -13283,13 +13283,13 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>6410.39</v>
+        <v>6465.76</v>
       </c>
       <c r="J286" t="n">
         <v>6417.33</v>
       </c>
       <c r="K286" t="n">
-        <v>99.89</v>
+        <v>100.75</v>
       </c>
     </row>
     <row r="287">
@@ -13508,13 +13508,13 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>14308.12</v>
+        <v>14386.09</v>
       </c>
       <c r="J291" t="n">
         <v>14381.01</v>
       </c>
       <c r="K291" t="n">
-        <v>99.48999999999999</v>
+        <v>100.04</v>
       </c>
     </row>
     <row r="292">
@@ -13598,13 +13598,13 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>7467.46</v>
+        <v>7438.55</v>
       </c>
       <c r="J293" t="n">
         <v>7426.35</v>
       </c>
       <c r="K293" t="n">
-        <v>100.55</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="294">
@@ -17333,13 +17333,13 @@
         </is>
       </c>
       <c r="I376" t="n">
-        <v>94.20999999999999</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="J376" t="n">
-        <v>94.31</v>
+        <v>95.77</v>
       </c>
       <c r="K376" t="n">
-        <v>99.89</v>
+        <v>99.79000000000001</v>
       </c>
     </row>
     <row r="377">
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="I460" t="n">
-        <v>29.38</v>
+        <v>29.24</v>
       </c>
       <c r="J460" t="n">
         <v>29.77</v>
       </c>
       <c r="K460" t="n">
-        <v>98.7</v>
+        <v>98.23</v>
       </c>
     </row>
     <row r="461">
@@ -26540,13 +26540,13 @@
         </is>
       </c>
       <c r="I581" t="n">
-        <v>83.33</v>
+        <v>83.17</v>
       </c>
       <c r="J581" t="n">
         <v>83.06</v>
       </c>
       <c r="K581" t="n">
-        <v>100.32</v>
+        <v>100.13</v>
       </c>
     </row>
     <row r="582">
@@ -33650,13 +33650,13 @@
         </is>
       </c>
       <c r="I739" t="n">
-        <v>6397.73</v>
+        <v>6310.25</v>
       </c>
       <c r="J739" t="n">
         <v>6456.02</v>
       </c>
       <c r="K739" t="n">
-        <v>99.09999999999999</v>
+        <v>97.73999999999999</v>
       </c>
     </row>
     <row r="740">
@@ -33965,13 +33965,13 @@
         </is>
       </c>
       <c r="I746" t="n">
-        <v>7880.89</v>
+        <v>7944.65</v>
       </c>
       <c r="J746" t="n">
         <v>8132.47</v>
       </c>
       <c r="K746" t="n">
-        <v>96.91</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="747">
@@ -43727,10 +43727,10 @@
         <v>4.19</v>
       </c>
       <c r="J963" t="n">
-        <v>5.33</v>
+        <v>5.16</v>
       </c>
       <c r="K963" t="n">
-        <v>78.58</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="964">
@@ -44038,9 +44038,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I970" t="inlineStr"/>
-      <c r="J970" t="inlineStr"/>
-      <c r="K970" t="inlineStr"/>
+      <c r="I970" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="J970" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="K970" t="n">
+        <v>107.25</v>
+      </c>
     </row>
     <row r="971">
       <c r="A971" t="n">
@@ -44600,13 +44606,13 @@
         </is>
       </c>
       <c r="I983" t="n">
-        <v>29.51</v>
+        <v>29.18</v>
       </c>
       <c r="J983" t="n">
         <v>32.72</v>
       </c>
       <c r="K983" t="n">
-        <v>90.19</v>
+        <v>89.18000000000001</v>
       </c>
     </row>
     <row r="984">
@@ -52610,10 +52616,10 @@
         </is>
       </c>
       <c r="I1161" t="n">
-        <v>223.3</v>
+        <v>224.94</v>
       </c>
       <c r="J1161" t="n">
-        <v>223.3</v>
+        <v>224.94</v>
       </c>
       <c r="K1161" t="n">
         <v>100</v>
@@ -53015,13 +53021,13 @@
         </is>
       </c>
       <c r="I1170" t="n">
-        <v>6564.04</v>
+        <v>6717.04</v>
       </c>
       <c r="J1170" t="n">
         <v>6564.04</v>
       </c>
       <c r="K1170" t="n">
-        <v>100</v>
+        <v>102.33</v>
       </c>
     </row>
     <row r="1171">
@@ -53285,13 +53291,13 @@
         </is>
       </c>
       <c r="I1176" t="n">
-        <v>7069.22</v>
+        <v>7047.24</v>
       </c>
       <c r="J1176" t="n">
         <v>7069.22</v>
       </c>
       <c r="K1176" t="n">
-        <v>100</v>
+        <v>99.69</v>
       </c>
     </row>
     <row r="1177">
@@ -55625,13 +55631,13 @@
         </is>
       </c>
       <c r="I1228" t="n">
-        <v>66.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="J1228" t="n">
         <v>67.92</v>
       </c>
       <c r="K1228" t="n">
-        <v>98.48999999999999</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="1229">
@@ -59978,13 +59984,13 @@
         </is>
       </c>
       <c r="I1325" t="n">
-        <v>33.46</v>
+        <v>33.4</v>
       </c>
       <c r="J1325" t="n">
         <v>33.46</v>
       </c>
       <c r="K1325" t="n">
-        <v>100</v>
+        <v>99.81999999999999</v>
       </c>
     </row>
     <row r="1326">
@@ -60023,13 +60029,13 @@
         </is>
       </c>
       <c r="I1326" t="n">
-        <v>54.77</v>
+        <v>54.74</v>
       </c>
       <c r="J1326" t="n">
         <v>55.14</v>
       </c>
       <c r="K1326" t="n">
-        <v>99.33</v>
+        <v>99.28</v>
       </c>
     </row>
     <row r="1327">
@@ -64325,13 +64331,13 @@
         </is>
       </c>
       <c r="I1422" t="n">
-        <v>60.01</v>
+        <v>59.78</v>
       </c>
       <c r="J1422" t="n">
         <v>57</v>
       </c>
       <c r="K1422" t="n">
-        <v>105.28</v>
+        <v>104.89</v>
       </c>
     </row>
     <row r="1423">
@@ -72470,13 +72476,13 @@
         </is>
       </c>
       <c r="I1603" t="n">
-        <v>5799.75</v>
+        <v>5795.06</v>
       </c>
       <c r="J1603" t="n">
         <v>5683.32</v>
       </c>
       <c r="K1603" t="n">
-        <v>102.05</v>
+        <v>101.97</v>
       </c>
     </row>
     <row r="1604">
@@ -72785,13 +72791,13 @@
         </is>
       </c>
       <c r="I1610" t="n">
-        <v>6302.04</v>
+        <v>6236.82</v>
       </c>
       <c r="J1610" t="n">
         <v>6305.68</v>
       </c>
       <c r="K1610" t="n">
-        <v>99.94</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="1611">
@@ -73010,13 +73016,13 @@
         </is>
       </c>
       <c r="I1615" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="J1615" t="n">
         <v>21.61</v>
       </c>
       <c r="K1615" t="n">
-        <v>102.75</v>
+        <v>103.21</v>
       </c>
     </row>
     <row r="1616">
@@ -78995,13 +79001,13 @@
         </is>
       </c>
       <c r="I1748" t="n">
-        <v>922.95</v>
+        <v>921.58</v>
       </c>
       <c r="J1748" t="n">
         <v>922.95</v>
       </c>
       <c r="K1748" t="n">
-        <v>100</v>
+        <v>99.84999999999999</v>
       </c>
     </row>
     <row r="1749">
@@ -79040,13 +79046,13 @@
         </is>
       </c>
       <c r="I1749" t="n">
-        <v>116.03</v>
+        <v>119.72</v>
       </c>
       <c r="J1749" t="n">
         <v>116.03</v>
       </c>
       <c r="K1749" t="n">
-        <v>100</v>
+        <v>103.18</v>
       </c>
     </row>
     <row r="1750">

--- a/ReportforHeaderU/ReportforHeaderU.xlsx
+++ b/ReportforHeaderU/ReportforHeaderU.xlsx
@@ -565,9 +565,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>324.71</v>
+      </c>
+      <c r="J3" t="n">
+        <v>322.24</v>
+      </c>
+      <c r="K3" t="n">
+        <v>100.77</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -650,13 +656,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>27.48</v>
+        <v>27.62</v>
       </c>
       <c r="J5" t="n">
-        <v>27.65</v>
+        <v>27.63</v>
       </c>
       <c r="K5" t="n">
-        <v>99.39</v>
+        <v>99.95999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1238,10 +1244,10 @@
         <v>153.2</v>
       </c>
       <c r="J18" t="n">
-        <v>152.61</v>
+        <v>153.47</v>
       </c>
       <c r="K18" t="n">
-        <v>100.39</v>
+        <v>99.81999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1283,10 +1289,10 @@
         <v>76.95</v>
       </c>
       <c r="J19" t="n">
-        <v>77.56</v>
+        <v>76.58</v>
       </c>
       <c r="K19" t="n">
-        <v>99.20999999999999</v>
+        <v>100.48</v>
       </c>
     </row>
     <row r="20">
@@ -1370,11 +1376,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>24.71</v>
+      </c>
+      <c r="J21" t="n">
+        <v>24.83</v>
+      </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1412,9 +1420,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="J22" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>100.7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2352,10 +2366,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>238.45</v>
+        <v>219.64</v>
       </c>
       <c r="J43" t="n">
-        <v>238.45</v>
+        <v>219.64</v>
       </c>
       <c r="K43" t="n">
         <v>100</v>
@@ -2442,10 +2456,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>108.95</v>
+        <v>105.49</v>
       </c>
       <c r="J45" t="n">
-        <v>108.95</v>
+        <v>105.49</v>
       </c>
       <c r="K45" t="n">
         <v>100</v>
@@ -2531,9 +2545,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>105.77</v>
+      </c>
+      <c r="J47" t="n">
+        <v>105.77</v>
+      </c>
+      <c r="K47" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2571,13 +2591,13 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>473.94</v>
+        <v>481.1</v>
       </c>
       <c r="J48" t="n">
         <v>481.1</v>
       </c>
       <c r="K48" t="n">
-        <v>98.51000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
@@ -3021,13 +3041,13 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>251.86</v>
+        <v>250.23</v>
       </c>
       <c r="J58" t="n">
         <v>251.52</v>
       </c>
       <c r="K58" t="n">
-        <v>100.14</v>
+        <v>99.48999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4223,9 +4243,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>107.27</v>
+      </c>
+      <c r="J85" t="n">
+        <v>110.68</v>
+      </c>
+      <c r="K85" t="n">
+        <v>96.93000000000001</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4353,13 +4379,13 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>53.59</v>
+        <v>53.54</v>
       </c>
       <c r="J88" t="n">
-        <v>58.09</v>
+        <v>57.69</v>
       </c>
       <c r="K88" t="n">
-        <v>92.25</v>
+        <v>92.79000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -4487,9 +4513,15 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>143.43</v>
+      </c>
+      <c r="J91" t="n">
+        <v>150.53</v>
+      </c>
+      <c r="K91" t="n">
+        <v>95.28</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6145,13 +6177,13 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>50.82</v>
+        <v>50.85</v>
       </c>
       <c r="J128" t="n">
         <v>50.39</v>
       </c>
       <c r="K128" t="n">
-        <v>100.85</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="129">
@@ -6279,12 +6311,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="n">
+        <v>9.890000000000001</v>
+      </c>
       <c r="J131" t="n">
         <v>10.23</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>96.65000000000001</v>
       </c>
     </row>
     <row r="132">
@@ -6323,13 +6357,13 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>25.89</v>
+        <v>25.6</v>
       </c>
       <c r="J132" t="n">
-        <v>25.9</v>
+        <v>25.55</v>
       </c>
       <c r="K132" t="n">
-        <v>99.94</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="133">
@@ -6371,10 +6405,10 @@
         <v>40.88</v>
       </c>
       <c r="J133" t="n">
-        <v>42.66</v>
+        <v>42.22</v>
       </c>
       <c r="K133" t="n">
-        <v>95.83</v>
+        <v>96.81</v>
       </c>
     </row>
     <row r="134">
@@ -6457,12 +6491,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="n">
+        <v>23.56</v>
+      </c>
       <c r="J135" t="n">
-        <v>24.72</v>
+        <v>24.59</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>95.81999999999999</v>
       </c>
     </row>
     <row r="136">
@@ -6500,12 +6536,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="n">
+        <v>26.78</v>
+      </c>
       <c r="J136" t="n">
         <v>27.45</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>97.56999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -6543,12 +6581,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="n">
+        <v>42.9</v>
+      </c>
       <c r="J137" t="n">
-        <v>43.44</v>
+        <v>42.51</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>100.92</v>
       </c>
     </row>
     <row r="138">
@@ -6677,10 +6717,10 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>13.8</v>
+        <v>14.16</v>
       </c>
       <c r="J140" t="n">
-        <v>13.8</v>
+        <v>14.16</v>
       </c>
       <c r="K140" t="n">
         <v>100</v>
@@ -6815,10 +6855,10 @@
         <v>79.45</v>
       </c>
       <c r="J143" t="n">
-        <v>80.58</v>
+        <v>78.73</v>
       </c>
       <c r="K143" t="n">
-        <v>98.59999999999999</v>
+        <v>100.91</v>
       </c>
     </row>
     <row r="144">
@@ -6856,12 +6896,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="n">
+        <v>135.42</v>
+      </c>
       <c r="J144" t="n">
-        <v>131.94</v>
+        <v>132.54</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>102.18</v>
       </c>
     </row>
     <row r="145">
@@ -6945,13 +6987,13 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>22.76</v>
+        <v>22.85</v>
       </c>
       <c r="J146" t="n">
         <v>22.72</v>
       </c>
       <c r="K146" t="n">
-        <v>100.2</v>
+        <v>100.59</v>
       </c>
     </row>
     <row r="147">
@@ -6990,13 +7032,13 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>53.31</v>
+        <v>53.67</v>
       </c>
       <c r="J147" t="n">
-        <v>52.52</v>
+        <v>52.91</v>
       </c>
       <c r="K147" t="n">
-        <v>101.5</v>
+        <v>101.44</v>
       </c>
     </row>
     <row r="148">
@@ -7035,13 +7077,13 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>64.45</v>
+        <v>63.95</v>
       </c>
       <c r="J148" t="n">
-        <v>63.86</v>
+        <v>63.4</v>
       </c>
       <c r="K148" t="n">
-        <v>100.92</v>
+        <v>100.86</v>
       </c>
     </row>
     <row r="149">
@@ -7080,13 +7122,13 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>15.92</v>
+        <v>16.65</v>
       </c>
       <c r="J149" t="n">
-        <v>15.86</v>
+        <v>16.6</v>
       </c>
       <c r="K149" t="n">
-        <v>100.35</v>
+        <v>100.33</v>
       </c>
     </row>
     <row r="150">
@@ -7214,12 +7256,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
+      <c r="I152" t="n">
+        <v>11.77</v>
+      </c>
       <c r="J152" t="n">
         <v>11.81</v>
       </c>
       <c r="K152" t="n">
-        <v>0</v>
+        <v>99.67</v>
       </c>
     </row>
     <row r="153">
@@ -7257,12 +7301,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="n">
+        <v>16.87</v>
+      </c>
       <c r="J153" t="n">
         <v>16.87</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="154">
@@ -7301,10 +7347,10 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>21</v>
+        <v>21.19</v>
       </c>
       <c r="J154" t="n">
-        <v>21</v>
+        <v>21.19</v>
       </c>
       <c r="K154" t="n">
         <v>100</v>
@@ -7345,12 +7391,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="n">
+        <v>416.18</v>
+      </c>
       <c r="J155" t="n">
-        <v>427.32</v>
+        <v>428.12</v>
       </c>
       <c r="K155" t="n">
-        <v>0</v>
+        <v>97.20999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -7433,12 +7481,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="n">
+        <v>18.68</v>
+      </c>
       <c r="J157" t="n">
         <v>18.65</v>
       </c>
       <c r="K157" t="n">
-        <v>0</v>
+        <v>100.15</v>
       </c>
     </row>
     <row r="158">
@@ -8242,13 +8292,13 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>47.09</v>
+        <v>46.68</v>
       </c>
       <c r="J175" t="n">
-        <v>46.24</v>
+        <v>45.98</v>
       </c>
       <c r="K175" t="n">
-        <v>101.84</v>
+        <v>101.53</v>
       </c>
     </row>
     <row r="176">
@@ -8286,12 +8336,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
+      <c r="I176" t="n">
+        <v>176.15</v>
+      </c>
       <c r="J176" t="n">
         <v>176.96</v>
       </c>
       <c r="K176" t="n">
-        <v>0</v>
+        <v>99.54000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -8375,13 +8427,13 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>47.79</v>
+        <v>48.29</v>
       </c>
       <c r="J178" t="n">
         <v>48.33</v>
       </c>
       <c r="K178" t="n">
-        <v>98.89</v>
+        <v>99.91</v>
       </c>
     </row>
     <row r="179">
@@ -9050,13 +9102,13 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>63.98</v>
+        <v>63.72</v>
       </c>
       <c r="J193" t="n">
         <v>63.72</v>
       </c>
       <c r="K193" t="n">
-        <v>100.41</v>
+        <v>100</v>
       </c>
     </row>
     <row r="194">
@@ -12689,10 +12741,10 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>146.62</v>
+        <v>146.12</v>
       </c>
       <c r="J274" t="n">
-        <v>146.67</v>
+        <v>146.17</v>
       </c>
       <c r="K274" t="n">
         <v>99.95999999999999</v>
@@ -12869,13 +12921,13 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>304.07</v>
+        <v>310.53</v>
       </c>
       <c r="J278" t="n">
-        <v>305.61</v>
+        <v>310.53</v>
       </c>
       <c r="K278" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="279">
@@ -12913,12 +12965,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="n">
+        <v>101.39</v>
+      </c>
       <c r="J279" t="n">
         <v>100.87</v>
       </c>
       <c r="K279" t="n">
-        <v>0</v>
+        <v>100.51</v>
       </c>
     </row>
     <row r="280">
@@ -13226,12 +13280,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
+      <c r="I286" t="n">
+        <v>6431.31</v>
+      </c>
       <c r="J286" t="n">
-        <v>6465.76</v>
+        <v>6391.41</v>
       </c>
       <c r="K286" t="n">
-        <v>0</v>
+        <v>100.62</v>
       </c>
     </row>
     <row r="287">
@@ -13315,13 +13371,13 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>644.52</v>
+        <v>644.59</v>
       </c>
       <c r="J288" t="n">
         <v>644.2</v>
       </c>
       <c r="K288" t="n">
-        <v>100.05</v>
+        <v>100.06</v>
       </c>
     </row>
     <row r="289">
@@ -13359,12 +13415,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
+      <c r="I289" t="n">
+        <v>840.33</v>
+      </c>
       <c r="J289" t="n">
         <v>841.23</v>
       </c>
       <c r="K289" t="n">
-        <v>0</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="290">
@@ -13406,10 +13464,10 @@
         <v>2051.92</v>
       </c>
       <c r="J290" t="n">
-        <v>2197.5</v>
+        <v>2145.64</v>
       </c>
       <c r="K290" t="n">
-        <v>93.38</v>
+        <v>95.63</v>
       </c>
     </row>
     <row r="291">
@@ -13447,12 +13505,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
+      <c r="I291" t="n">
+        <v>14438.88</v>
+      </c>
       <c r="J291" t="n">
         <v>14386.09</v>
       </c>
       <c r="K291" t="n">
-        <v>0</v>
+        <v>100.37</v>
       </c>
     </row>
     <row r="292">
@@ -13494,10 +13554,10 @@
         <v>2061.97</v>
       </c>
       <c r="J292" t="n">
-        <v>2223.45</v>
+        <v>2150.92</v>
       </c>
       <c r="K292" t="n">
-        <v>92.73999999999999</v>
+        <v>95.86</v>
       </c>
     </row>
     <row r="293">
@@ -13535,12 +13595,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
+      <c r="I293" t="n">
+        <v>7491.6</v>
+      </c>
       <c r="J293" t="n">
         <v>7438.55</v>
       </c>
       <c r="K293" t="n">
-        <v>0</v>
+        <v>100.71</v>
       </c>
     </row>
     <row r="294">
@@ -13578,12 +13640,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
+      <c r="I294" t="n">
+        <v>802.14</v>
+      </c>
       <c r="J294" t="n">
-        <v>802.54</v>
+        <v>804.89</v>
       </c>
       <c r="K294" t="n">
-        <v>0</v>
+        <v>99.66</v>
       </c>
     </row>
     <row r="295">
@@ -13621,12 +13685,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr"/>
+      <c r="I295" t="n">
+        <v>65.53</v>
+      </c>
       <c r="J295" t="n">
-        <v>62.45</v>
+        <v>61.95</v>
       </c>
       <c r="K295" t="n">
-        <v>0</v>
+        <v>105.77</v>
       </c>
     </row>
     <row r="296">
@@ -14205,13 +14271,13 @@
         </is>
       </c>
       <c r="I308" t="n">
-        <v>25.94</v>
+        <v>26.22</v>
       </c>
       <c r="J308" t="n">
         <v>24.77</v>
       </c>
       <c r="K308" t="n">
-        <v>104.73</v>
+        <v>105.85</v>
       </c>
     </row>
     <row r="309">
@@ -16365,13 +16431,13 @@
         </is>
       </c>
       <c r="I356" t="n">
-        <v>26.6</v>
+        <v>27.12</v>
       </c>
       <c r="J356" t="n">
-        <v>26.68</v>
+        <v>26.83</v>
       </c>
       <c r="K356" t="n">
-        <v>99.72</v>
+        <v>101.08</v>
       </c>
     </row>
     <row r="357">
@@ -16409,12 +16475,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I357" t="inlineStr"/>
+      <c r="I357" t="n">
+        <v>88.13</v>
+      </c>
       <c r="J357" t="n">
-        <v>90</v>
+        <v>88.73</v>
       </c>
       <c r="K357" t="n">
-        <v>0</v>
+        <v>99.31999999999999</v>
       </c>
     </row>
     <row r="358">
@@ -16538,12 +16606,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I360" t="inlineStr"/>
+      <c r="I360" t="n">
+        <v>76.31</v>
+      </c>
       <c r="J360" t="n">
-        <v>75.51000000000001</v>
+        <v>75.37</v>
       </c>
       <c r="K360" t="n">
-        <v>0</v>
+        <v>101.25</v>
       </c>
     </row>
     <row r="361">
@@ -16627,13 +16697,13 @@
         </is>
       </c>
       <c r="I362" t="n">
-        <v>41.68</v>
+        <v>42.23</v>
       </c>
       <c r="J362" t="n">
-        <v>41.44</v>
+        <v>41.99</v>
       </c>
       <c r="K362" t="n">
-        <v>100.59</v>
+        <v>100.58</v>
       </c>
     </row>
     <row r="363">
@@ -16672,10 +16742,10 @@
         </is>
       </c>
       <c r="I363" t="n">
-        <v>31.5</v>
+        <v>42</v>
       </c>
       <c r="J363" t="n">
-        <v>31.5</v>
+        <v>42</v>
       </c>
       <c r="K363" t="n">
         <v>100</v>
@@ -17032,13 +17102,13 @@
         </is>
       </c>
       <c r="I371" t="n">
-        <v>145.46</v>
+        <v>142.73</v>
       </c>
       <c r="J371" t="n">
-        <v>123.74</v>
+        <v>122.19</v>
       </c>
       <c r="K371" t="n">
-        <v>117.55</v>
+        <v>116.82</v>
       </c>
     </row>
     <row r="372">
@@ -17924,10 +17994,10 @@
         </is>
       </c>
       <c r="I391" t="n">
-        <v>60.16</v>
+        <v>60.92</v>
       </c>
       <c r="J391" t="n">
-        <v>60.16</v>
+        <v>60.92</v>
       </c>
       <c r="K391" t="n">
         <v>100</v>
@@ -17969,13 +18039,13 @@
         </is>
       </c>
       <c r="I392" t="n">
-        <v>973.83</v>
+        <v>1016.48</v>
       </c>
       <c r="J392" t="n">
-        <v>959.15</v>
+        <v>1002.32</v>
       </c>
       <c r="K392" t="n">
-        <v>101.53</v>
+        <v>101.41</v>
       </c>
     </row>
     <row r="393">
@@ -18418,12 +18488,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr"/>
+      <c r="I402" t="n">
+        <v>2351.71</v>
+      </c>
       <c r="J402" t="n">
-        <v>2425.76</v>
+        <v>2351.71</v>
       </c>
       <c r="K402" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="403">
@@ -19317,13 +19389,13 @@
         </is>
       </c>
       <c r="I422" t="n">
-        <v>9335.799999999999</v>
+        <v>9571.49</v>
       </c>
       <c r="J422" t="n">
-        <v>9298.1</v>
+        <v>9379.52</v>
       </c>
       <c r="K422" t="n">
-        <v>100.41</v>
+        <v>102.05</v>
       </c>
     </row>
     <row r="423">
@@ -19361,12 +19433,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I423" t="inlineStr"/>
+      <c r="I423" t="n">
+        <v>1163.56</v>
+      </c>
       <c r="J423" t="n">
         <v>1138.24</v>
       </c>
       <c r="K423" t="n">
-        <v>0</v>
+        <v>102.22</v>
       </c>
     </row>
     <row r="424">
@@ -19405,10 +19479,10 @@
         </is>
       </c>
       <c r="I424" t="n">
-        <v>366.27</v>
+        <v>356.96</v>
       </c>
       <c r="J424" t="n">
-        <v>366.27</v>
+        <v>356.96</v>
       </c>
       <c r="K424" t="n">
         <v>100</v>
@@ -19449,12 +19523,14 @@
           <t>กลาง</t>
         </is>
       </c>
-      <c r="I425" t="inlineStr"/>
+      <c r="I425" t="n">
+        <v>4956.33</v>
+      </c>
       <c r="J425" t="n">
         <v>4823.27</v>
       </c>
       <c r="K425" t="n">
-        <v>0</v>
+        <v>102.76</v>
       </c>
     </row>
     <row r="426">
@@ -20078,10 +20154,10 @@
         </is>
       </c>
       <c r="I439" t="n">
-        <v>1581.14</v>
+        <v>1158.29</v>
       </c>
       <c r="J439" t="n">
-        <v>1581.14</v>
+        <v>1158.29</v>
       </c>
       <c r="K439" t="n">
         <v>100</v>
@@ -21110,9 +21186,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I462" t="inlineStr"/>
-      <c r="J462" t="inlineStr"/>
-      <c r="K462" t="inlineStr"/>
+      <c r="I462" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="J462" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="K462" t="n">
+        <v>99.66</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -21644,9 +21726,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I474" t="inlineStr"/>
-      <c r="J474" t="inlineStr"/>
-      <c r="K474" t="inlineStr"/>
+      <c r="I474" t="n">
+        <v>112.73</v>
+      </c>
+      <c r="J474" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="K474" t="n">
+        <v>99.63</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -21819,13 +21907,13 @@
         </is>
       </c>
       <c r="I478" t="n">
-        <v>49.76</v>
+        <v>51.66</v>
       </c>
       <c r="J478" t="n">
-        <v>49.42</v>
+        <v>51.35</v>
       </c>
       <c r="K478" t="n">
-        <v>100.69</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="479">
@@ -21864,13 +21952,13 @@
         </is>
       </c>
       <c r="I479" t="n">
-        <v>26.2</v>
+        <v>25.42</v>
       </c>
       <c r="J479" t="n">
-        <v>26.35</v>
+        <v>25.49</v>
       </c>
       <c r="K479" t="n">
-        <v>99.42</v>
+        <v>99.75</v>
       </c>
     </row>
     <row r="480">
@@ -21909,13 +21997,13 @@
         </is>
       </c>
       <c r="I480" t="n">
-        <v>95.47</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="J480" t="n">
         <v>96.97</v>
       </c>
       <c r="K480" t="n">
-        <v>98.45</v>
+        <v>98.38</v>
       </c>
     </row>
     <row r="481">
@@ -22358,9 +22446,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I490" t="inlineStr"/>
-      <c r="J490" t="inlineStr"/>
-      <c r="K490" t="inlineStr"/>
+      <c r="I490" t="n">
+        <v>287.07</v>
+      </c>
+      <c r="J490" t="n">
+        <v>288.38</v>
+      </c>
+      <c r="K490" t="n">
+        <v>99.55</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -22442,9 +22536,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I492" t="inlineStr"/>
-      <c r="J492" t="inlineStr"/>
-      <c r="K492" t="inlineStr"/>
+      <c r="I492" t="n">
+        <v>223.64</v>
+      </c>
+      <c r="J492" t="n">
+        <v>223.64</v>
+      </c>
+      <c r="K492" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -22481,9 +22581,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I493" t="inlineStr"/>
-      <c r="J493" t="inlineStr"/>
-      <c r="K493" t="inlineStr"/>
+      <c r="I493" t="n">
+        <v>195.08</v>
+      </c>
+      <c r="J493" t="n">
+        <v>196.26</v>
+      </c>
+      <c r="K493" t="n">
+        <v>99.40000000000001</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -22655,9 +22761,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I497" t="inlineStr"/>
-      <c r="J497" t="inlineStr"/>
-      <c r="K497" t="inlineStr"/>
+      <c r="I497" t="n">
+        <v>136.28</v>
+      </c>
+      <c r="J497" t="n">
+        <v>135.94</v>
+      </c>
+      <c r="K497" t="n">
+        <v>100.25</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -23460,13 +23572,13 @@
         </is>
       </c>
       <c r="I515" t="n">
-        <v>254.98</v>
+        <v>255.52</v>
       </c>
       <c r="J515" t="n">
         <v>255.35</v>
       </c>
       <c r="K515" t="n">
-        <v>99.86</v>
+        <v>100.07</v>
       </c>
     </row>
     <row r="516">
@@ -24701,9 +24813,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I543" t="inlineStr"/>
-      <c r="J543" t="inlineStr"/>
-      <c r="K543" t="inlineStr"/>
+      <c r="I543" t="n">
+        <v>52.47</v>
+      </c>
+      <c r="J543" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="K543" t="n">
+        <v>102.7</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -25506,13 +25624,13 @@
         </is>
       </c>
       <c r="I561" t="n">
-        <v>43.81</v>
+        <v>43.85</v>
       </c>
       <c r="J561" t="n">
         <v>44.73</v>
       </c>
       <c r="K561" t="n">
-        <v>97.94</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="562">
@@ -26406,10 +26524,10 @@
         </is>
       </c>
       <c r="I581" t="n">
-        <v>90.45999999999999</v>
+        <v>88.16</v>
       </c>
       <c r="J581" t="n">
-        <v>91.01000000000001</v>
+        <v>88.69</v>
       </c>
       <c r="K581" t="n">
         <v>99.40000000000001</v>
@@ -26628,9 +26746,15 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I586" t="inlineStr"/>
-      <c r="J586" t="inlineStr"/>
-      <c r="K586" t="inlineStr"/>
+      <c r="I586" t="n">
+        <v>60.26</v>
+      </c>
+      <c r="J586" t="n">
+        <v>60.26</v>
+      </c>
+      <c r="K586" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -27253,13 +27377,13 @@
         </is>
       </c>
       <c r="I600" t="n">
-        <v>148.94</v>
+        <v>149.45</v>
       </c>
       <c r="J600" t="n">
         <v>149.16</v>
       </c>
       <c r="K600" t="n">
-        <v>99.84999999999999</v>
+        <v>100.19</v>
       </c>
     </row>
     <row r="601">
@@ -27343,13 +27467,13 @@
         </is>
       </c>
       <c r="I602" t="n">
-        <v>22.58</v>
+        <v>22.6</v>
       </c>
       <c r="J602" t="n">
         <v>22.53</v>
       </c>
       <c r="K602" t="n">
-        <v>100.21</v>
+        <v>100.29</v>
       </c>
     </row>
     <row r="603">
@@ -27388,13 +27512,13 @@
         </is>
       </c>
       <c r="I603" t="n">
-        <v>37.58</v>
+        <v>38.82</v>
       </c>
       <c r="J603" t="n">
-        <v>36.42</v>
+        <v>37.86</v>
       </c>
       <c r="K603" t="n">
-        <v>103.17</v>
+        <v>102.52</v>
       </c>
     </row>
     <row r="604">
@@ -27478,13 +27602,13 @@
         </is>
       </c>
       <c r="I605" t="n">
-        <v>12.01</v>
+        <v>13.1</v>
       </c>
       <c r="J605" t="n">
-        <v>10.1</v>
+        <v>13.1</v>
       </c>
       <c r="K605" t="n">
-        <v>118.91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="606">
@@ -27522,12 +27646,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I606" t="inlineStr"/>
+      <c r="I606" t="n">
+        <v>8.119999999999999</v>
+      </c>
       <c r="J606" t="n">
         <v>8.119999999999999</v>
       </c>
       <c r="K606" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="607">
@@ -27565,12 +27691,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I607" t="inlineStr"/>
+      <c r="I607" t="n">
+        <v>32.78</v>
+      </c>
       <c r="J607" t="n">
-        <v>31.15</v>
+        <v>32.78</v>
       </c>
       <c r="K607" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="608">
@@ -27743,12 +27871,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I611" t="inlineStr"/>
+      <c r="I611" t="n">
+        <v>385.63</v>
+      </c>
       <c r="J611" t="n">
         <v>399.58</v>
       </c>
       <c r="K611" t="n">
-        <v>0</v>
+        <v>96.51000000000001</v>
       </c>
     </row>
     <row r="612">
@@ -28625,12 +28755,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I631" t="inlineStr"/>
+      <c r="I631" t="n">
+        <v>43.27</v>
+      </c>
       <c r="J631" t="n">
         <v>43.27</v>
       </c>
       <c r="K631" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="632">
@@ -28668,12 +28800,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I632" t="inlineStr"/>
+      <c r="I632" t="n">
+        <v>153.22</v>
+      </c>
       <c r="J632" t="n">
-        <v>153.38</v>
+        <v>153.22</v>
       </c>
       <c r="K632" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="633">
@@ -28711,12 +28845,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I633" t="inlineStr"/>
+      <c r="I633" t="n">
+        <v>18.62</v>
+      </c>
       <c r="J633" t="n">
         <v>18.64</v>
       </c>
       <c r="K633" t="n">
-        <v>0</v>
+        <v>99.88</v>
       </c>
     </row>
     <row r="634">
@@ -28754,12 +28890,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I634" t="inlineStr"/>
+      <c r="I634" t="n">
+        <v>47.53</v>
+      </c>
       <c r="J634" t="n">
         <v>47.51</v>
       </c>
       <c r="K634" t="n">
-        <v>0</v>
+        <v>100.05</v>
       </c>
     </row>
     <row r="635">
@@ -29063,12 +29201,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I641" t="inlineStr"/>
+      <c r="I641" t="n">
+        <v>111.18</v>
+      </c>
       <c r="J641" t="n">
-        <v>109.94</v>
+        <v>109.49</v>
       </c>
       <c r="K641" t="n">
-        <v>0</v>
+        <v>101.54</v>
       </c>
     </row>
     <row r="642">
@@ -29106,12 +29246,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I642" t="inlineStr"/>
+      <c r="I642" t="n">
+        <v>47.49</v>
+      </c>
       <c r="J642" t="n">
         <v>47.49</v>
       </c>
       <c r="K642" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="643">
@@ -29149,12 +29291,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I643" t="inlineStr"/>
+      <c r="I643" t="n">
+        <v>27.14</v>
+      </c>
       <c r="J643" t="n">
-        <v>26.22</v>
+        <v>27.14</v>
       </c>
       <c r="K643" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="644">
@@ -29328,10 +29472,10 @@
         </is>
       </c>
       <c r="I647" t="n">
-        <v>255.26</v>
+        <v>251.45</v>
       </c>
       <c r="J647" t="n">
-        <v>255.26</v>
+        <v>251.45</v>
       </c>
       <c r="K647" t="n">
         <v>100</v>
@@ -32664,7 +32808,7 @@
         <v>4.24</v>
       </c>
       <c r="K721" t="n">
-        <v>100.02</v>
+        <v>100</v>
       </c>
     </row>
     <row r="722">
@@ -33243,10 +33387,10 @@
         </is>
       </c>
       <c r="I734" t="n">
-        <v>208.93</v>
+        <v>193.74</v>
       </c>
       <c r="J734" t="n">
-        <v>208.93</v>
+        <v>193.74</v>
       </c>
       <c r="K734" t="n">
         <v>100</v>
@@ -33828,13 +33972,13 @@
         </is>
       </c>
       <c r="I747" t="n">
-        <v>7738.72</v>
+        <v>7883.65</v>
       </c>
       <c r="J747" t="n">
-        <v>7944.65</v>
+        <v>7797.65</v>
       </c>
       <c r="K747" t="n">
-        <v>97.41</v>
+        <v>101.1</v>
       </c>
     </row>
     <row r="748">
@@ -33872,12 +34016,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I748" t="inlineStr"/>
+      <c r="I748" t="n">
+        <v>894.75</v>
+      </c>
       <c r="J748" t="n">
         <v>891.42</v>
       </c>
       <c r="K748" t="n">
-        <v>0</v>
+        <v>100.37</v>
       </c>
     </row>
     <row r="749">
@@ -33916,13 +34062,13 @@
         </is>
       </c>
       <c r="I749" t="n">
-        <v>71.56</v>
+        <v>72.25</v>
       </c>
       <c r="J749" t="n">
         <v>69.94</v>
       </c>
       <c r="K749" t="n">
-        <v>102.32</v>
+        <v>103.31</v>
       </c>
     </row>
     <row r="750">
@@ -34456,13 +34602,13 @@
         </is>
       </c>
       <c r="I761" t="n">
-        <v>23.79</v>
+        <v>24.16</v>
       </c>
       <c r="J761" t="n">
-        <v>23.28</v>
+        <v>23.17</v>
       </c>
       <c r="K761" t="n">
-        <v>102.18</v>
+        <v>104.25</v>
       </c>
     </row>
     <row r="762">
@@ -36166,13 +36312,13 @@
         </is>
       </c>
       <c r="I799" t="n">
-        <v>97.95999999999999</v>
+        <v>97.33</v>
       </c>
       <c r="J799" t="n">
         <v>92.18000000000001</v>
       </c>
       <c r="K799" t="n">
-        <v>106.27</v>
+        <v>105.58</v>
       </c>
     </row>
     <row r="800">
@@ -36566,12 +36712,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I808" t="inlineStr"/>
+      <c r="I808" t="n">
+        <v>68.51000000000001</v>
+      </c>
       <c r="J808" t="n">
         <v>68.61</v>
       </c>
       <c r="K808" t="n">
-        <v>0</v>
+        <v>99.84999999999999</v>
       </c>
     </row>
     <row r="809">
@@ -37683,10 +37831,10 @@
         <v>29.79</v>
       </c>
       <c r="J833" t="n">
-        <v>31.72</v>
+        <v>31.18</v>
       </c>
       <c r="K833" t="n">
-        <v>93.91</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="834">
@@ -37814,12 +37962,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I836" t="inlineStr"/>
+      <c r="I836" t="n">
+        <v>1163.38</v>
+      </c>
       <c r="J836" t="n">
-        <v>967.14</v>
+        <v>1163.38</v>
       </c>
       <c r="K836" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="837">
@@ -37992,12 +38142,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I840" t="inlineStr"/>
+      <c r="I840" t="n">
+        <v>2453.92</v>
+      </c>
       <c r="J840" t="n">
         <v>2453.92</v>
       </c>
       <c r="K840" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="841">
@@ -38080,12 +38232,14 @@
           <t>ตะวันออกเฉียงเหนือ</t>
         </is>
       </c>
-      <c r="I842" t="inlineStr"/>
+      <c r="I842" t="n">
+        <v>2392.98</v>
+      </c>
       <c r="J842" t="n">
         <v>2371.69</v>
       </c>
       <c r="K842" t="n">
-        <v>0</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="843">
@@ -38889,13 +39043,13 @@
         </is>
       </c>
       <c r="I860" t="n">
-        <v>7834.89</v>
+        <v>7107.94</v>
       </c>
       <c r="J860" t="n">
-        <v>7831.06</v>
+        <v>6936.28</v>
       </c>
       <c r="K860" t="n">
-        <v>100.05</v>
+        <v>102.47</v>
       </c>
     </row>
     <row r="861">
@@ -40287,10 +40441,10 @@
         <v>63.36</v>
       </c>
       <c r="J891" t="n">
-        <v>63.51</v>
+        <v>63.45</v>
       </c>
       <c r="K891" t="n">
-        <v>99.77</v>
+        <v>99.86</v>
       </c>
     </row>
     <row r="892">
@@ -40458,13 +40612,13 @@
         </is>
       </c>
       <c r="I895" t="n">
-        <v>467.69</v>
+        <v>469.48</v>
       </c>
       <c r="J895" t="n">
-        <v>479.85</v>
+        <v>476.16</v>
       </c>
       <c r="K895" t="n">
-        <v>97.47</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="896">
@@ -40548,13 +40702,13 @@
         </is>
       </c>
       <c r="I897" t="n">
-        <v>36.38</v>
+        <v>36.87</v>
       </c>
       <c r="J897" t="n">
-        <v>36.08</v>
+        <v>36.57</v>
       </c>
       <c r="K897" t="n">
-        <v>100.82</v>
+        <v>100.81</v>
       </c>
     </row>
     <row r="898">
@@ -40592,9 +40746,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I898" t="inlineStr"/>
-      <c r="J898" t="inlineStr"/>
-      <c r="K898" t="inlineStr"/>
+      <c r="I898" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="J898" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="K898" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="n">
@@ -41037,11 +41197,13 @@
         </is>
       </c>
       <c r="I908" t="n">
-        <v>0</v>
-      </c>
-      <c r="J908" t="inlineStr"/>
+        <v>61.01</v>
+      </c>
+      <c r="J908" t="n">
+        <v>61.38</v>
+      </c>
       <c r="K908" t="n">
-        <v>0</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="909">
@@ -41125,13 +41287,13 @@
         </is>
       </c>
       <c r="I910" t="n">
-        <v>0</v>
+        <v>112.99</v>
       </c>
       <c r="J910" t="n">
-        <v>113.28</v>
+        <v>112.2</v>
       </c>
       <c r="K910" t="n">
-        <v>0</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="911">
@@ -41170,13 +41332,13 @@
         </is>
       </c>
       <c r="I911" t="n">
-        <v>59.14</v>
+        <v>59.37</v>
       </c>
       <c r="J911" t="n">
-        <v>59.14</v>
+        <v>59.02</v>
       </c>
       <c r="K911" t="n">
-        <v>100</v>
+        <v>100.59</v>
       </c>
     </row>
     <row r="912">
@@ -41215,13 +41377,13 @@
         </is>
       </c>
       <c r="I912" t="n">
-        <v>43.08</v>
+        <v>43.56</v>
       </c>
       <c r="J912" t="n">
-        <v>43.41</v>
+        <v>43.88</v>
       </c>
       <c r="K912" t="n">
-        <v>99.23999999999999</v>
+        <v>99.28</v>
       </c>
     </row>
     <row r="913">
@@ -41259,9 +41421,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I913" t="inlineStr"/>
-      <c r="J913" t="inlineStr"/>
-      <c r="K913" t="inlineStr"/>
+      <c r="I913" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="J913" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="K913" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="n">
@@ -41299,13 +41467,13 @@
         </is>
       </c>
       <c r="I914" t="n">
-        <v>84.08</v>
+        <v>83.95</v>
       </c>
       <c r="J914" t="n">
-        <v>85.20999999999999</v>
+        <v>84.78</v>
       </c>
       <c r="K914" t="n">
-        <v>98.67</v>
+        <v>99.02</v>
       </c>
     </row>
     <row r="915">
@@ -41842,10 +42010,10 @@
         <v>177.21</v>
       </c>
       <c r="J926" t="n">
-        <v>181.33</v>
+        <v>175.59</v>
       </c>
       <c r="K926" t="n">
-        <v>97.73</v>
+        <v>100.92</v>
       </c>
     </row>
     <row r="927">
@@ -41928,9 +42096,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I928" t="inlineStr"/>
-      <c r="J928" t="inlineStr"/>
-      <c r="K928" t="inlineStr"/>
+      <c r="I928" t="n">
+        <v>73.64</v>
+      </c>
+      <c r="J928" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="K928" t="n">
+        <v>100.33</v>
+      </c>
     </row>
     <row r="929">
       <c r="A929" t="n">
@@ -41971,10 +42145,10 @@
         <v>300.59</v>
       </c>
       <c r="J929" t="n">
-        <v>290.36</v>
+        <v>300.59</v>
       </c>
       <c r="K929" t="n">
-        <v>103.52</v>
+        <v>100</v>
       </c>
     </row>
     <row r="930">
@@ -42012,9 +42186,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I930" t="inlineStr"/>
-      <c r="J930" t="inlineStr"/>
-      <c r="K930" t="inlineStr"/>
+      <c r="I930" t="n">
+        <v>126.43</v>
+      </c>
+      <c r="J930" t="n">
+        <v>127.11</v>
+      </c>
+      <c r="K930" t="n">
+        <v>99.47</v>
+      </c>
     </row>
     <row r="931">
       <c r="A931" t="n">
@@ -43080,9 +43260,15 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I954" t="inlineStr"/>
-      <c r="J954" t="inlineStr"/>
-      <c r="K954" t="inlineStr"/>
+      <c r="I954" t="n">
+        <v>108.78</v>
+      </c>
+      <c r="J954" t="n">
+        <v>108.16</v>
+      </c>
+      <c r="K954" t="n">
+        <v>100.57</v>
+      </c>
     </row>
     <row r="955">
       <c r="A955" t="n">
@@ -43840,13 +44026,13 @@
         </is>
       </c>
       <c r="I971" t="n">
-        <v>48.55</v>
+        <v>48.5</v>
       </c>
       <c r="J971" t="n">
-        <v>47.59</v>
+        <v>49.11</v>
       </c>
       <c r="K971" t="n">
-        <v>102.02</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="972">
@@ -44002,13 +44188,13 @@
         </is>
       </c>
       <c r="I975" t="n">
-        <v>52.11</v>
+        <v>49.83</v>
       </c>
       <c r="J975" t="n">
         <v>44.81</v>
       </c>
       <c r="K975" t="n">
-        <v>116.29</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="976">
@@ -44047,13 +44233,13 @@
         </is>
       </c>
       <c r="I976" t="n">
-        <v>65.5</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="J976" t="n">
         <v>65.03</v>
       </c>
       <c r="K976" t="n">
-        <v>100.73</v>
+        <v>100.32</v>
       </c>
     </row>
     <row r="977">
@@ -46021,13 +46207,13 @@
         </is>
       </c>
       <c r="I1020" t="n">
-        <v>67.72</v>
+        <v>66.08</v>
       </c>
       <c r="J1020" t="n">
-        <v>67.73</v>
+        <v>66.05</v>
       </c>
       <c r="K1020" t="n">
-        <v>99.98999999999999</v>
+        <v>100.05</v>
       </c>
     </row>
     <row r="1021">
@@ -46599,10 +46785,10 @@
         <v>86.03</v>
       </c>
       <c r="J1033" t="n">
-        <v>85.48999999999999</v>
+        <v>85.39</v>
       </c>
       <c r="K1033" t="n">
-        <v>100.63</v>
+        <v>100.74</v>
       </c>
     </row>
     <row r="1034">
@@ -46730,12 +46916,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1036" t="inlineStr"/>
+      <c r="I1036" t="n">
+        <v>22.55</v>
+      </c>
       <c r="J1036" t="n">
         <v>22.4</v>
       </c>
       <c r="K1036" t="n">
-        <v>0</v>
+        <v>100.66</v>
       </c>
     </row>
     <row r="1037">
@@ -46773,12 +46961,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1037" t="inlineStr"/>
+      <c r="I1037" t="n">
+        <v>45.59</v>
+      </c>
       <c r="J1037" t="n">
-        <v>49.12</v>
+        <v>45.36</v>
       </c>
       <c r="K1037" t="n">
-        <v>0</v>
+        <v>100.51</v>
       </c>
     </row>
     <row r="1038">
@@ -46861,12 +47051,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1039" t="inlineStr"/>
+      <c r="I1039" t="n">
+        <v>12.12</v>
+      </c>
       <c r="J1039" t="n">
         <v>12.12</v>
       </c>
       <c r="K1039" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1040">
@@ -47039,12 +47231,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1043" t="inlineStr"/>
+      <c r="I1043" t="n">
+        <v>16.7</v>
+      </c>
       <c r="J1043" t="n">
         <v>16.68</v>
       </c>
       <c r="K1043" t="n">
-        <v>0</v>
+        <v>100.17</v>
       </c>
     </row>
     <row r="1044">
@@ -47127,12 +47321,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1045" t="inlineStr"/>
+      <c r="I1045" t="n">
+        <v>451.6</v>
+      </c>
       <c r="J1045" t="n">
-        <v>475.1</v>
+        <v>471.45</v>
       </c>
       <c r="K1045" t="n">
-        <v>0</v>
+        <v>95.79000000000001</v>
       </c>
     </row>
     <row r="1046">
@@ -47260,12 +47456,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1048" t="inlineStr"/>
+      <c r="I1048" t="n">
+        <v>17.8</v>
+      </c>
       <c r="J1048" t="n">
         <v>17.8</v>
       </c>
       <c r="K1048" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1049">
@@ -48020,10 +48218,10 @@
         </is>
       </c>
       <c r="I1065" t="n">
-        <v>38.88</v>
+        <v>38.55</v>
       </c>
       <c r="J1065" t="n">
-        <v>38.88</v>
+        <v>38.55</v>
       </c>
       <c r="K1065" t="n">
         <v>100</v>
@@ -48064,12 +48262,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1066" t="inlineStr"/>
+      <c r="I1066" t="n">
+        <v>144.67</v>
+      </c>
       <c r="J1066" t="n">
         <v>144.67</v>
       </c>
       <c r="K1066" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1067">
@@ -48108,13 +48308,13 @@
         </is>
       </c>
       <c r="I1067" t="n">
-        <v>18.57</v>
+        <v>18.56</v>
       </c>
       <c r="J1067" t="n">
         <v>18.56</v>
       </c>
       <c r="K1067" t="n">
-        <v>100.04</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1068">
@@ -48152,12 +48352,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1068" t="inlineStr"/>
+      <c r="I1068" t="n">
+        <v>43.2</v>
+      </c>
       <c r="J1068" t="n">
         <v>42.43</v>
       </c>
       <c r="K1068" t="n">
-        <v>0</v>
+        <v>101.82</v>
       </c>
     </row>
     <row r="1069">
@@ -48376,13 +48578,13 @@
         </is>
       </c>
       <c r="I1073" t="n">
-        <v>57.92</v>
+        <v>58.86</v>
       </c>
       <c r="J1073" t="n">
-        <v>58.66</v>
+        <v>58.49</v>
       </c>
       <c r="K1073" t="n">
-        <v>98.73</v>
+        <v>100.63</v>
       </c>
     </row>
     <row r="1074">
@@ -48421,13 +48623,13 @@
         </is>
       </c>
       <c r="I1074" t="n">
-        <v>49.33</v>
+        <v>48.96</v>
       </c>
       <c r="J1074" t="n">
         <v>47.75</v>
       </c>
       <c r="K1074" t="n">
-        <v>103.31</v>
+        <v>102.55</v>
       </c>
     </row>
     <row r="1075">
@@ -48556,13 +48758,13 @@
         </is>
       </c>
       <c r="I1077" t="n">
-        <v>30.3</v>
+        <v>29.16</v>
       </c>
       <c r="J1077" t="n">
         <v>29.16</v>
       </c>
       <c r="K1077" t="n">
-        <v>103.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1078">
@@ -48694,10 +48896,10 @@
         <v>143.19</v>
       </c>
       <c r="J1080" t="n">
-        <v>137.42</v>
+        <v>139.51</v>
       </c>
       <c r="K1080" t="n">
-        <v>104.19</v>
+        <v>102.64</v>
       </c>
     </row>
     <row r="1081">
@@ -48780,12 +48982,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1082" t="inlineStr"/>
+      <c r="I1082" t="n">
+        <v>285.2</v>
+      </c>
       <c r="J1082" t="n">
-        <v>285.79</v>
+        <v>285.2</v>
       </c>
       <c r="K1082" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1083">
@@ -52151,12 +52355,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1157" t="inlineStr"/>
+      <c r="I1157" t="n">
+        <v>476.9</v>
+      </c>
       <c r="J1157" t="n">
         <v>476.9</v>
       </c>
       <c r="K1157" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1158">
@@ -55298,13 +55504,13 @@
         </is>
       </c>
       <c r="I1227" t="n">
-        <v>116.72</v>
+        <v>116.49</v>
       </c>
       <c r="J1227" t="n">
         <v>98.42</v>
       </c>
       <c r="K1227" t="n">
-        <v>118.59</v>
+        <v>118.36</v>
       </c>
     </row>
     <row r="1228">
@@ -55433,10 +55639,10 @@
         </is>
       </c>
       <c r="I1230" t="n">
-        <v>81.31999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="J1230" t="n">
-        <v>79.05</v>
+        <v>80.05</v>
       </c>
       <c r="K1230" t="n">
         <v>102.88</v>
@@ -55567,12 +55773,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1233" t="inlineStr"/>
+      <c r="I1233" t="n">
+        <v>86.11</v>
+      </c>
       <c r="J1233" t="n">
-        <v>89.20999999999999</v>
+        <v>88.28</v>
       </c>
       <c r="K1233" t="n">
-        <v>0</v>
+        <v>97.54000000000001</v>
       </c>
     </row>
     <row r="1234">
@@ -55696,12 +55904,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1236" t="inlineStr"/>
+      <c r="I1236" t="n">
+        <v>104.72</v>
+      </c>
       <c r="J1236" t="n">
-        <v>89.98999999999999</v>
+        <v>102.35</v>
       </c>
       <c r="K1236" t="n">
-        <v>0</v>
+        <v>102.32</v>
       </c>
     </row>
     <row r="1237">
@@ -55739,12 +55949,14 @@
           <t>เหนือ</t>
         </is>
       </c>
-      <c r="I1237" t="inlineStr"/>
+      <c r="I1237" t="n">
+        <v>40.51</v>
+      </c>
       <c r="J1237" t="n">
         <v>39.2</v>
       </c>
       <c r="K1237" t="n">
-        <v>0</v>
+        <v>103.34</v>
       </c>
     </row>
     <row r="1238">
@@ -56053,13 +56265,13 @@
         </is>
       </c>
       <c r="I1244" t="n">
-        <v>123.32</v>
+        <v>131.76</v>
       </c>
       <c r="J1244" t="n">
-        <v>115.35</v>
+        <v>124.08</v>
       </c>
       <c r="K1244" t="n">
-        <v>106.91</v>
+        <v>106.19</v>
       </c>
     </row>
     <row r="1245">
@@ -59597,10 +59809,10 @@
         <v>25.37</v>
       </c>
       <c r="J1323" t="n">
-        <v>24.32</v>
+        <v>25.54</v>
       </c>
       <c r="K1323" t="n">
-        <v>104.3</v>
+        <v>99.33</v>
       </c>
     </row>
     <row r="1324">
@@ -60089,13 +60301,13 @@
         </is>
       </c>
       <c r="I1334" t="n">
-        <v>86.69</v>
+        <v>84.31</v>
       </c>
       <c r="J1334" t="n">
-        <v>88.01000000000001</v>
+        <v>85.48</v>
       </c>
       <c r="K1334" t="n">
-        <v>98.5</v>
+        <v>98.62</v>
       </c>
     </row>
     <row r="1335">
@@ -60134,13 +60346,13 @@
         </is>
       </c>
       <c r="I1335" t="n">
-        <v>62.09</v>
+        <v>62.07</v>
       </c>
       <c r="J1335" t="n">
-        <v>62.28</v>
+        <v>62.34</v>
       </c>
       <c r="K1335" t="n">
-        <v>99.7</v>
+        <v>99.56999999999999</v>
       </c>
     </row>
     <row r="1336">
@@ -60269,13 +60481,13 @@
         </is>
       </c>
       <c r="I1338" t="n">
-        <v>0</v>
+        <v>48.99</v>
       </c>
       <c r="J1338" t="n">
         <v>49.88</v>
       </c>
       <c r="K1338" t="n">
-        <v>0</v>
+        <v>98.23</v>
       </c>
     </row>
     <row r="1339">
@@ -60313,9 +60525,15 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1339" t="inlineStr"/>
-      <c r="J1339" t="inlineStr"/>
-      <c r="K1339" t="inlineStr"/>
+      <c r="I1339" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="J1339" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="K1339" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="1340">
       <c r="A1340" t="n">
@@ -60353,10 +60571,10 @@
         </is>
       </c>
       <c r="I1340" t="n">
-        <v>85.31999999999999</v>
+        <v>85.52</v>
       </c>
       <c r="J1340" t="n">
-        <v>86.26000000000001</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="K1340" t="n">
         <v>98.90000000000001</v>
@@ -61073,13 +61291,13 @@
         </is>
       </c>
       <c r="I1356" t="n">
-        <v>327.76</v>
+        <v>327.7</v>
       </c>
       <c r="J1356" t="n">
         <v>331.98</v>
       </c>
       <c r="K1356" t="n">
-        <v>98.73</v>
+        <v>98.70999999999999</v>
       </c>
     </row>
     <row r="1357">
@@ -63202,9 +63420,15 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1404" t="inlineStr"/>
-      <c r="J1404" t="inlineStr"/>
-      <c r="K1404" t="inlineStr"/>
+      <c r="I1404" t="n">
+        <v>88.56999999999999</v>
+      </c>
+      <c r="J1404" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="K1404" t="n">
+        <v>102.81</v>
+      </c>
     </row>
     <row r="1405">
       <c r="A1405" t="n">
@@ -64439,13 +64663,13 @@
         </is>
       </c>
       <c r="I1432" t="n">
-        <v>74.89</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="J1432" t="n">
         <v>71.59999999999999</v>
       </c>
       <c r="K1432" t="n">
-        <v>104.59</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="1433">
@@ -65783,13 +66007,13 @@
         </is>
       </c>
       <c r="I1462" t="n">
-        <v>132.71</v>
+        <v>133.5</v>
       </c>
       <c r="J1462" t="n">
         <v>132.36</v>
       </c>
       <c r="K1462" t="n">
-        <v>100.27</v>
+        <v>100.86</v>
       </c>
     </row>
     <row r="1463">
@@ -65873,13 +66097,13 @@
         </is>
       </c>
       <c r="I1464" t="n">
-        <v>21.23</v>
+        <v>21.26</v>
       </c>
       <c r="J1464" t="n">
         <v>21.23</v>
       </c>
       <c r="K1464" t="n">
-        <v>100.04</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="1465">
@@ -65918,13 +66142,13 @@
         </is>
       </c>
       <c r="I1465" t="n">
-        <v>48.15</v>
+        <v>48</v>
       </c>
       <c r="J1465" t="n">
         <v>47.51</v>
       </c>
       <c r="K1465" t="n">
-        <v>101.34</v>
+        <v>101.03</v>
       </c>
     </row>
     <row r="1466">
@@ -66098,10 +66322,10 @@
         </is>
       </c>
       <c r="I1469" t="n">
-        <v>31.93</v>
+        <v>33.13</v>
       </c>
       <c r="J1469" t="n">
-        <v>31.93</v>
+        <v>33.13</v>
       </c>
       <c r="K1469" t="n">
         <v>100</v>
@@ -66277,12 +66501,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1473" t="inlineStr"/>
+      <c r="I1473" t="n">
+        <v>364.71</v>
+      </c>
       <c r="J1473" t="n">
         <v>382.04</v>
       </c>
       <c r="K1473" t="n">
-        <v>0</v>
+        <v>95.45999999999999</v>
       </c>
     </row>
     <row r="1474">
@@ -67311,13 +67537,13 @@
         </is>
       </c>
       <c r="I1496" t="n">
-        <v>42.73</v>
+        <v>42.75</v>
       </c>
       <c r="J1496" t="n">
         <v>42.33</v>
       </c>
       <c r="K1496" t="n">
-        <v>100.94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1497">
@@ -67626,10 +67852,10 @@
         </is>
       </c>
       <c r="I1503" t="n">
-        <v>108.51</v>
+        <v>107.64</v>
       </c>
       <c r="J1503" t="n">
-        <v>109.29</v>
+        <v>108.43</v>
       </c>
       <c r="K1503" t="n">
         <v>99.28</v>
@@ -67986,10 +68212,10 @@
         </is>
       </c>
       <c r="I1511" t="n">
-        <v>361.38</v>
+        <v>296.77</v>
       </c>
       <c r="J1511" t="n">
-        <v>361.38</v>
+        <v>296.77</v>
       </c>
       <c r="K1511" t="n">
         <v>100</v>
@@ -68211,10 +68437,10 @@
         </is>
       </c>
       <c r="I1516" t="n">
-        <v>302.74</v>
+        <v>383.86</v>
       </c>
       <c r="J1516" t="n">
-        <v>302.74</v>
+        <v>383.86</v>
       </c>
       <c r="K1516" t="n">
         <v>100</v>
@@ -68256,10 +68482,10 @@
         </is>
       </c>
       <c r="I1517" t="n">
-        <v>255.16</v>
+        <v>253.95</v>
       </c>
       <c r="J1517" t="n">
-        <v>255.16</v>
+        <v>253.95</v>
       </c>
       <c r="K1517" t="n">
         <v>100</v>
@@ -68346,10 +68572,10 @@
         </is>
       </c>
       <c r="I1519" t="n">
-        <v>318.28</v>
+        <v>319.76</v>
       </c>
       <c r="J1519" t="n">
-        <v>318.28</v>
+        <v>319.76</v>
       </c>
       <c r="K1519" t="n">
         <v>100</v>
@@ -68391,10 +68617,10 @@
         </is>
       </c>
       <c r="I1520" t="n">
-        <v>73.09999999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="J1520" t="n">
-        <v>73.09999999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="K1520" t="n">
         <v>100</v>
@@ -68436,10 +68662,10 @@
         </is>
       </c>
       <c r="I1521" t="n">
-        <v>94.62</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="J1521" t="n">
-        <v>94.62</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="K1521" t="n">
         <v>100</v>
@@ -68526,10 +68752,10 @@
         </is>
       </c>
       <c r="I1523" t="n">
-        <v>159.69</v>
+        <v>216.69</v>
       </c>
       <c r="J1523" t="n">
-        <v>159.69</v>
+        <v>216.69</v>
       </c>
       <c r="K1523" t="n">
         <v>100</v>
@@ -68571,10 +68797,10 @@
         </is>
       </c>
       <c r="I1524" t="n">
-        <v>144.48</v>
+        <v>143.1</v>
       </c>
       <c r="J1524" t="n">
-        <v>144.48</v>
+        <v>143.1</v>
       </c>
       <c r="K1524" t="n">
         <v>100</v>
@@ -69111,10 +69337,10 @@
         </is>
       </c>
       <c r="I1536" t="n">
-        <v>314.4</v>
+        <v>312.29</v>
       </c>
       <c r="J1536" t="n">
-        <v>314.4</v>
+        <v>312.29</v>
       </c>
       <c r="K1536" t="n">
         <v>100</v>
@@ -69246,10 +69472,10 @@
         </is>
       </c>
       <c r="I1539" t="n">
-        <v>237.37</v>
+        <v>233.54</v>
       </c>
       <c r="J1539" t="n">
-        <v>237.37</v>
+        <v>233.54</v>
       </c>
       <c r="K1539" t="n">
         <v>100</v>
@@ -69561,10 +69787,10 @@
         </is>
       </c>
       <c r="I1546" t="n">
-        <v>32.33</v>
+        <v>32.73</v>
       </c>
       <c r="J1546" t="n">
-        <v>32.33</v>
+        <v>32.73</v>
       </c>
       <c r="K1546" t="n">
         <v>100</v>
@@ -69741,13 +69967,13 @@
         </is>
       </c>
       <c r="I1550" t="n">
-        <v>356.48</v>
+        <v>350.62</v>
       </c>
       <c r="J1550" t="n">
         <v>350.62</v>
       </c>
       <c r="K1550" t="n">
-        <v>101.67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1551">
@@ -70506,10 +70732,10 @@
         </is>
       </c>
       <c r="I1567" t="n">
-        <v>171.91</v>
+        <v>173.06</v>
       </c>
       <c r="J1567" t="n">
-        <v>171.79</v>
+        <v>172.95</v>
       </c>
       <c r="K1567" t="n">
         <v>100.07</v>
@@ -70551,13 +70777,13 @@
         </is>
       </c>
       <c r="I1568" t="n">
-        <v>472.24</v>
+        <v>483.49</v>
       </c>
       <c r="J1568" t="n">
-        <v>464.33</v>
+        <v>483.49</v>
       </c>
       <c r="K1568" t="n">
-        <v>101.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1569">
@@ -70596,13 +70822,13 @@
         </is>
       </c>
       <c r="I1569" t="n">
-        <v>41.12</v>
+        <v>46.37</v>
       </c>
       <c r="J1569" t="n">
-        <v>40.86</v>
+        <v>46.09</v>
       </c>
       <c r="K1569" t="n">
-        <v>100.64</v>
+        <v>100.61</v>
       </c>
     </row>
     <row r="1570">
@@ -70641,10 +70867,10 @@
         </is>
       </c>
       <c r="I1570" t="n">
-        <v>189.08</v>
+        <v>191.39</v>
       </c>
       <c r="J1570" t="n">
-        <v>187.76</v>
+        <v>190.04</v>
       </c>
       <c r="K1570" t="n">
         <v>100.71</v>
@@ -70821,10 +71047,10 @@
         </is>
       </c>
       <c r="I1574" t="n">
-        <v>423.85</v>
+        <v>481.06</v>
       </c>
       <c r="J1574" t="n">
-        <v>423.85</v>
+        <v>481.06</v>
       </c>
       <c r="K1574" t="n">
         <v>100</v>
@@ -70866,10 +71092,10 @@
         </is>
       </c>
       <c r="I1575" t="n">
-        <v>224.67</v>
+        <v>226.46</v>
       </c>
       <c r="J1575" t="n">
-        <v>224.67</v>
+        <v>226.46</v>
       </c>
       <c r="K1575" t="n">
         <v>100</v>
@@ -70910,12 +71136,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1576" t="inlineStr"/>
+      <c r="I1576" t="n">
+        <v>147.67</v>
+      </c>
       <c r="J1576" t="n">
         <v>147.67</v>
       </c>
       <c r="K1576" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1577">
@@ -73069,13 +73297,13 @@
         </is>
       </c>
       <c r="I1624" t="n">
-        <v>23.92</v>
+        <v>24.5</v>
       </c>
       <c r="J1624" t="n">
-        <v>22.79</v>
+        <v>23.16</v>
       </c>
       <c r="K1624" t="n">
-        <v>104.97</v>
+        <v>105.79</v>
       </c>
     </row>
     <row r="1625">
@@ -74689,13 +74917,13 @@
         </is>
       </c>
       <c r="I1660" t="n">
-        <v>61.88</v>
+        <v>61.72</v>
       </c>
       <c r="J1660" t="n">
         <v>62.71</v>
       </c>
       <c r="K1660" t="n">
-        <v>98.69</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="1661">
@@ -74734,10 +74962,10 @@
         </is>
       </c>
       <c r="I1661" t="n">
-        <v>97.54000000000001</v>
+        <v>100.43</v>
       </c>
       <c r="J1661" t="n">
-        <v>94.90000000000001</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="K1661" t="n">
         <v>102.79</v>
@@ -74779,13 +75007,13 @@
         </is>
       </c>
       <c r="I1662" t="n">
-        <v>62.79</v>
+        <v>62.53</v>
       </c>
       <c r="J1662" t="n">
         <v>62.53</v>
       </c>
       <c r="K1662" t="n">
-        <v>100.41</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1663">
@@ -74824,13 +75052,13 @@
         </is>
       </c>
       <c r="I1663" t="n">
-        <v>55.64</v>
+        <v>55.41</v>
       </c>
       <c r="J1663" t="n">
-        <v>54.18</v>
+        <v>54.33</v>
       </c>
       <c r="K1663" t="n">
-        <v>102.69</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="1664">
@@ -75048,12 +75276,14 @@
           <t>ใต้</t>
         </is>
       </c>
-      <c r="I1668" t="inlineStr"/>
+      <c r="I1668" t="n">
+        <v>61.08</v>
+      </c>
       <c r="J1668" t="n">
-        <v>60.49</v>
+        <v>62.03</v>
       </c>
       <c r="K1668" t="n">
-        <v>0</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="1669">
@@ -75448,13 +75678,13 @@
         </is>
       </c>
       <c r="I1677" t="n">
-        <v>69.23999999999999</v>
+        <v>70.14</v>
       </c>
       <c r="J1677" t="n">
         <v>66.23</v>
       </c>
       <c r="K1677" t="n">
-        <v>104.56</v>
+        <v>105.91</v>
       </c>
     </row>
     <row r="1678">
